--- a/database/event/2637/event_2637_evp_summary.xlsx
+++ b/database/event/2637/event_2637_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8311</v>
+        <v>7.4096</v>
       </c>
       <c r="C2" t="n">
-        <v>4.1587</v>
+        <v>4.5109</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3383</v>
+        <v>2.5081</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8311</v>
+        <v>7.4096</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4738</v>
+        <v>3.5523</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3573</v>
+        <v>3.8573</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4738</v>
+        <v>3.5523</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4969</v>
+        <v>3.6123</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3573</v>
+        <v>3.8573</v>
       </c>
       <c r="K2" t="n">
         <v>198</v>
@@ -529,7 +529,7 @@
         <v>211</v>
       </c>
       <c r="M2" t="n">
-        <v>6.854200000000001</v>
+        <v>7.4696</v>
       </c>
       <c r="N2" t="n">
         <v>409</v>
@@ -538,127 +538,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.7218</v>
+        <v>7.3372</v>
       </c>
       <c r="C3" t="n">
-        <v>4.0922</v>
+        <v>4.4668</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2941</v>
+        <v>2.4792</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7218</v>
+        <v>7.3372</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8645</v>
+        <v>3.5973</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8573</v>
+        <v>3.7399</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8645</v>
+        <v>3.5973</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8912</v>
+        <v>2.9157</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8573</v>
+        <v>3.7399</v>
       </c>
       <c r="K3" t="n">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="L3" t="n">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="M3" t="n">
-        <v>6.7485</v>
+        <v>6.6556</v>
       </c>
       <c r="N3" t="n">
-        <v>409</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4367</v>
+        <v>7.1823</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9186</v>
+        <v>4.3725</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1789</v>
+        <v>2.4175</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4367</v>
+        <v>7.1823</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6968</v>
+        <v>3.5414</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7399</v>
+        <v>3.6409</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6968</v>
+        <v>3.5414</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1858</v>
+        <v>3.6013</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7399</v>
+        <v>3.6409</v>
       </c>
       <c r="K4" t="n">
-        <v>146</v>
+        <v>198</v>
       </c>
       <c r="L4" t="n">
-        <v>161</v>
+        <v>211</v>
       </c>
       <c r="M4" t="n">
-        <v>5.9257</v>
+        <v>7.2422</v>
       </c>
       <c r="N4" t="n">
-        <v>307</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.3583</v>
+        <v>6.8857</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8709</v>
+        <v>4.192</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1473</v>
+        <v>2.2994</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3583</v>
+        <v>6.8857</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7174</v>
+        <v>2.5284</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6409</v>
+        <v>4.3573</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7174</v>
+        <v>2.5284</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7427</v>
+        <v>2.5711</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6409</v>
+        <v>4.3573</v>
       </c>
       <c r="K5" t="n">
         <v>198</v>
@@ -667,7 +667,7 @@
         <v>211</v>
       </c>
       <c r="M5" t="n">
-        <v>6.383599999999999</v>
+        <v>6.9284</v>
       </c>
       <c r="N5" t="n">
         <v>409</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.6352</v>
+        <v>5.9688</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4307</v>
+        <v>3.6338</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8551</v>
+        <v>1.9341</v>
       </c>
       <c r="E6" t="n">
-        <v>5.6352</v>
+        <v>5.9688</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3404</v>
+        <v>4.674</v>
       </c>
       <c r="G6" t="n">
         <v>1.2948</v>
       </c>
       <c r="H6" t="n">
-        <v>4.902</v>
+        <v>6.2441</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9732</v>
+        <v>5.061</v>
       </c>
       <c r="J6" t="n">
         <v>1.2948</v>
@@ -713,7 +713,7 @@
         <v>161</v>
       </c>
       <c r="M6" t="n">
-        <v>5.268</v>
+        <v>6.3558</v>
       </c>
       <c r="N6" t="n">
         <v>307</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9669</v>
+        <v>4.459</v>
       </c>
       <c r="C7" t="n">
-        <v>2.415</v>
+        <v>2.7146</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1812</v>
+        <v>1.3326</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9669</v>
+        <v>4.459</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4115</v>
+        <v>1.9036</v>
       </c>
       <c r="G7" t="n">
         <v>2.5554</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4115</v>
+        <v>1.9036</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4181</v>
+        <v>1.9196</v>
       </c>
       <c r="J7" t="n">
         <v>2.5554</v>
@@ -759,7 +759,7 @@
         <v>137</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9735</v>
+        <v>4.475</v>
       </c>
       <c r="N7" t="n">
         <v>312</v>
@@ -768,323 +768,323 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8208</v>
+        <v>3.6844</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7173</v>
+        <v>2.243</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7181999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8208</v>
+        <v>3.6844</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.09429999999999999</v>
+        <v>3.6844</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9151</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.09429999999999999</v>
+        <v>3.6844</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09470000000000001</v>
+        <v>3.6844</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9151</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="L8" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8204</v>
+        <v>3.6844</v>
       </c>
       <c r="N8" t="n">
-        <v>312</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7309</v>
+        <v>3.4671</v>
       </c>
       <c r="C9" t="n">
-        <v>1.6626</v>
+        <v>2.1107</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6819</v>
+        <v>0.9374</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7309</v>
+        <v>3.4671</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9859</v>
+        <v>3.4671</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.255</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9859</v>
+        <v>3.4671</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4201</v>
+        <v>3.4671</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.255</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="L9" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1651</v>
+        <v>3.4671</v>
       </c>
       <c r="N9" t="n">
-        <v>307</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5879</v>
+        <v>3.2957</v>
       </c>
       <c r="C10" t="n">
-        <v>1.5755</v>
+        <v>2.0064</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6241</v>
+        <v>0.8691</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5879</v>
+        <v>3.2957</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.46</v>
+        <v>3.5507</v>
       </c>
       <c r="G10" t="n">
-        <v>3.0479</v>
+        <v>-0.255</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.46</v>
+        <v>3.5507</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4642</v>
+        <v>2.8779</v>
       </c>
       <c r="J10" t="n">
-        <v>3.0479</v>
+        <v>-0.255</v>
       </c>
       <c r="K10" t="n">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="L10" t="n">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5837</v>
+        <v>2.6229</v>
       </c>
       <c r="N10" t="n">
-        <v>409</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2733</v>
+        <v>2.8745</v>
       </c>
       <c r="C11" t="n">
-        <v>1.384</v>
+        <v>1.75</v>
       </c>
       <c r="D11" t="n">
-        <v>0.497</v>
+        <v>0.7013</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2733</v>
+        <v>2.8745</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2733</v>
+        <v>-0.1734</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3.0479</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2733</v>
+        <v>-0.1734</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2733</v>
+        <v>-0.1763</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3.0479</v>
       </c>
       <c r="K11" t="n">
-        <v>118</v>
+        <v>198</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2733</v>
+        <v>2.8716</v>
       </c>
       <c r="N11" t="n">
-        <v>118</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1104</v>
+        <v>2.8212</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2848</v>
+        <v>1.7175</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4312</v>
+        <v>0.6801</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1104</v>
+        <v>2.8212</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6299</v>
+        <v>-0.0939</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5195</v>
+        <v>2.9151</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6299</v>
+        <v>-0.0939</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6299</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5195</v>
+        <v>2.9151</v>
       </c>
       <c r="K12" t="n">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="L12" t="n">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1104</v>
+        <v>2.8204</v>
       </c>
       <c r="N12" t="n">
-        <v>231</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0683</v>
+        <v>2.7018</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2592</v>
+        <v>1.6448</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4142</v>
+        <v>0.6325</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0683</v>
+        <v>2.7018</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0683</v>
+        <v>3.2213</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.5195</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0683</v>
+        <v>3.2213</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0683</v>
+        <v>3.2213</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.5195</v>
       </c>
       <c r="K13" t="n">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M13" t="n">
-        <v>2.0683</v>
+        <v>2.7018</v>
       </c>
       <c r="N13" t="n">
-        <v>128</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0382</v>
+        <v>2.5089</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2408</v>
+        <v>1.5274</v>
       </c>
       <c r="D14" t="n">
-        <v>0.402</v>
+        <v>0.5556</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0382</v>
+        <v>2.5089</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9205</v>
+        <v>2.5089</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8823</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9205</v>
+        <v>2.5089</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9205</v>
+        <v>2.5089</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8823</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L14" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0382</v>
+        <v>2.5089</v>
       </c>
       <c r="N14" t="n">
-        <v>176</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9867</v>
+        <v>2.4084</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2095</v>
+        <v>1.4662</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3812</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9867</v>
+        <v>2.4084</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5134</v>
+        <v>2.9351</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5266999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5134</v>
+        <v>2.9351</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0372</v>
+        <v>2.379</v>
       </c>
       <c r="J15" t="n">
         <v>-0.5266999999999999</v>
@@ -1127,7 +1127,7 @@
         <v>161</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5105</v>
+        <v>1.8523</v>
       </c>
       <c r="N15" t="n">
         <v>307</v>
@@ -1136,231 +1136,231 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9732</v>
+        <v>2.4015</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2013</v>
+        <v>1.462</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3758</v>
+        <v>0.5128</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9732</v>
+        <v>2.4015</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9732</v>
+        <v>3.2838</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.8823</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9732</v>
+        <v>3.2838</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9732</v>
+        <v>3.2838</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.8823</v>
       </c>
       <c r="K16" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9732</v>
+        <v>2.4015</v>
       </c>
       <c r="N16" t="n">
-        <v>128</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9689</v>
+        <v>2.2868</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1987</v>
+        <v>1.3922</v>
       </c>
       <c r="D17" t="n">
-        <v>0.374</v>
+        <v>0.4672</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9689</v>
+        <v>2.2868</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9689</v>
+        <v>2.2868</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9689</v>
+        <v>2.2868</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9689</v>
+        <v>2.2868</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9689</v>
+        <v>2.2868</v>
       </c>
       <c r="N17" t="n">
-        <v>149</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8446</v>
+        <v>2.2148</v>
       </c>
       <c r="C18" t="n">
-        <v>1.123</v>
+        <v>1.3484</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3238</v>
+        <v>0.4385</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8446</v>
+        <v>2.2148</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8446</v>
+        <v>2.2148</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8446</v>
+        <v>2.2148</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8446</v>
+        <v>2.2148</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8446</v>
+        <v>2.2148</v>
       </c>
       <c r="N18" t="n">
-        <v>128</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4839</v>
+        <v>1.9827</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9034</v>
+        <v>1.2071</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1781</v>
+        <v>0.346</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4839</v>
+        <v>1.9827</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5927</v>
+        <v>1.9827</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5927</v>
+        <v>1.9827</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2909</v>
+        <v>1.9827</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="L19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1821</v>
+        <v>1.9827</v>
       </c>
       <c r="N19" t="n">
-        <v>194</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3907</v>
+        <v>1.5887</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8466</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1404</v>
+        <v>0.189</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3907</v>
+        <v>1.5887</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3907</v>
+        <v>1.6975</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.1088</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3907</v>
+        <v>1.6975</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3907</v>
+        <v>1.3759</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.1088</v>
       </c>
       <c r="K20" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3907</v>
+        <v>1.2671</v>
       </c>
       <c r="N20" t="n">
-        <v>135</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2777</v>
+        <v>1.4062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7779</v>
+        <v>0.8561</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0948</v>
+        <v>0.1163</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2777</v>
+        <v>1.4062</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2777</v>
+        <v>1.4062</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2777</v>
+        <v>1.4062</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2777</v>
+        <v>1.4062</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2777</v>
+        <v>1.4062</v>
       </c>
       <c r="N21" t="n">
         <v>149</v>
@@ -1412,47 +1412,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.052</v>
+        <v>1.3907</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6404</v>
+        <v>0.8466</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0036</v>
+        <v>0.1101</v>
       </c>
       <c r="E22" t="n">
-        <v>1.052</v>
+        <v>1.3907</v>
       </c>
       <c r="F22" t="n">
-        <v>1.052</v>
+        <v>1.3907</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.052</v>
+        <v>1.3907</v>
       </c>
       <c r="I22" t="n">
-        <v>1.052</v>
+        <v>1.3907</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.052</v>
+        <v>1.3907</v>
       </c>
       <c r="N22" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9429</v>
+        <v>1.1058</v>
       </c>
       <c r="C23" t="n">
-        <v>0.574</v>
+        <v>0.6732</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0405</v>
+        <v>-0.0034</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9429</v>
+        <v>1.1058</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9429</v>
+        <v>1.1058</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9429</v>
+        <v>1.1058</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9429</v>
+        <v>1.1058</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9429</v>
+        <v>1.1058</v>
       </c>
       <c r="N23" t="n">
         <v>163</v>
@@ -1504,277 +1504,277 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8569</v>
+        <v>1.0724</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.6529</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0752</v>
+        <v>-0.0167</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8569</v>
+        <v>1.0724</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8569</v>
+        <v>1.0724</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8569</v>
+        <v>1.0724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8569</v>
+        <v>1.0724</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8569</v>
+        <v>1.0724</v>
       </c>
       <c r="N24" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6384</v>
+        <v>0.9048</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3887</v>
+        <v>0.5508</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1635</v>
+        <v>-0.0834</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6384</v>
+        <v>0.9048</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3019</v>
+        <v>0.4903</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3365</v>
+        <v>0.4145</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3019</v>
+        <v>0.4903</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3019</v>
+        <v>0.4903</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3365</v>
+        <v>0.4145</v>
       </c>
       <c r="K25" t="n">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="L25" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6384000000000001</v>
+        <v>0.9048</v>
       </c>
       <c r="N25" t="n">
-        <v>231</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6137</v>
+        <v>0.8569</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3736</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1734</v>
+        <v>-0.1025</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6137</v>
+        <v>0.8569</v>
       </c>
       <c r="F26" t="n">
-        <v>0.463</v>
+        <v>0.8569</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1507</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.463</v>
+        <v>0.8569</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3753</v>
+        <v>0.8569</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1507</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="L26" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.526</v>
+        <v>0.8569</v>
       </c>
       <c r="N26" t="n">
-        <v>194</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6078</v>
+        <v>0.6797</v>
       </c>
       <c r="C27" t="n">
-        <v>0.37</v>
+        <v>0.4138</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1758</v>
+        <v>-0.1731</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6078</v>
+        <v>0.6797</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1933</v>
+        <v>0.529</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4145</v>
+        <v>0.1507</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1933</v>
+        <v>0.529</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1933</v>
+        <v>0.4288</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4145</v>
+        <v>0.1507</v>
       </c>
       <c r="K27" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="L27" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6078</v>
+        <v>0.5795</v>
       </c>
       <c r="N27" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4168</v>
+        <v>0.6744</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2537</v>
+        <v>0.4106</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.253</v>
+        <v>-0.1752</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4168</v>
+        <v>0.6744</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4168</v>
+        <v>1.6744</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4168</v>
+        <v>1.6744</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4168</v>
+        <v>1.6744</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K28" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4168</v>
+        <v>0.6744000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>134</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3122</v>
+        <v>0.6384</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1901</v>
+        <v>0.3887</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2952</v>
+        <v>-0.1896</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3122</v>
+        <v>0.6384</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3122</v>
+        <v>0.3019</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.3365</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3122</v>
+        <v>0.3019</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3122</v>
+        <v>0.3019</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.3365</v>
       </c>
       <c r="K29" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3122</v>
+        <v>0.6384000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>134</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2798</v>
+        <v>0.6379</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1703</v>
+        <v>0.3883</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3083</v>
+        <v>-0.1898</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2798</v>
+        <v>0.6379</v>
       </c>
       <c r="F30" t="n">
-        <v>1.0103</v>
+        <v>1.3684</v>
       </c>
       <c r="G30" t="n">
         <v>-0.7305</v>
       </c>
       <c r="H30" t="n">
-        <v>1.0103</v>
+        <v>1.3684</v>
       </c>
       <c r="I30" t="n">
-        <v>1.0103</v>
+        <v>1.3684</v>
       </c>
       <c r="J30" t="n">
         <v>-0.7305</v>
@@ -1817,7 +1817,7 @@
         <v>45</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2797999999999999</v>
+        <v>0.6379</v>
       </c>
       <c r="N30" t="n">
         <v>176</v>
@@ -1826,403 +1826,403 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2121</v>
+        <v>0.6088</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1291</v>
+        <v>0.3706</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.3357</v>
+        <v>-0.2014</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2121</v>
+        <v>0.6088</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2121</v>
+        <v>0.6088</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2121</v>
+        <v>0.6088</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2121</v>
+        <v>0.6088</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2121</v>
+        <v>0.6088</v>
       </c>
       <c r="N31" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.199</v>
+        <v>0.399</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1211</v>
+        <v>0.2429</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.341</v>
+        <v>-0.2849</v>
       </c>
       <c r="E32" t="n">
-        <v>0.199</v>
+        <v>0.399</v>
       </c>
       <c r="F32" t="n">
-        <v>0.199</v>
+        <v>0.8892</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.4902</v>
       </c>
       <c r="H32" t="n">
-        <v>0.199</v>
+        <v>0.8892</v>
       </c>
       <c r="I32" t="n">
-        <v>0.199</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.4902</v>
       </c>
       <c r="K32" t="n">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="M32" t="n">
-        <v>0.199</v>
+        <v>0.4065</v>
       </c>
       <c r="N32" t="n">
-        <v>134</v>
+        <v>312</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1713</v>
+        <v>0.3831</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1043</v>
+        <v>0.2332</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3522</v>
+        <v>-0.2913</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1713</v>
+        <v>0.3831</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1713</v>
+        <v>1.1239</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.7408</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1713</v>
+        <v>1.1239</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1713</v>
+        <v>0.9109</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.7408</v>
       </c>
       <c r="K33" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1713</v>
+        <v>0.1701</v>
       </c>
       <c r="N33" t="n">
-        <v>149</v>
+        <v>307</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1476</v>
+        <v>0.3122</v>
       </c>
       <c r="C34" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.1901</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3617</v>
+        <v>-0.3195</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1476</v>
+        <v>0.3122</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6378</v>
+        <v>0.3122</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.4902</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6378</v>
+        <v>0.3122</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6407</v>
+        <v>0.3122</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.4902</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="L34" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1505</v>
+        <v>0.3122</v>
       </c>
       <c r="N34" t="n">
-        <v>312</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.2121</v>
       </c>
       <c r="C35" t="n">
-        <v>0.053</v>
+        <v>0.1291</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3862</v>
+        <v>-0.3594</v>
       </c>
       <c r="E35" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.2121</v>
       </c>
       <c r="F35" t="n">
-        <v>0.263</v>
+        <v>0.2121</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.176</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.263</v>
+        <v>0.2121</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2642</v>
+        <v>0.2121</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.176</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="L35" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0882</v>
+        <v>0.2121</v>
       </c>
       <c r="N35" t="n">
-        <v>312</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.0356</v>
+        <v>0.1713</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0217</v>
+        <v>0.1043</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.4357</v>
+        <v>-0.3757</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.0356</v>
+        <v>0.1713</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.0356</v>
+        <v>0.1713</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.0356</v>
+        <v>0.1713</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0356</v>
+        <v>0.1713</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.0356</v>
+        <v>0.1713</v>
       </c>
       <c r="N36" t="n">
-        <v>128</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.0626</v>
+        <v>0.1339</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0381</v>
+        <v>0.0815</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4467</v>
+        <v>-0.3906</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.0626</v>
+        <v>0.1339</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5501</v>
+        <v>0.3099</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6127</v>
+        <v>-0.176</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5501</v>
+        <v>0.3099</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4459</v>
+        <v>0.3125</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6127</v>
+        <v>-0.176</v>
       </c>
       <c r="K37" t="n">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="L37" t="n">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.1668</v>
+        <v>0.1365</v>
       </c>
       <c r="N37" t="n">
-        <v>194</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.06270000000000001</v>
+        <v>0.0056</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.0382</v>
+        <v>0.0034</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.4467</v>
+        <v>-0.4417</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.06270000000000001</v>
+        <v>0.0056</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.06270000000000001</v>
+        <v>0.0056</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.06270000000000001</v>
+        <v>0.0056</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.06270000000000001</v>
+        <v>0.0056</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.06270000000000001</v>
+        <v>0.0056</v>
       </c>
       <c r="N38" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.1318</v>
+        <v>0.0015</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.0009</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4746</v>
+        <v>-0.4433</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.1318</v>
+        <v>0.0015</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2432</v>
+        <v>0.6936</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.375</v>
+        <v>-0.6921</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2432</v>
+        <v>0.6936</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2432</v>
+        <v>0.6936</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.375</v>
+        <v>-0.6921</v>
       </c>
       <c r="K39" t="n">
         <v>145</v>
@@ -2231,7 +2231,7 @@
         <v>86</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.1318</v>
+        <v>0.001499999999999946</v>
       </c>
       <c r="N39" t="n">
         <v>231</v>
@@ -2240,185 +2240,185 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.1343</v>
+        <v>0.0015</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.0818</v>
+        <v>0.0009</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4756</v>
+        <v>-0.4433</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.1343</v>
+        <v>0.0015</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6065</v>
+        <v>0.0015</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7408</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6065</v>
+        <v>0.0015</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4916</v>
+        <v>0.0015</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7408</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="L40" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.2492</v>
+        <v>0.0015</v>
       </c>
       <c r="N40" t="n">
-        <v>307</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.146</v>
+        <v>-0.0116</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.0071</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4803</v>
+        <v>-0.4485</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.146</v>
+        <v>-0.0116</v>
       </c>
       <c r="F41" t="n">
-        <v>0.854</v>
+        <v>0.3634</v>
       </c>
       <c r="G41" t="n">
-        <v>-1</v>
+        <v>-0.375</v>
       </c>
       <c r="H41" t="n">
-        <v>0.854</v>
+        <v>0.3634</v>
       </c>
       <c r="I41" t="n">
-        <v>0.854</v>
+        <v>0.3634</v>
       </c>
       <c r="J41" t="n">
-        <v>-1</v>
+        <v>-0.375</v>
       </c>
       <c r="K41" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="L41" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.146</v>
+        <v>-0.0116</v>
       </c>
       <c r="N41" t="n">
-        <v>176</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1474</v>
+        <v>-0.0626</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0897</v>
+        <v>-0.0381</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4809</v>
+        <v>-0.4689</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1474</v>
+        <v>-0.0626</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1474</v>
+        <v>0.5501</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-0.6127</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1474</v>
+        <v>0.5501</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1474</v>
+        <v>0.4459</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-0.6127</v>
       </c>
       <c r="K42" t="n">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.1474</v>
+        <v>-0.1668</v>
       </c>
       <c r="N42" t="n">
-        <v>149</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.2424</v>
+        <v>-0.1474</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.1476</v>
+        <v>-0.0897</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5193</v>
+        <v>-0.5026</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.2424</v>
+        <v>-0.1474</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4497</v>
+        <v>-0.1474</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.6921</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4497</v>
+        <v>-0.1474</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4497</v>
+        <v>-0.1474</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.6921</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L43" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.2424000000000001</v>
+        <v>-0.1474</v>
       </c>
       <c r="N43" t="n">
-        <v>231</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44">
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.3346</v>
+        <v>-0.1781</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.2037</v>
+        <v>-0.1084</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5565</v>
+        <v>-0.5149</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.3346</v>
+        <v>-0.1781</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.3346</v>
+        <v>-0.1781</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.3346</v>
+        <v>-0.1781</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3346</v>
+        <v>-0.1781</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.3346</v>
+        <v>-0.1781</v>
       </c>
       <c r="N44" t="n">
         <v>163</v>
@@ -2470,93 +2470,93 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.4054</v>
+        <v>-0.3791</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.2468</v>
+        <v>-0.2308</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5851</v>
+        <v>-0.5949</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.4054</v>
+        <v>-0.3791</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.4054</v>
+        <v>0.4615</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.8406</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4054</v>
+        <v>0.4615</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4054</v>
+        <v>0.4615</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.8406</v>
       </c>
       <c r="K45" t="n">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.4054</v>
+        <v>-0.3791</v>
       </c>
       <c r="N45" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.4206</v>
+        <v>-0.4054</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2561</v>
+        <v>-0.2468</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5913</v>
+        <v>-0.6054</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.4206</v>
+        <v>-0.4054</v>
       </c>
       <c r="F46" t="n">
-        <v>0.42</v>
+        <v>-0.4054</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.8406</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.42</v>
+        <v>-0.4054</v>
       </c>
       <c r="I46" t="n">
-        <v>0.42</v>
+        <v>-0.4054</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.8406</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="L46" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.4206</v>
+        <v>-0.4054</v>
       </c>
       <c r="N46" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47">
@@ -2572,7 +2572,7 @@
         <v>-0.2771</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6052999999999999</v>
+        <v>-0.6253</v>
       </c>
       <c r="E47" t="n">
         <v>-0.4552</v>
@@ -2608,170 +2608,170 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6042</v>
+        <v>-0.4682</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.3678</v>
+        <v>-0.285</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6654</v>
+        <v>-0.6304</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.6042</v>
+        <v>-0.4682</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.3752</v>
+        <v>-0.4682</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.229</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.3752</v>
+        <v>-0.4682</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.3752</v>
+        <v>-0.4682</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.229</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="L48" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.6042</v>
+        <v>-0.4682</v>
       </c>
       <c r="N48" t="n">
-        <v>231</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.6929</v>
+        <v>-0.5145</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.4218</v>
+        <v>-0.3132</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7013</v>
+        <v>-0.6489</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.6929</v>
+        <v>-0.5145</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.6929</v>
+        <v>-0.5145</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.6929</v>
+        <v>-0.5145</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.6929</v>
+        <v>-0.5145</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.6929</v>
+        <v>-0.5145</v>
       </c>
       <c r="N49" t="n">
-        <v>163</v>
+        <v>149</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.7502</v>
+        <v>-0.6042</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.4567</v>
+        <v>-0.3678</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7244</v>
+        <v>-0.6846</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.7502</v>
+        <v>-0.6042</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.7502</v>
+        <v>-0.3752</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-0.229</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.7502</v>
+        <v>-0.3752</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.7502</v>
+        <v>-0.3752</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-0.229</v>
       </c>
       <c r="K50" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.7502</v>
+        <v>-0.6042</v>
       </c>
       <c r="N50" t="n">
-        <v>149</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.774</v>
+        <v>-0.6918</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.4712</v>
+        <v>-0.4212</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.734</v>
+        <v>-0.7195</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.774</v>
+        <v>-0.6918</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.774</v>
+        <v>-0.6918</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.774</v>
+        <v>-0.6918</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.774</v>
+        <v>-0.6918</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.774</v>
+        <v>-0.6918</v>
       </c>
       <c r="N51" t="n">
         <v>163</v>
@@ -2792,185 +2792,185 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.8321</v>
+        <v>-0.774</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.4712</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.7575</v>
+        <v>-0.7523</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.8321</v>
+        <v>-0.774</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.8321</v>
+        <v>-0.774</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.8321</v>
+        <v>-0.774</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.8321</v>
+        <v>-0.774</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.8321</v>
+        <v>-0.774</v>
       </c>
       <c r="N52" t="n">
-        <v>135</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.0494</v>
+        <v>-0.7804</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.6389</v>
+        <v>-0.4751</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-0.7548</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.0494</v>
+        <v>-0.7804</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.238</v>
+        <v>-0.7804</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.8114</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.238</v>
+        <v>-0.7804</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1929</v>
+        <v>-0.7804</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.8114</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="L53" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-1.0043</v>
+        <v>-0.7804</v>
       </c>
       <c r="N53" t="n">
-        <v>194</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.0504</v>
+        <v>-0.7876</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.6395</v>
+        <v>-0.4795</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.8457</v>
+        <v>-0.7577</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.0504</v>
+        <v>-0.7876</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.0504</v>
+        <v>0.0238</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>-0.8114</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.0504</v>
+        <v>0.0238</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0504</v>
+        <v>0.0193</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>-0.8114</v>
       </c>
       <c r="K54" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M54" t="n">
-        <v>-1.0504</v>
+        <v>-0.7921</v>
       </c>
       <c r="N54" t="n">
-        <v>128</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.0987</v>
+        <v>-0.8321</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.8652</v>
+        <v>-0.7754</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.0987</v>
+        <v>-0.8321</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.0987</v>
+        <v>-0.8321</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.0987</v>
+        <v>-0.8321</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.0987</v>
+        <v>-0.8321</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-1.0987</v>
+        <v>-0.8321</v>
       </c>
       <c r="N55" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56">
@@ -2986,7 +2986,7 @@
         <v>-0.7252999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.9186</v>
       </c>
       <c r="E56" t="n">
         <v>-1.1914</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.238</v>
+        <v>-1.2169</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.7537</v>
+        <v>-0.7408</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.9215</v>
+        <v>-0.9287</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.238</v>
+        <v>-1.2169</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.8239</v>
+        <v>-2.8028</v>
       </c>
       <c r="G57" t="n">
         <v>1.5859</v>
       </c>
       <c r="H57" t="n">
-        <v>-2.8239</v>
+        <v>-2.8028</v>
       </c>
       <c r="I57" t="n">
         <v>-2.8502</v>
@@ -3078,7 +3078,7 @@
         <v>-0.8935</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.0143</v>
+        <v>-1.0286</v>
       </c>
       <c r="E58" t="n">
         <v>-1.4677</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.6557</v>
+        <v>-1.5825</v>
       </c>
       <c r="C59" t="n">
-        <v>-1.008</v>
+        <v>-0.9634</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.0902</v>
+        <v>-1.0744</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.6557</v>
+        <v>-1.5825</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.8446</v>
       </c>
       <c r="G59" t="n">
         <v>-0.7379</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.8446</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.922</v>
+        <v>-0.8517</v>
       </c>
       <c r="J59" t="n">
         <v>-0.7379</v>
@@ -3151,7 +3151,7 @@
         <v>137</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.6599</v>
+        <v>-1.5896</v>
       </c>
       <c r="N59" t="n">
         <v>312</v>
@@ -3170,7 +3170,7 @@
         <v>-1.0239</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.1008</v>
+        <v>-1.1139</v>
       </c>
       <c r="E60" t="n">
         <v>-1.6818</v>
@@ -3216,7 +3216,7 @@
         <v>-1.7623</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.5908</v>
+        <v>-1.5972</v>
       </c>
       <c r="E61" t="n">
         <v>-2.8948</v>

--- a/database/event/2637/event_2637_evp_summary.xlsx
+++ b/database/event/2637/event_2637_evp_summary.xlsx
@@ -492,127 +492,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.4096</v>
+        <v>6.6585</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5109</v>
+        <v>4.0536</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5081</v>
+        <v>2.368</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4096</v>
+        <v>6.6585</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5523</v>
+        <v>3.2871</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8573</v>
+        <v>3.3714</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5523</v>
+        <v>6.0953</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6123</v>
+        <v>3.1693</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8573</v>
+        <v>3.3714</v>
       </c>
       <c r="K2" t="n">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="L2" t="n">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="M2" t="n">
-        <v>7.4696</v>
+        <v>6.540699999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>409</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.3372</v>
+        <v>6.4318</v>
       </c>
       <c r="C3" t="n">
-        <v>4.4668</v>
+        <v>3.9156</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4792</v>
+        <v>2.2656</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3372</v>
+        <v>6.4318</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5973</v>
+        <v>3.111</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7399</v>
+        <v>3.3208</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5973</v>
+        <v>3.4715</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9157</v>
+        <v>3.7629</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7399</v>
+        <v>3.3208</v>
       </c>
       <c r="K3" t="n">
-        <v>146</v>
+        <v>198</v>
       </c>
       <c r="L3" t="n">
-        <v>161</v>
+        <v>211</v>
       </c>
       <c r="M3" t="n">
-        <v>6.6556</v>
+        <v>7.0837</v>
       </c>
       <c r="N3" t="n">
-        <v>307</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.1823</v>
+        <v>6.3558</v>
       </c>
       <c r="C4" t="n">
-        <v>4.3725</v>
+        <v>3.8694</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4175</v>
+        <v>2.2313</v>
       </c>
       <c r="E4" t="n">
-        <v>7.1823</v>
+        <v>6.3558</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5414</v>
+        <v>3.0952</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6409</v>
+        <v>3.2606</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5414</v>
+        <v>3.4368</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6013</v>
+        <v>3.7253</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6409</v>
+        <v>3.2606</v>
       </c>
       <c r="K4" t="n">
         <v>198</v>
@@ -621,7 +621,7 @@
         <v>211</v>
       </c>
       <c r="M4" t="n">
-        <v>7.2422</v>
+        <v>6.9859</v>
       </c>
       <c r="N4" t="n">
         <v>409</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.8857</v>
+        <v>6.3443</v>
       </c>
       <c r="C5" t="n">
-        <v>4.192</v>
+        <v>3.8624</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2994</v>
+        <v>2.2261</v>
       </c>
       <c r="E5" t="n">
-        <v>6.8857</v>
+        <v>6.3443</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5284</v>
+        <v>2.4439</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3573</v>
+        <v>3.9004</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5284</v>
+        <v>2.4439</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5711</v>
+        <v>2.6491</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3573</v>
+        <v>3.9004</v>
       </c>
       <c r="K5" t="n">
         <v>198</v>
@@ -667,7 +667,7 @@
         <v>211</v>
       </c>
       <c r="M5" t="n">
-        <v>6.9284</v>
+        <v>6.5495</v>
       </c>
       <c r="N5" t="n">
         <v>409</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.9688</v>
+        <v>5.7178</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6338</v>
+        <v>3.481</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9341</v>
+        <v>1.9433</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9688</v>
+        <v>5.7178</v>
       </c>
       <c r="F6" t="n">
-        <v>4.674</v>
+        <v>4.2743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2948</v>
+        <v>1.4435</v>
       </c>
       <c r="H6" t="n">
-        <v>6.2441</v>
+        <v>9.5738</v>
       </c>
       <c r="I6" t="n">
-        <v>5.061</v>
+        <v>4.9779</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2948</v>
+        <v>1.4435</v>
       </c>
       <c r="K6" t="n">
         <v>146</v>
@@ -713,7 +713,7 @@
         <v>161</v>
       </c>
       <c r="M6" t="n">
-        <v>6.3558</v>
+        <v>6.4214</v>
       </c>
       <c r="N6" t="n">
         <v>307</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.459</v>
+        <v>4.0107</v>
       </c>
       <c r="C7" t="n">
-        <v>2.7146</v>
+        <v>2.4417</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3326</v>
+        <v>1.1726</v>
       </c>
       <c r="E7" t="n">
-        <v>4.459</v>
+        <v>4.0107</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9036</v>
+        <v>1.8589</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5554</v>
+        <v>2.1517</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9036</v>
+        <v>1.8589</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9196</v>
+        <v>1.9354</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5554</v>
+        <v>2.1517</v>
       </c>
       <c r="K7" t="n">
         <v>175</v>
@@ -759,7 +759,7 @@
         <v>137</v>
       </c>
       <c r="M7" t="n">
-        <v>4.475</v>
+        <v>4.0871</v>
       </c>
       <c r="N7" t="n">
         <v>312</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6844</v>
+        <v>3.3891</v>
       </c>
       <c r="C8" t="n">
-        <v>2.243</v>
+        <v>2.0633</v>
       </c>
       <c r="D8" t="n">
-        <v>1.024</v>
+        <v>0.892</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6844</v>
+        <v>3.3891</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6844</v>
+        <v>3.1993</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.1898</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6844</v>
+        <v>5.7861</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6844</v>
+        <v>3.0085</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.1898</v>
       </c>
       <c r="K8" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6844</v>
+        <v>3.1983</v>
       </c>
       <c r="N8" t="n">
-        <v>118</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4671</v>
+        <v>3.1563</v>
       </c>
       <c r="C9" t="n">
-        <v>2.1107</v>
+        <v>1.9215</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9374</v>
+        <v>0.7869</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4671</v>
+        <v>3.1563</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4671</v>
+        <v>3.1563</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4671</v>
+        <v>3.571</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4671</v>
+        <v>3.571</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4671</v>
+        <v>3.571</v>
       </c>
       <c r="N9" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2957</v>
+        <v>3.0364</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0064</v>
+        <v>1.8485</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8691</v>
+        <v>0.7328</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2957</v>
+        <v>3.0364</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5507</v>
+        <v>3.0364</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.255</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5507</v>
+        <v>3.3077</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8779</v>
+        <v>3.3077</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.255</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="L10" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6229</v>
+        <v>3.3077</v>
       </c>
       <c r="N10" t="n">
-        <v>307</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8745</v>
+        <v>2.9632</v>
       </c>
       <c r="C11" t="n">
-        <v>1.75</v>
+        <v>1.804</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7013</v>
+        <v>0.6997</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8745</v>
+        <v>2.9632</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1734</v>
+        <v>0.2244</v>
       </c>
       <c r="G11" t="n">
-        <v>3.0479</v>
+        <v>2.7388</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1734</v>
+        <v>0.2244</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1763</v>
+        <v>0.2432</v>
       </c>
       <c r="J11" t="n">
-        <v>3.0479</v>
+        <v>2.7388</v>
       </c>
       <c r="K11" t="n">
         <v>198</v>
@@ -943,7 +943,7 @@
         <v>211</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8716</v>
+        <v>2.982</v>
       </c>
       <c r="N11" t="n">
         <v>409</v>
@@ -952,645 +952,645 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8212</v>
+        <v>2.7765</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7175</v>
+        <v>1.6903</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6801</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8212</v>
+        <v>2.7765</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0939</v>
+        <v>2.9769</v>
       </c>
       <c r="G12" t="n">
-        <v>2.9151</v>
+        <v>-0.2004</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0939</v>
+        <v>5.0026</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.09470000000000001</v>
+        <v>2.6011</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9151</v>
+        <v>-0.2004</v>
       </c>
       <c r="K12" t="n">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="L12" t="n">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8204</v>
+        <v>2.4007</v>
       </c>
       <c r="N12" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7018</v>
+        <v>2.6922</v>
       </c>
       <c r="C13" t="n">
-        <v>1.6448</v>
+        <v>1.639</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6325</v>
+        <v>0.5774</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7018</v>
+        <v>2.6922</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2213</v>
+        <v>0.276</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5195</v>
+        <v>2.4162</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2213</v>
+        <v>0.276</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2213</v>
+        <v>0.2873</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5195</v>
+        <v>2.4162</v>
       </c>
       <c r="K13" t="n">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="L13" t="n">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7018</v>
+        <v>2.7035</v>
       </c>
       <c r="N13" t="n">
-        <v>231</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5089</v>
+        <v>2.6779</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5274</v>
+        <v>1.6303</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5556</v>
+        <v>0.5709</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5089</v>
+        <v>2.6779</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5089</v>
+        <v>3.0233</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.3454</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5089</v>
+        <v>3.2788</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5089</v>
+        <v>3.2788</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.3454</v>
       </c>
       <c r="K14" t="n">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5089</v>
+        <v>2.9334</v>
       </c>
       <c r="N14" t="n">
-        <v>128</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4084</v>
+        <v>2.6183</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4662</v>
+        <v>1.594</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.544</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4084</v>
+        <v>2.6183</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9351</v>
+        <v>2.6183</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5266999999999999</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9351</v>
+        <v>2.6183</v>
       </c>
       <c r="I15" t="n">
-        <v>2.379</v>
+        <v>2.6183</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5266999999999999</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L15" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8523</v>
+        <v>2.6183</v>
       </c>
       <c r="N15" t="n">
-        <v>307</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4015</v>
+        <v>2.5998</v>
       </c>
       <c r="C16" t="n">
-        <v>1.462</v>
+        <v>1.5827</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5128</v>
+        <v>0.5357</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4015</v>
+        <v>2.5998</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2838</v>
+        <v>2.5998</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8823</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2838</v>
+        <v>2.5998</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2838</v>
+        <v>2.5998</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8823</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L16" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4015</v>
+        <v>2.5998</v>
       </c>
       <c r="N16" t="n">
-        <v>176</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2868</v>
+        <v>2.5097</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3922</v>
+        <v>1.5279</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4672</v>
+        <v>0.495</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2868</v>
+        <v>2.5097</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2868</v>
+        <v>3.1472</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.6375</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2868</v>
+        <v>3.5509</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2868</v>
+        <v>3.5509</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.6375</v>
       </c>
       <c r="K17" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2868</v>
+        <v>2.9134</v>
       </c>
       <c r="N17" t="n">
-        <v>128</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2148</v>
+        <v>2.4934</v>
       </c>
       <c r="C18" t="n">
-        <v>1.3484</v>
+        <v>1.518</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4385</v>
+        <v>0.4876</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2148</v>
+        <v>2.4934</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2148</v>
+        <v>2.4934</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2148</v>
+        <v>2.4934</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2148</v>
+        <v>2.4934</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.2148</v>
+        <v>2.4934</v>
       </c>
       <c r="N18" t="n">
-        <v>149</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9827</v>
+        <v>2.4026</v>
       </c>
       <c r="C19" t="n">
-        <v>1.2071</v>
+        <v>1.4627</v>
       </c>
       <c r="D19" t="n">
-        <v>0.346</v>
+        <v>0.4466</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9827</v>
+        <v>2.4026</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9827</v>
+        <v>2.4106</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9827</v>
+        <v>3.007</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9827</v>
+        <v>1.5635</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="K19" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9827</v>
+        <v>1.5555</v>
       </c>
       <c r="N19" t="n">
-        <v>134</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5887</v>
+        <v>2.0165</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9671999999999999</v>
+        <v>1.2276</v>
       </c>
       <c r="D20" t="n">
-        <v>0.189</v>
+        <v>0.2723</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5887</v>
+        <v>2.0165</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6975</v>
+        <v>2.0165</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6975</v>
+        <v>2.0165</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3759</v>
+        <v>2.0165</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="L20" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2671</v>
+        <v>2.0165</v>
       </c>
       <c r="N20" t="n">
-        <v>194</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4062</v>
+        <v>1.8173</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8561</v>
+        <v>1.1064</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1163</v>
+        <v>0.1824</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4062</v>
+        <v>1.8173</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4062</v>
+        <v>1.8173</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4062</v>
+        <v>1.8173</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4062</v>
+        <v>1.8173</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4062</v>
+        <v>1.8173</v>
       </c>
       <c r="N21" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3907</v>
+        <v>1.7588</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8466</v>
+        <v>1.0707</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1101</v>
+        <v>0.156</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3907</v>
+        <v>1.7588</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3907</v>
+        <v>2.1584</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.3996</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3907</v>
+        <v>2.1584</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3907</v>
+        <v>1.1223</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.3996</v>
       </c>
       <c r="K22" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3907</v>
+        <v>0.7227000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>135</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1058</v>
+        <v>1.7176</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6732</v>
+        <v>1.0457</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0034</v>
+        <v>0.1374</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1058</v>
+        <v>1.7176</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1058</v>
+        <v>1.7176</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1058</v>
+        <v>1.7176</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1058</v>
+        <v>1.7176</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1058</v>
+        <v>1.7176</v>
       </c>
       <c r="N23" t="n">
-        <v>163</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0724</v>
+        <v>1.68</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6529</v>
+        <v>1.0228</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0167</v>
+        <v>0.1204</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0724</v>
+        <v>1.68</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0724</v>
+        <v>1.5546</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.1254</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0724</v>
+        <v>1.5546</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0724</v>
+        <v>0.8083</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.1254</v>
       </c>
       <c r="K24" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0724</v>
+        <v>0.9337</v>
       </c>
       <c r="N24" t="n">
-        <v>134</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9048</v>
+        <v>1.4856</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5508</v>
+        <v>0.9044</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0834</v>
+        <v>0.0327</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9048</v>
+        <v>1.4856</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4903</v>
+        <v>1.4856</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4145</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4903</v>
+        <v>1.4856</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4903</v>
+        <v>1.4856</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4145</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="L25" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9048</v>
+        <v>1.4856</v>
       </c>
       <c r="N25" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8569</v>
+        <v>1.269</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.7726</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1025</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8569</v>
+        <v>1.269</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8569</v>
+        <v>1.269</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8569</v>
+        <v>1.269</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8569</v>
+        <v>1.269</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8569</v>
+        <v>1.269</v>
       </c>
       <c r="N26" t="n">
         <v>135</v>
@@ -1642,81 +1642,81 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6797</v>
+        <v>1.2419</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4138</v>
+        <v>0.7561</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1731</v>
+        <v>-0.0774</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6797</v>
+        <v>1.2419</v>
       </c>
       <c r="F27" t="n">
-        <v>0.529</v>
+        <v>1.2419</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1507</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.529</v>
+        <v>1.2419</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4288</v>
+        <v>1.2419</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1507</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="L27" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5795</v>
+        <v>1.2419</v>
       </c>
       <c r="N27" t="n">
-        <v>194</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6744</v>
+        <v>1.1648</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4106</v>
+        <v>0.7091</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1752</v>
+        <v>-0.1122</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6744</v>
+        <v>1.1648</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6744</v>
+        <v>1.6909</v>
       </c>
       <c r="G28" t="n">
-        <v>-1</v>
+        <v>-0.5261</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6744</v>
+        <v>1.6909</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6744</v>
+        <v>1.6909</v>
       </c>
       <c r="J28" t="n">
-        <v>-1</v>
+        <v>-0.5261</v>
       </c>
       <c r="K28" t="n">
         <v>131</v>
@@ -1725,7 +1725,7 @@
         <v>45</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6744000000000001</v>
+        <v>1.1648</v>
       </c>
       <c r="N28" t="n">
         <v>176</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6384</v>
+        <v>1.0542</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3887</v>
+        <v>0.6418</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1896</v>
+        <v>-0.1621</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6384</v>
+        <v>1.0542</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3019</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3365</v>
+        <v>0.3511</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3019</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3019</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3365</v>
+        <v>0.3511</v>
       </c>
       <c r="K29" t="n">
         <v>145</v>
@@ -1771,7 +1771,7 @@
         <v>86</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6384000000000001</v>
+        <v>1.0542</v>
       </c>
       <c r="N29" t="n">
         <v>231</v>
@@ -1780,599 +1780,599 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6379</v>
+        <v>1.0522</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3883</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1898</v>
+        <v>-0.163</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6379</v>
+        <v>1.0522</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3684</v>
+        <v>1.0522</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.7305</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.3684</v>
+        <v>1.0522</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3684</v>
+        <v>1.0522</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.7305</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L30" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6379</v>
+        <v>1.0522</v>
       </c>
       <c r="N30" t="n">
-        <v>176</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6088</v>
+        <v>0.9438</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3706</v>
+        <v>0.5746</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2014</v>
+        <v>-0.2119</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6088</v>
+        <v>0.9438</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6088</v>
+        <v>0.5505</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.3933</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6088</v>
+        <v>0.5505</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6088</v>
+        <v>0.5505</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.3933</v>
       </c>
       <c r="K31" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6088</v>
+        <v>0.9438</v>
       </c>
       <c r="N31" t="n">
-        <v>134</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.399</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2429</v>
+        <v>0.5079</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2849</v>
+        <v>-0.2614</v>
       </c>
       <c r="E32" t="n">
-        <v>0.399</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8892</v>
+        <v>1.8342</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.4902</v>
+        <v>-1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8892</v>
+        <v>1.8342</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8967000000000001</v>
+        <v>1.8342</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.4902</v>
+        <v>-1</v>
       </c>
       <c r="K32" t="n">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="L32" t="n">
-        <v>137</v>
+        <v>45</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4065</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>312</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.3831</v>
+        <v>0.8117</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2332</v>
+        <v>0.4942</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2913</v>
+        <v>-0.2716</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3831</v>
+        <v>0.8117</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1239</v>
+        <v>1.2299</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.7408</v>
+        <v>-0.4182</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1239</v>
+        <v>1.2299</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9109</v>
+        <v>0.6395</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.7408</v>
+        <v>-0.4182</v>
       </c>
       <c r="K33" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="L33" t="n">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1701</v>
+        <v>0.2212999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>307</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.3122</v>
+        <v>0.7065</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1901</v>
+        <v>0.4301</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3195</v>
+        <v>-0.3191</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3122</v>
+        <v>0.7065</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3122</v>
+        <v>1.0876</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.3811</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3122</v>
+        <v>1.0876</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3122</v>
+        <v>1.1323</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.3811</v>
       </c>
       <c r="K34" t="n">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="M34" t="n">
-        <v>0.3122</v>
+        <v>0.7512000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>134</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.2121</v>
+        <v>0.5965</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1291</v>
+        <v>0.3631</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3594</v>
+        <v>-0.3687</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2121</v>
+        <v>0.5965</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2121</v>
+        <v>1.0469</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.4504</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2121</v>
+        <v>1.0469</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2121</v>
+        <v>1.0469</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.4504</v>
       </c>
       <c r="K35" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2121</v>
+        <v>0.5964999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>135</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.1713</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1043</v>
+        <v>0.3465</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3757</v>
+        <v>-0.3811</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1713</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1713</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1713</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1713</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1713</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>149</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1339</v>
+        <v>0.521</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0815</v>
+        <v>0.3172</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3906</v>
+        <v>-0.4028</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1339</v>
+        <v>0.521</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3099</v>
+        <v>0.521</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.176</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3099</v>
+        <v>0.521</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3125</v>
+        <v>0.521</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.176</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="L37" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1365</v>
+        <v>0.521</v>
       </c>
       <c r="N37" t="n">
-        <v>312</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.0056</v>
+        <v>0.5102</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0034</v>
+        <v>0.3106</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.4417</v>
+        <v>-0.4077</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0056</v>
+        <v>0.5102</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0056</v>
+        <v>0.5102</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0056</v>
+        <v>0.5102</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0056</v>
+        <v>0.5102</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.0056</v>
+        <v>0.5102</v>
       </c>
       <c r="N38" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0015</v>
+        <v>0.4876</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0009</v>
+        <v>0.2968</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4433</v>
+        <v>-0.4179</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0015</v>
+        <v>0.4876</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6936</v>
+        <v>0.4876</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.6921</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6936</v>
+        <v>0.4876</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6936</v>
+        <v>0.4876</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.6921</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="L39" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.001499999999999946</v>
+        <v>0.4876</v>
       </c>
       <c r="N39" t="n">
-        <v>231</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0015</v>
+        <v>0.46</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0009</v>
+        <v>0.28</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4433</v>
+        <v>-0.4303</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0015</v>
+        <v>0.46</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0015</v>
+        <v>0.5782</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.1182</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0015</v>
+        <v>0.5782</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0015</v>
+        <v>0.602</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.1182</v>
       </c>
       <c r="K40" t="n">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="M40" t="n">
-        <v>0.0015</v>
+        <v>0.4838</v>
       </c>
       <c r="N40" t="n">
-        <v>118</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.0116</v>
+        <v>0.4138</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.0071</v>
+        <v>0.2519</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4485</v>
+        <v>-0.4512</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.0116</v>
+        <v>0.4138</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3634</v>
+        <v>0.4138</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.375</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3634</v>
+        <v>0.4138</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3634</v>
+        <v>0.4138</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.375</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="L41" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.0116</v>
+        <v>0.4138</v>
       </c>
       <c r="N41" t="n">
-        <v>231</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.0626</v>
+        <v>0.3372</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0381</v>
+        <v>0.2053</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4689</v>
+        <v>-0.4858</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.0626</v>
+        <v>0.3372</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5501</v>
+        <v>0.5527</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.6127</v>
+        <v>-0.2155</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5501</v>
+        <v>0.5527</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4459</v>
+        <v>0.5527</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.6127</v>
+        <v>-0.2155</v>
       </c>
       <c r="K42" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="L42" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.1668</v>
+        <v>0.3371999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>194</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.1474</v>
+        <v>0.2885</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0897</v>
+        <v>0.1756</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5026</v>
+        <v>-0.5078</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.1474</v>
+        <v>0.2885</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.1474</v>
+        <v>0.2885</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.1474</v>
+        <v>0.2885</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1474</v>
+        <v>0.2885</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.1474</v>
+        <v>0.2885</v>
       </c>
       <c r="N43" t="n">
         <v>149</v>
@@ -2424,277 +2424,277 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.1781</v>
+        <v>0.2072</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.1084</v>
+        <v>0.1261</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5149</v>
+        <v>-0.5445</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.1781</v>
+        <v>0.2072</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.1781</v>
+        <v>0.8032</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-0.596</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.1781</v>
+        <v>0.8032</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1781</v>
+        <v>0.8032</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-0.596</v>
       </c>
       <c r="K44" t="n">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.1781</v>
+        <v>0.2072000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.3791</v>
+        <v>0.1802</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.2308</v>
+        <v>0.1097</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5949</v>
+        <v>-0.5567</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.3791</v>
+        <v>0.1802</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4615</v>
+        <v>0.1802</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.8406</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4615</v>
+        <v>0.1802</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4615</v>
+        <v>0.1802</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.8406</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="L45" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.3791</v>
+        <v>0.1802</v>
       </c>
       <c r="N45" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.4054</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2468</v>
+        <v>0.0444</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6054</v>
+        <v>-0.6051</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.4054</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.4054</v>
+        <v>0.5939</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-0.521</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.4054</v>
+        <v>0.5939</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4054</v>
+        <v>0.3088</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-0.521</v>
       </c>
       <c r="K46" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.4054</v>
+        <v>-0.2122</v>
       </c>
       <c r="N46" t="n">
-        <v>163</v>
+        <v>194</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.4552</v>
+        <v>-0.0515</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.2771</v>
+        <v>-0.0314</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6253</v>
+        <v>-0.6613</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.4552</v>
+        <v>-0.0515</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.4552</v>
+        <v>-0.0515</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.4552</v>
+        <v>-0.0515</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.4552</v>
+        <v>-0.0515</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.4552</v>
+        <v>-0.0515</v>
       </c>
       <c r="N47" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.4682</v>
+        <v>-0.0736</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.285</v>
+        <v>-0.0448</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6304</v>
+        <v>-0.6712</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.4682</v>
+        <v>-0.0736</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.4682</v>
+        <v>-0.0736</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.4682</v>
+        <v>-0.0736</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.4682</v>
+        <v>-0.0736</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.4682</v>
+        <v>-0.0736</v>
       </c>
       <c r="N48" t="n">
-        <v>128</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.5145</v>
+        <v>-0.1663</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.3132</v>
+        <v>-0.1012</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6489</v>
+        <v>-0.7131</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.5145</v>
+        <v>-0.1663</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.5145</v>
+        <v>-0.1663</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.5145</v>
+        <v>-0.1663</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5145</v>
+        <v>-0.1663</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.5145</v>
+        <v>-0.1663</v>
       </c>
       <c r="N49" t="n">
-        <v>149</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50">
@@ -2704,31 +2704,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.6042</v>
+        <v>-0.1746</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.3678</v>
+        <v>-0.1063</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.6846</v>
+        <v>-0.7168</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.6042</v>
+        <v>-0.1746</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.3752</v>
+        <v>-0.0436</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.229</v>
+        <v>-0.131</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.3752</v>
+        <v>-0.0436</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3752</v>
+        <v>-0.0436</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.229</v>
+        <v>-0.131</v>
       </c>
       <c r="K50" t="n">
         <v>145</v>
@@ -2737,7 +2737,7 @@
         <v>86</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.6042</v>
+        <v>-0.1746</v>
       </c>
       <c r="N50" t="n">
         <v>231</v>
@@ -2746,415 +2746,415 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.6918</v>
+        <v>-0.1848</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.4212</v>
+        <v>-0.1125</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.7195</v>
+        <v>-0.7214</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.6918</v>
+        <v>-0.1848</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.6918</v>
+        <v>-0.1848</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.6918</v>
+        <v>-0.1848</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6918</v>
+        <v>-0.1848</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.6918</v>
+        <v>-0.1848</v>
       </c>
       <c r="N51" t="n">
-        <v>163</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.774</v>
+        <v>-0.2025</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.4712</v>
+        <v>-0.1233</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.7523</v>
+        <v>-0.7294</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.774</v>
+        <v>-0.2025</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.774</v>
+        <v>-0.2025</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.774</v>
+        <v>-0.2025</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.774</v>
+        <v>-0.2025</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.774</v>
+        <v>-0.2025</v>
       </c>
       <c r="N52" t="n">
-        <v>163</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.7804</v>
+        <v>-0.2313</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.4751</v>
+        <v>-0.1408</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.7548</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.7804</v>
+        <v>-0.2313</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.7804</v>
+        <v>-0.2313</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.7804</v>
+        <v>-0.2313</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.7804</v>
+        <v>-0.2313</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.7804</v>
+        <v>-0.2313</v>
       </c>
       <c r="N53" t="n">
-        <v>118</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.7876</v>
+        <v>-0.3075</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.4795</v>
+        <v>-0.1872</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.7577</v>
+        <v>-0.7768</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.7876</v>
+        <v>-0.3075</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0238</v>
+        <v>-0.3075</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.8114</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0238</v>
+        <v>-0.3075</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0193</v>
+        <v>-0.3075</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.8114</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="L54" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.7921</v>
+        <v>-0.3075</v>
       </c>
       <c r="N54" t="n">
-        <v>194</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.8321</v>
+        <v>-0.3635</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.2213</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.7754</v>
+        <v>-0.8021</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.8321</v>
+        <v>-0.3635</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.8321</v>
+        <v>-0.3635</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.8321</v>
+        <v>-0.3635</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.8321</v>
+        <v>-0.3635</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.8321</v>
+        <v>-0.3635</v>
       </c>
       <c r="N55" t="n">
-        <v>135</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.1914</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.3838</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.9186</v>
+        <v>-0.9227</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.1914</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.1914</v>
+        <v>-1.9569</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1.3264</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.1914</v>
+        <v>-1.9569</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.1914</v>
+        <v>-2.1212</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1.3264</v>
       </c>
       <c r="K56" t="n">
-        <v>118</v>
+        <v>198</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.1914</v>
+        <v>-0.7948</v>
       </c>
       <c r="N56" t="n">
-        <v>118</v>
+        <v>409</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.2169</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.7408</v>
+        <v>-0.4943</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.9287</v>
+        <v>-1.0046</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.2169</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.8028</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>1.5859</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-2.8028</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>-2.8502</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>1.5859</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>198</v>
+        <v>118</v>
       </c>
       <c r="L57" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.2643</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>409</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.4677</v>
+        <v>-0.8454</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.8935</v>
+        <v>-0.5147</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.0286</v>
+        <v>-1.0197</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.4677</v>
+        <v>-0.8454</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.4677</v>
+        <v>-0.4569</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>-0.3885</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.4677</v>
+        <v>-0.4569</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.4677</v>
+        <v>-0.4757</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>-0.3885</v>
       </c>
       <c r="K58" t="n">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.4677</v>
+        <v>-0.8642000000000001</v>
       </c>
       <c r="N58" t="n">
-        <v>135</v>
+        <v>312</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.5825</v>
+        <v>-0.8597</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.9634</v>
+        <v>-0.5234</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.0744</v>
+        <v>-1.0261</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.5825</v>
+        <v>-0.8597</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.8446</v>
+        <v>-0.8597</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.7379</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.8446</v>
+        <v>-0.8597</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.8517</v>
+        <v>-0.8597</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.7379</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="L59" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.5896</v>
+        <v>-0.8597</v>
       </c>
       <c r="N59" t="n">
-        <v>312</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60">
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.6818</v>
+        <v>-1.1738</v>
       </c>
       <c r="C60" t="n">
-        <v>-1.0239</v>
+        <v>-0.7146</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.1139</v>
+        <v>-1.1679</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.6818</v>
+        <v>-1.1738</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.6818</v>
+        <v>-1.1738</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.6818</v>
+        <v>-1.1738</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.6818</v>
+        <v>-1.1738</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.6818</v>
+        <v>-1.1738</v>
       </c>
       <c r="N60" t="n">
         <v>118</v>
@@ -3210,31 +3210,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-2.8948</v>
+        <v>-3.5371</v>
       </c>
       <c r="C61" t="n">
-        <v>-1.7623</v>
+        <v>-2.1534</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.5972</v>
+        <v>-2.2348</v>
       </c>
       <c r="E61" t="n">
-        <v>-2.8948</v>
+        <v>-3.5371</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.8073</v>
+        <v>-3.6272</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.08749999999999999</v>
+        <v>0.0901</v>
       </c>
       <c r="H61" t="n">
-        <v>-2.8073</v>
+        <v>-3.6272</v>
       </c>
       <c r="I61" t="n">
-        <v>-2.2754</v>
+        <v>-1.886</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.08749999999999999</v>
+        <v>0.0901</v>
       </c>
       <c r="K61" t="n">
         <v>138</v>
@@ -3243,7 +3243,7 @@
         <v>56</v>
       </c>
       <c r="M61" t="n">
-        <v>-2.3629</v>
+        <v>-1.7959</v>
       </c>
       <c r="N61" t="n">
         <v>194</v>
@@ -3349,10 +3349,10 @@
         <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6845</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>17.1125</v>
+        <v>15.0825</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4741</v>
+        <v>0.4081</v>
       </c>
       <c r="J3" t="n">
-        <v>11.8525</v>
+        <v>10.2025</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3329</v>
+        <v>0.2873</v>
       </c>
       <c r="J4" t="n">
-        <v>8.3225</v>
+        <v>7.1825</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>1.12</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1904</v>
+        <v>0.1861</v>
       </c>
       <c r="J5" t="n">
-        <v>4.76</v>
+        <v>4.6525</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.62</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.4243</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.99</v>
+        <v>-10.6075</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.35</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5916</v>
+        <v>0.5453</v>
       </c>
       <c r="J7" t="n">
-        <v>14.79</v>
+        <v>13.6325</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>1.3</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.4789</v>
       </c>
       <c r="J8" t="n">
-        <v>13.1925</v>
+        <v>11.9725</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2545</v>
+        <v>-0.1536</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.3625</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.74</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4627</v>
+        <v>-0.2954</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.5675</v>
+        <v>-7.385</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.62</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.618</v>
+        <v>-0.4085</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.45</v>
+        <v>-10.2125</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.18</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3883</v>
+        <v>0.4358</v>
       </c>
       <c r="J12" t="n">
-        <v>10.8724</v>
+        <v>12.2024</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>1.16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3586</v>
+        <v>0.3969</v>
       </c>
       <c r="J13" t="n">
-        <v>10.0408</v>
+        <v>11.1132</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1381</v>
+        <v>-0.1032</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.8668</v>
+        <v>-2.8896</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>0.64</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5798</v>
+        <v>-0.3816</v>
       </c>
       <c r="J15" t="n">
-        <v>-16.2344</v>
+        <v>-10.6848</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.63</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5927</v>
+        <v>-0.3909</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.5956</v>
+        <v>-10.9452</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.42</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0662</v>
+        <v>1.0402</v>
       </c>
       <c r="J17" t="n">
-        <v>29.8536</v>
+        <v>29.1256</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8244</v>
+        <v>0.8212</v>
       </c>
       <c r="J18" t="n">
-        <v>23.0832</v>
+        <v>22.9936</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.15</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3886</v>
+        <v>0.4403</v>
       </c>
       <c r="J19" t="n">
-        <v>10.8808</v>
+        <v>12.3284</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0568</v>
+        <v>0.1232</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5904</v>
+        <v>3.4496</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1173</v>
+        <v>-0.0446</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.2844</v>
+        <v>-1.2488</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6821</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>19.0988</v>
+        <v>23.5256</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3616</v>
+        <v>0.4002</v>
       </c>
       <c r="J23" t="n">
-        <v>10.1248</v>
+        <v>11.2056</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>0.76</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4147</v>
+        <v>-0.2661</v>
       </c>
       <c r="J24" t="n">
-        <v>-11.6116</v>
+        <v>-7.4508</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.63</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5911</v>
+        <v>-0.3899</v>
       </c>
       <c r="J25" t="n">
-        <v>-16.5508</v>
+        <v>-10.9172</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.54</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.703</v>
+        <v>-0.4729</v>
       </c>
       <c r="J26" t="n">
-        <v>-19.684</v>
+        <v>-13.2412</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2232</v>
+        <v>1.1418</v>
       </c>
       <c r="J27" t="n">
-        <v>34.2496</v>
+        <v>31.9704</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.27</v>
       </c>
       <c r="I28" t="n">
-        <v>0.721</v>
+        <v>0.7246</v>
       </c>
       <c r="J28" t="n">
-        <v>20.188</v>
+        <v>20.2888</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5917</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>16.5676</v>
+        <v>17.0072</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>1.15</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3792</v>
+        <v>0.4375</v>
       </c>
       <c r="J30" t="n">
-        <v>10.6176</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.85</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6073</v>
+        <v>-0.5427</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.0044</v>
+        <v>-15.1956</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.25</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4605</v>
+        <v>0.5364</v>
       </c>
       <c r="J32" t="n">
-        <v>13.3545</v>
+        <v>15.5556</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.03</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1019</v>
+        <v>0.0956</v>
       </c>
       <c r="J33" t="n">
-        <v>2.9551</v>
+        <v>2.7724</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>0.99</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0216</v>
+        <v>-0.0194</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.6264</v>
+        <v>-0.5626</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.83</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3343</v>
+        <v>-0.2063</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.694699999999999</v>
+        <v>-5.9827</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.8</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3788</v>
+        <v>-0.2367</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.9852</v>
+        <v>-6.8643</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.24</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7477</v>
+        <v>0.7099</v>
       </c>
       <c r="J37" t="n">
-        <v>21.6833</v>
+        <v>20.5871</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.2</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6493</v>
+        <v>0.6082</v>
       </c>
       <c r="J38" t="n">
-        <v>18.8297</v>
+        <v>17.6378</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.21</v>
+        <v>0.1897</v>
       </c>
       <c r="J39" t="n">
-        <v>6.09</v>
+        <v>5.5013</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>0.89</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.441</v>
+        <v>-0.3862</v>
       </c>
       <c r="J40" t="n">
-        <v>-12.789</v>
+        <v>-11.1998</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7521</v>
+        <v>-0.7073</v>
       </c>
       <c r="J41" t="n">
-        <v>-21.8109</v>
+        <v>-20.5117</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.06</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1924</v>
+        <v>0.1866</v>
       </c>
       <c r="J42" t="n">
-        <v>5.3872</v>
+        <v>5.2248</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1733</v>
+        <v>0.1633</v>
       </c>
       <c r="J43" t="n">
-        <v>4.8524</v>
+        <v>4.5724</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>0.95</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0774</v>
+        <v>-0.0679</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.1672</v>
+        <v>-1.9012</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>0.8</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3584</v>
+        <v>-0.2279</v>
       </c>
       <c r="J45" t="n">
-        <v>-10.0352</v>
+        <v>-6.3812</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>0.68</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.528</v>
+        <v>-0.3442</v>
       </c>
       <c r="J46" t="n">
-        <v>-14.784</v>
+        <v>-9.637600000000001</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.31</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8589</v>
+        <v>0.6334</v>
       </c>
       <c r="J47" t="n">
-        <v>24.0492</v>
+        <v>17.7352</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>1.3</v>
       </c>
       <c r="I48" t="n">
-        <v>0.836</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>23.408</v>
+        <v>17.346</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>1.27</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7661</v>
+        <v>0.5775</v>
       </c>
       <c r="J49" t="n">
-        <v>21.4508</v>
+        <v>16.17</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4221</v>
+        <v>-0.3539</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.8188</v>
+        <v>-9.9092</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6604</v>
+        <v>-0.6034</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.4912</v>
+        <v>-16.8952</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.21</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4405</v>
+        <v>0.4343</v>
       </c>
       <c r="J52" t="n">
-        <v>12.334</v>
+        <v>12.1604</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>0.97</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0226</v>
+        <v>-0.0379</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.6328</v>
+        <v>-1.0612</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>0.83</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3012</v>
+        <v>-0.1946</v>
       </c>
       <c r="J54" t="n">
-        <v>-8.4336</v>
+        <v>-5.4488</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.73</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.453</v>
+        <v>-0.2931</v>
       </c>
       <c r="J55" t="n">
-        <v>-12.684</v>
+        <v>-8.206799999999999</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.67</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5353</v>
+        <v>-0.3503</v>
       </c>
       <c r="J56" t="n">
-        <v>-14.9884</v>
+        <v>-9.808400000000001</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.4</v>
       </c>
       <c r="I57" t="n">
-        <v>1.052</v>
+        <v>0.7542</v>
       </c>
       <c r="J57" t="n">
-        <v>29.456</v>
+        <v>21.1176</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6389</v>
+        <v>0.5047</v>
       </c>
       <c r="J58" t="n">
-        <v>17.8892</v>
+        <v>14.1316</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>1.1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2782</v>
+        <v>0.3171</v>
       </c>
       <c r="J59" t="n">
-        <v>7.7896</v>
+        <v>8.8788</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>1.09</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2467</v>
+        <v>0.29</v>
       </c>
       <c r="J60" t="n">
-        <v>6.9076</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6129</v>
+        <v>-0.5523</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.1612</v>
+        <v>-15.4644</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.66</v>
       </c>
       <c r="I62" t="n">
-        <v>1.5388</v>
+        <v>1.0748</v>
       </c>
       <c r="J62" t="n">
-        <v>38.47</v>
+        <v>26.87</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.28</v>
       </c>
       <c r="I63" t="n">
-        <v>0.755</v>
+        <v>0.5804</v>
       </c>
       <c r="J63" t="n">
-        <v>18.875</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>1.05</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1567</v>
       </c>
       <c r="J64" t="n">
-        <v>2.2825</v>
+        <v>3.9175</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.98</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2171</v>
+        <v>-0.1402</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.4275</v>
+        <v>-3.505</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.354</v>
+        <v>-0.2781</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.85</v>
+        <v>-6.9525</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2775</v>
+        <v>0.306</v>
       </c>
       <c r="J67" t="n">
-        <v>6.9375</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>1.01</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0404</v>
+        <v>0.0377</v>
       </c>
       <c r="J68" t="n">
-        <v>1.01</v>
+        <v>0.9425</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>0.96</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1145</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.8625</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.96</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1145</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.8625</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1553</v>
+        <v>-0.0881</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.8825</v>
+        <v>-2.2025</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.52</v>
       </c>
       <c r="I72" t="n">
-        <v>1.269</v>
+        <v>0.8969</v>
       </c>
       <c r="J72" t="n">
-        <v>32.994</v>
+        <v>23.3194</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.24</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.5244</v>
       </c>
       <c r="J73" t="n">
-        <v>16.9962</v>
+        <v>13.6344</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4763</v>
+        <v>0.4404</v>
       </c>
       <c r="J74" t="n">
-        <v>12.3838</v>
+        <v>11.4504</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.118</v>
+        <v>-0.0451</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.068</v>
+        <v>-1.1726</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.99</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1766</v>
+        <v>-0.1</v>
       </c>
       <c r="J76" t="n">
-        <v>-4.5916</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.15</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3587</v>
+        <v>0.3696</v>
       </c>
       <c r="J77" t="n">
-        <v>9.3262</v>
+        <v>9.6096</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>0.91</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1349</v>
+        <v>-0.1101</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.5074</v>
+        <v>-2.8626</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>0.79</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3589</v>
+        <v>-0.2325</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.3314</v>
+        <v>-6.045</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.77</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3896</v>
+        <v>-0.2521</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.1296</v>
+        <v>-6.5546</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.71</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4766</v>
+        <v>-0.3101</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.3916</v>
+        <v>-8.0626</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.46</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1331</v>
+        <v>0.8126</v>
       </c>
       <c r="J82" t="n">
-        <v>30.5937</v>
+        <v>21.9402</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.24</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6317</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>17.0559</v>
+        <v>14.0589</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.14</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3409</v>
+        <v>0.3774</v>
       </c>
       <c r="J84" t="n">
-        <v>9.2043</v>
+        <v>10.1898</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>1.12</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2853</v>
+        <v>0.3453</v>
       </c>
       <c r="J85" t="n">
-        <v>7.7031</v>
+        <v>9.3231</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>1.12</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2853</v>
+        <v>0.3453</v>
       </c>
       <c r="J86" t="n">
-        <v>7.7031</v>
+        <v>9.3231</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5984</v>
+        <v>0.5632</v>
       </c>
       <c r="J87" t="n">
-        <v>16.1568</v>
+        <v>15.2064</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0113</v>
+        <v>-0.0336</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.3051</v>
+        <v>-0.9072</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3549</v>
+        <v>-0.2313</v>
       </c>
       <c r="J89" t="n">
-        <v>-9.5823</v>
+        <v>-6.2451</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.6</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6207</v>
+        <v>-0.4124</v>
       </c>
       <c r="J90" t="n">
-        <v>-16.7589</v>
+        <v>-11.1348</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.6</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6207</v>
+        <v>-0.4124</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.7589</v>
+        <v>-11.1348</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>1.83</v>
       </c>
       <c r="I92" t="n">
-        <v>1.6705</v>
+        <v>1.1859</v>
       </c>
       <c r="J92" t="n">
-        <v>30.069</v>
+        <v>21.3462</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>1.7</v>
       </c>
       <c r="I93" t="n">
-        <v>1.4361</v>
+        <v>1.0406</v>
       </c>
       <c r="J93" t="n">
-        <v>25.8498</v>
+        <v>18.7308</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>1.57</v>
       </c>
       <c r="I94" t="n">
-        <v>1.1578</v>
+        <v>0.8949</v>
       </c>
       <c r="J94" t="n">
-        <v>20.8404</v>
+        <v>16.1082</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>1.55</v>
       </c>
       <c r="I95" t="n">
-        <v>1.1119</v>
+        <v>0.8723</v>
       </c>
       <c r="J95" t="n">
-        <v>20.0142</v>
+        <v>15.7014</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>1.24</v>
       </c>
       <c r="I96" t="n">
-        <v>0.4575</v>
+        <v>0.4796</v>
       </c>
       <c r="J96" t="n">
-        <v>8.234999999999999</v>
+        <v>8.6328</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>0.8</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.1839</v>
+        <v>-0.1699</v>
       </c>
       <c r="J97" t="n">
-        <v>-3.3102</v>
+        <v>-3.0582</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>0.75</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2616</v>
+        <v>-0.2251</v>
       </c>
       <c r="J98" t="n">
-        <v>-4.7088</v>
+        <v>-4.0518</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>0.61</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4857</v>
+        <v>-0.3647</v>
       </c>
       <c r="J99" t="n">
-        <v>-8.742599999999999</v>
+        <v>-6.5646</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>0.47</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.7192</v>
+        <v>-0.4925</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.9456</v>
+        <v>-8.865</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>0.35</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8777</v>
+        <v>-0.6072</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.7986</v>
+        <v>-10.9296</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.63</v>
       </c>
       <c r="I102" t="n">
-        <v>1.4858</v>
+        <v>1.0391</v>
       </c>
       <c r="J102" t="n">
-        <v>44.574</v>
+        <v>31.173</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>1.3</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8057</v>
+        <v>0.6088</v>
       </c>
       <c r="J103" t="n">
-        <v>24.171</v>
+        <v>18.264</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>1.27</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7345</v>
+        <v>0.5676</v>
       </c>
       <c r="J104" t="n">
-        <v>22.035</v>
+        <v>17.028</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.88</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5232</v>
+        <v>-0.4545</v>
       </c>
       <c r="J105" t="n">
-        <v>-15.696</v>
+        <v>-13.635</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.8</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7239</v>
+        <v>-0.6693</v>
       </c>
       <c r="J106" t="n">
-        <v>-21.717</v>
+        <v>-20.079</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>1.2</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3956</v>
+        <v>0.4025</v>
       </c>
       <c r="J107" t="n">
-        <v>11.868</v>
+        <v>12.075</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0589</v>
+        <v>0.0435</v>
       </c>
       <c r="J108" t="n">
-        <v>1.767</v>
+        <v>1.305</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>0.99</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0131</v>
+        <v>-0.0182</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.393</v>
+        <v>-0.546</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>0.83</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3304</v>
+        <v>-0.2046</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.912000000000001</v>
+        <v>-6.138</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.8</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3753</v>
+        <v>-0.235</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.259</v>
+        <v>-7.05</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.33</v>
       </c>
       <c r="I112" t="n">
-        <v>0.536</v>
+        <v>0.4274</v>
       </c>
       <c r="J112" t="n">
-        <v>18.224</v>
+        <v>14.5316</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.13</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2506</v>
+        <v>0.2218</v>
       </c>
       <c r="J113" t="n">
-        <v>8.5204</v>
+        <v>7.5412</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.04</v>
       </c>
       <c r="I114" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0815</v>
       </c>
       <c r="J114" t="n">
-        <v>2.363</v>
+        <v>2.771</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1777</v>
+        <v>-0.0955</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.0418</v>
+        <v>-3.247</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2306</v>
+        <v>-0.1307</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.8404</v>
+        <v>-4.4438</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4518</v>
+        <v>0.3603</v>
       </c>
       <c r="J117" t="n">
-        <v>15.3612</v>
+        <v>12.2502</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2764</v>
+        <v>0.2236</v>
       </c>
       <c r="J118" t="n">
-        <v>9.397600000000001</v>
+        <v>7.6024</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>1.06</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1328</v>
+        <v>0.1094</v>
       </c>
       <c r="J119" t="n">
-        <v>4.5152</v>
+        <v>3.7196</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1106</v>
+        <v>-0.0545</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.7604</v>
+        <v>-1.853</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.8</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3936</v>
+        <v>-0.2442</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.3824</v>
+        <v>-8.3028</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.79</v>
       </c>
       <c r="I122" t="n">
-        <v>1.6927</v>
+        <v>1.1868</v>
       </c>
       <c r="J122" t="n">
-        <v>37.2394</v>
+        <v>26.1096</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.53</v>
       </c>
       <c r="I123" t="n">
-        <v>1.2129</v>
+        <v>0.8754</v>
       </c>
       <c r="J123" t="n">
-        <v>26.6838</v>
+        <v>19.2588</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.4</v>
       </c>
       <c r="I124" t="n">
-        <v>0.9377</v>
+        <v>0.7146</v>
       </c>
       <c r="J124" t="n">
-        <v>20.6294</v>
+        <v>15.7212</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>1.15</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3122</v>
+        <v>0.3759</v>
       </c>
       <c r="J125" t="n">
-        <v>6.8684</v>
+        <v>8.2698</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.85</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6412</v>
+        <v>-0.5755</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.1064</v>
+        <v>-12.661</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.0336</v>
+        <v>-0.0559</v>
       </c>
       <c r="J127" t="n">
-        <v>-0.7392</v>
+        <v>-1.2298</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>0.86</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.175</v>
+        <v>-0.15</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.85</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1919</v>
+        <v>-0.1608</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.2218</v>
+        <v>-3.5376</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3574</v>
+        <v>-0.2497</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.8628</v>
+        <v>-5.4934</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.43</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8137</v>
+        <v>-0.5576</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.9014</v>
+        <v>-12.2672</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.14</v>
       </c>
       <c r="I132" t="n">
-        <v>0.49</v>
+        <v>0.4493</v>
       </c>
       <c r="J132" t="n">
-        <v>14.7</v>
+        <v>13.479</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.14</v>
       </c>
       <c r="I133" t="n">
-        <v>0.49</v>
+        <v>0.4493</v>
       </c>
       <c r="J133" t="n">
-        <v>14.7</v>
+        <v>13.479</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>1.06</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2444</v>
+        <v>0.2205</v>
       </c>
       <c r="J134" t="n">
-        <v>7.332</v>
+        <v>6.615</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>1.01</v>
       </c>
       <c r="I135" t="n">
-        <v>0.026</v>
+        <v>0.0481</v>
       </c>
       <c r="J135" t="n">
-        <v>0.78</v>
+        <v>1.443</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6549</v>
+        <v>-0.6046</v>
       </c>
       <c r="J136" t="n">
-        <v>-19.647</v>
+        <v>-18.138</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.23</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3989</v>
+        <v>0.4695</v>
       </c>
       <c r="J137" t="n">
-        <v>11.967</v>
+        <v>14.085</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3557</v>
+        <v>0.4164</v>
       </c>
       <c r="J138" t="n">
-        <v>10.671</v>
+        <v>12.492</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1275</v>
+        <v>0.171</v>
       </c>
       <c r="J139" t="n">
-        <v>3.825</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.95</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1617</v>
+        <v>-0.0842</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.851</v>
+        <v>-2.526</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.95</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1617</v>
+        <v>-0.0842</v>
       </c>
       <c r="J141" t="n">
-        <v>-4.851</v>
+        <v>-2.526</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.02</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1269</v>
+        <v>0.1008</v>
       </c>
       <c r="J142" t="n">
-        <v>2.7918</v>
+        <v>2.2176</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.01</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1018</v>
+        <v>0.0709</v>
       </c>
       <c r="J143" t="n">
-        <v>2.2396</v>
+        <v>1.5598</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>0.92</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.116</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.552</v>
+        <v>-2.1692</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>0.86</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2381</v>
+        <v>-0.1628</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.2382</v>
+        <v>-3.5816</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>0.52</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7219</v>
+        <v>-0.4874</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.8818</v>
+        <v>-10.7228</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>1.54</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2375</v>
+        <v>1.1632</v>
       </c>
       <c r="J147" t="n">
-        <v>27.225</v>
+        <v>25.5904</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>1.47</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0951</v>
+        <v>1.0769</v>
       </c>
       <c r="J148" t="n">
-        <v>24.0922</v>
+        <v>23.6918</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>1.32</v>
       </c>
       <c r="I149" t="n">
-        <v>0.7362</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="J149" t="n">
-        <v>16.1964</v>
+        <v>17.864</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>1.25</v>
       </c>
       <c r="I150" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.6543</v>
       </c>
       <c r="J150" t="n">
-        <v>12.386</v>
+        <v>14.3946</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>1.09</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1553</v>
+        <v>0.2426</v>
       </c>
       <c r="J151" t="n">
-        <v>3.4166</v>
+        <v>5.3372</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.1</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3347</v>
+        <v>0.362</v>
       </c>
       <c r="J152" t="n">
-        <v>8.0328</v>
+        <v>8.688000000000001</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>0.72</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.4059</v>
+        <v>-0.2829</v>
       </c>
       <c r="J153" t="n">
-        <v>-9.7416</v>
+        <v>-6.7896</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.71</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4236</v>
+        <v>-0.292</v>
       </c>
       <c r="J154" t="n">
-        <v>-10.1664</v>
+        <v>-7.008</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.7</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4403</v>
+        <v>-0.3013</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.5672</v>
+        <v>-7.2312</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.44</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7954</v>
+        <v>-0.5438</v>
       </c>
       <c r="J156" t="n">
-        <v>-19.0896</v>
+        <v>-13.0512</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.72</v>
       </c>
       <c r="I157" t="n">
-        <v>1.579</v>
+        <v>1.3807</v>
       </c>
       <c r="J157" t="n">
-        <v>37.896</v>
+        <v>33.1368</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.61</v>
       </c>
       <c r="I158" t="n">
-        <v>1.3746</v>
+        <v>1.2488</v>
       </c>
       <c r="J158" t="n">
-        <v>32.9904</v>
+        <v>29.9712</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.38</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8991</v>
+        <v>0.9379</v>
       </c>
       <c r="J159" t="n">
-        <v>21.5784</v>
+        <v>22.5096</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.08</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1275</v>
+        <v>0.2137</v>
       </c>
       <c r="J160" t="n">
-        <v>3.06</v>
+        <v>5.1288</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5887</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.1288</v>
+        <v>-12.4464</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.28</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5112</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="J162" t="n">
-        <v>14.3136</v>
+        <v>16.8644</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.25</v>
       </c>
       <c r="I163" t="n">
-        <v>0.471</v>
+        <v>0.5482</v>
       </c>
       <c r="J163" t="n">
-        <v>13.188</v>
+        <v>15.3496</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>0.78</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4001</v>
+        <v>-0.2529</v>
       </c>
       <c r="J164" t="n">
-        <v>-11.2028</v>
+        <v>-7.0812</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>0.74</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4565</v>
+        <v>-0.2921</v>
       </c>
       <c r="J165" t="n">
-        <v>-12.782</v>
+        <v>-8.178800000000001</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5105</v>
+        <v>-0.3304</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.294</v>
+        <v>-9.251200000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.42</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0827</v>
+        <v>1.0485</v>
       </c>
       <c r="J167" t="n">
-        <v>30.3156</v>
+        <v>29.358</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1.27</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7487</v>
+        <v>0.7375</v>
       </c>
       <c r="J168" t="n">
-        <v>20.9636</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>1.21</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5989</v>
+        <v>0.5933</v>
       </c>
       <c r="J169" t="n">
-        <v>16.7692</v>
+        <v>16.6124</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.97</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2433</v>
+        <v>-0.1697</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.8124</v>
+        <v>-4.7516</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.89</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4887</v>
+        <v>-0.42</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.6836</v>
+        <v>-11.76</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.14</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3117</v>
+        <v>0.3411</v>
       </c>
       <c r="J172" t="n">
-        <v>8.727600000000001</v>
+        <v>9.550800000000001</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.08</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2124</v>
+        <v>0.218</v>
       </c>
       <c r="J173" t="n">
-        <v>5.9472</v>
+        <v>6.104</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0309</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="J174" t="n">
-        <v>0.8652</v>
+        <v>0.2296</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>0.87</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2616</v>
+        <v>-0.1611</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.3248</v>
+        <v>-4.5108</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>0.66</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5627</v>
+        <v>-0.3682</v>
       </c>
       <c r="J176" t="n">
-        <v>-15.7556</v>
+        <v>-10.3096</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.46</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1411</v>
+        <v>1.09</v>
       </c>
       <c r="J177" t="n">
-        <v>31.9508</v>
+        <v>30.52</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.2</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5269</v>
+        <v>0.5602</v>
       </c>
       <c r="J178" t="n">
-        <v>14.7532</v>
+        <v>15.6856</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.19</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4924</v>
+        <v>0.5366</v>
       </c>
       <c r="J179" t="n">
-        <v>13.7872</v>
+        <v>15.0248</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>1.16</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4059</v>
+        <v>0.4626</v>
       </c>
       <c r="J180" t="n">
-        <v>11.3652</v>
+        <v>12.9528</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1818</v>
+        <v>-0.1036</v>
       </c>
       <c r="J181" t="n">
-        <v>-5.0904</v>
+        <v>-2.9008</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.24</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4297</v>
+        <v>0.5014</v>
       </c>
       <c r="J182" t="n">
-        <v>12.891</v>
+        <v>15.042</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>1.04</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0983</v>
+        <v>0.1112</v>
       </c>
       <c r="J183" t="n">
-        <v>2.949</v>
+        <v>3.336</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>1.04</v>
       </c>
       <c r="I184" t="n">
-        <v>0.0983</v>
+        <v>0.1112</v>
       </c>
       <c r="J184" t="n">
-        <v>2.949</v>
+        <v>3.336</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1658</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.974</v>
+        <v>-2.739</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.89</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2534</v>
+        <v>-0.1486</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.602</v>
+        <v>-4.458</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.18</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5684</v>
+        <v>0.5393</v>
       </c>
       <c r="J187" t="n">
-        <v>17.052</v>
+        <v>16.179</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.15</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4873</v>
+        <v>0.4614</v>
       </c>
       <c r="J188" t="n">
-        <v>14.619</v>
+        <v>13.842</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4591</v>
+        <v>0.435</v>
       </c>
       <c r="J189" t="n">
-        <v>13.773</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>1.05</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1513</v>
+        <v>0.1815</v>
       </c>
       <c r="J190" t="n">
-        <v>4.539</v>
+        <v>5.445</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.87</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5168</v>
+        <v>-0.4562</v>
       </c>
       <c r="J191" t="n">
-        <v>-15.504</v>
+        <v>-13.686</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.63</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8875</v>
+        <v>1.0761</v>
       </c>
       <c r="J192" t="n">
-        <v>24.85</v>
+        <v>30.1308</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>1.22</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3902</v>
+        <v>0.456</v>
       </c>
       <c r="J193" t="n">
-        <v>10.9256</v>
+        <v>12.768</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>0.92</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2119</v>
+        <v>-0.1186</v>
       </c>
       <c r="J194" t="n">
-        <v>-5.9332</v>
+        <v>-3.3208</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.79</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4112</v>
+        <v>-0.2562</v>
       </c>
       <c r="J195" t="n">
-        <v>-11.5136</v>
+        <v>-7.1736</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.76</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4522</v>
+        <v>-0.2857</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.6616</v>
+        <v>-7.9996</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.42</v>
       </c>
       <c r="I197" t="n">
-        <v>1.1154</v>
+        <v>1.0658</v>
       </c>
       <c r="J197" t="n">
-        <v>31.2312</v>
+        <v>29.8424</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.38</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0308</v>
+        <v>1.0049</v>
       </c>
       <c r="J198" t="n">
-        <v>28.8624</v>
+        <v>28.1372</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.07</v>
       </c>
       <c r="I199" t="n">
-        <v>0.212</v>
+        <v>0.2402</v>
       </c>
       <c r="J199" t="n">
-        <v>5.936</v>
+        <v>6.7256</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>0.84</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5998</v>
+        <v>-0.5415</v>
       </c>
       <c r="J200" t="n">
-        <v>-16.7944</v>
+        <v>-15.162</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>0.74</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.8408</v>
+        <v>-0.7996</v>
       </c>
       <c r="J201" t="n">
-        <v>-23.5424</v>
+        <v>-22.3888</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>1.09</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3438</v>
+        <v>0.3793</v>
       </c>
       <c r="J202" t="n">
-        <v>6.876</v>
+        <v>7.586</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>0.62</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.538</v>
+        <v>-0.3673</v>
       </c>
       <c r="J203" t="n">
-        <v>-10.76</v>
+        <v>-7.346</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>0.58</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.5969</v>
+        <v>-0.4046</v>
       </c>
       <c r="J204" t="n">
-        <v>-11.938</v>
+        <v>-8.092000000000001</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.6252</v>
+        <v>-0.4232</v>
       </c>
       <c r="J205" t="n">
-        <v>-12.504</v>
+        <v>-8.464</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.55</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.639</v>
+        <v>-0.4326</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.78</v>
+        <v>-8.651999999999999</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>2.12</v>
       </c>
       <c r="I207" t="n">
-        <v>2.0593</v>
+        <v>1.8041</v>
       </c>
       <c r="J207" t="n">
-        <v>41.186</v>
+        <v>36.082</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>1.71</v>
       </c>
       <c r="I208" t="n">
-        <v>1.5031</v>
+        <v>1.342</v>
       </c>
       <c r="J208" t="n">
-        <v>30.062</v>
+        <v>26.84</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>1.57</v>
       </c>
       <c r="I209" t="n">
-        <v>1.2345</v>
+        <v>1.1789</v>
       </c>
       <c r="J209" t="n">
-        <v>24.69</v>
+        <v>23.578</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2533</v>
+        <v>-0.1631</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.066</v>
+        <v>-3.262</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4251</v>
+        <v>-0.3413</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.502000000000001</v>
+        <v>-6.826</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.95</v>
       </c>
       <c r="I212" t="n">
-        <v>1.8958</v>
+        <v>1.6037</v>
       </c>
       <c r="J212" t="n">
-        <v>39.8118</v>
+        <v>33.6777</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.68</v>
       </c>
       <c r="I213" t="n">
-        <v>1.4249</v>
+        <v>1.2994</v>
       </c>
       <c r="J213" t="n">
-        <v>29.9229</v>
+        <v>27.2874</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>1.38</v>
       </c>
       <c r="I214" t="n">
-        <v>0.7784</v>
+        <v>0.9093</v>
       </c>
       <c r="J214" t="n">
-        <v>16.3464</v>
+        <v>19.0953</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>1.36</v>
       </c>
       <c r="I215" t="n">
-        <v>0.7357</v>
+        <v>0.8663</v>
       </c>
       <c r="J215" t="n">
-        <v>15.4497</v>
+        <v>18.1923</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>1.22</v>
       </c>
       <c r="I216" t="n">
-        <v>0.4277</v>
+        <v>0.5447</v>
       </c>
       <c r="J216" t="n">
-        <v>8.9817</v>
+        <v>11.4387</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>0.73</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.2749</v>
+        <v>-0.2364</v>
       </c>
       <c r="J217" t="n">
-        <v>-5.7729</v>
+        <v>-4.9644</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>0.55</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.5806</v>
+        <v>-0.4125</v>
       </c>
       <c r="J218" t="n">
-        <v>-12.1926</v>
+        <v>-8.6625</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>0.55</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.5806</v>
+        <v>-0.4125</v>
       </c>
       <c r="J219" t="n">
-        <v>-12.1926</v>
+        <v>-8.6625</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>0.52</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.6313</v>
+        <v>-0.4397</v>
       </c>
       <c r="J220" t="n">
-        <v>-13.2573</v>
+        <v>-9.233700000000001</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.48</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6922</v>
+        <v>-0.477</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.5362</v>
+        <v>-10.017</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.3</v>
       </c>
       <c r="I222" t="n">
-        <v>0.78</v>
+        <v>0.7882</v>
       </c>
       <c r="J222" t="n">
-        <v>22.62</v>
+        <v>22.8578</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.25</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6554</v>
+        <v>0.6733</v>
       </c>
       <c r="J223" t="n">
-        <v>19.0066</v>
+        <v>19.5257</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.23</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6</v>
+        <v>0.6271</v>
       </c>
       <c r="J224" t="n">
-        <v>17.4</v>
+        <v>18.1859</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.17</v>
       </c>
       <c r="I225" t="n">
-        <v>0.4207</v>
+        <v>0.4838</v>
       </c>
       <c r="J225" t="n">
-        <v>12.2003</v>
+        <v>14.0302</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>1.15</v>
       </c>
       <c r="I226" t="n">
-        <v>0.3661</v>
+        <v>0.4328</v>
       </c>
       <c r="J226" t="n">
-        <v>10.6169</v>
+        <v>12.5512</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.14</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3425</v>
+        <v>0.3732</v>
       </c>
       <c r="J227" t="n">
-        <v>9.932499999999999</v>
+        <v>10.8228</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>0.89</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.174</v>
+        <v>-0.1323</v>
       </c>
       <c r="J228" t="n">
-        <v>-5.046</v>
+        <v>-3.8367</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>0.85</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2592</v>
+        <v>-0.1729</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.5168</v>
+        <v>-5.0141</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.82</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3116</v>
+        <v>-0.203</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.0364</v>
+        <v>-5.887</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.64</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5716</v>
+        <v>-0.3767</v>
       </c>
       <c r="J231" t="n">
-        <v>-16.5764</v>
+        <v>-10.9243</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.91</v>
       </c>
       <c r="I232" t="n">
-        <v>1.9249</v>
+        <v>1.623</v>
       </c>
       <c r="J232" t="n">
-        <v>44.2727</v>
+        <v>37.329</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>1.47</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1269</v>
+        <v>1.088</v>
       </c>
       <c r="J233" t="n">
-        <v>25.9187</v>
+        <v>25.024</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>1.15</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3414</v>
+        <v>0.4217</v>
       </c>
       <c r="J234" t="n">
-        <v>7.8522</v>
+        <v>9.6991</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.97</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2831</v>
+        <v>-0.1991</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.5113</v>
+        <v>-4.5793</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6253</v>
+        <v>-0.5596</v>
       </c>
       <c r="J236" t="n">
-        <v>-14.3819</v>
+        <v>-12.8708</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.06</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2251</v>
+        <v>0.2184</v>
       </c>
       <c r="J237" t="n">
-        <v>5.1773</v>
+        <v>5.0232</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.01</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1184</v>
+        <v>0.0859</v>
       </c>
       <c r="J238" t="n">
-        <v>2.7232</v>
+        <v>1.9757</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>0.82</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2869</v>
+        <v>-0.1986</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.5987</v>
+        <v>-4.5678</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4927</v>
+        <v>-0.3237</v>
       </c>
       <c r="J240" t="n">
-        <v>-11.3321</v>
+        <v>-7.4451</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.55</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6777</v>
+        <v>-0.4548</v>
       </c>
       <c r="J241" t="n">
-        <v>-15.5871</v>
+        <v>-10.4604</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.17</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3224</v>
+        <v>0.3697</v>
       </c>
       <c r="J242" t="n">
-        <v>11.6064</v>
+        <v>13.3092</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>1.15</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2915</v>
+        <v>0.3325</v>
       </c>
       <c r="J243" t="n">
-        <v>10.494</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>1.15</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2915</v>
+        <v>0.3325</v>
       </c>
       <c r="J244" t="n">
-        <v>10.494</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>1.04</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0814</v>
+        <v>0.1095</v>
       </c>
       <c r="J245" t="n">
-        <v>2.9304</v>
+        <v>3.942</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.73</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4894</v>
+        <v>-0.3129</v>
       </c>
       <c r="J246" t="n">
-        <v>-17.6184</v>
+        <v>-11.2644</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.3</v>
       </c>
       <c r="I247" t="n">
-        <v>0.8606</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="J247" t="n">
-        <v>30.9816</v>
+        <v>30.1032</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.27</v>
       </c>
       <c r="I248" t="n">
-        <v>0.7912</v>
+        <v>0.7637</v>
       </c>
       <c r="J248" t="n">
-        <v>28.4832</v>
+        <v>27.4932</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.06</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1875</v>
+        <v>0.2126</v>
       </c>
       <c r="J249" t="n">
-        <v>6.75</v>
+        <v>7.6536</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>0.95</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2803</v>
+        <v>-0.2182</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.0908</v>
+        <v>-7.8552</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6711</v>
+        <v>-0.6177</v>
       </c>
       <c r="J251" t="n">
-        <v>-24.1596</v>
+        <v>-22.2372</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.49</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2324</v>
+        <v>1.1443</v>
       </c>
       <c r="J252" t="n">
-        <v>34.5072</v>
+        <v>32.0404</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.38</v>
       </c>
       <c r="I253" t="n">
-        <v>1.004</v>
+        <v>0.9879</v>
       </c>
       <c r="J253" t="n">
-        <v>28.112</v>
+        <v>27.6612</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>1.37</v>
       </c>
       <c r="I254" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9689</v>
       </c>
       <c r="J254" t="n">
-        <v>27.5072</v>
+        <v>27.1292</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>0.83</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.641</v>
+        <v>-0.5816</v>
       </c>
       <c r="J255" t="n">
-        <v>-17.948</v>
+        <v>-16.2848</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.63</v>
       </c>
       <c r="I256" t="n">
-        <v>-1.0918</v>
+        <v>-1.0786</v>
       </c>
       <c r="J256" t="n">
-        <v>-30.5704</v>
+        <v>-30.2008</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.14</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3198</v>
+        <v>0.3488</v>
       </c>
       <c r="J257" t="n">
-        <v>8.9544</v>
+        <v>9.766400000000001</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>1.09</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2383</v>
+        <v>0.2462</v>
       </c>
       <c r="J258" t="n">
-        <v>6.6724</v>
+        <v>6.8936</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>0.91</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1801</v>
+        <v>-0.1156</v>
       </c>
       <c r="J259" t="n">
-        <v>-5.0428</v>
+        <v>-3.2368</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>0.82</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3342</v>
+        <v>-0.2102</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.3576</v>
+        <v>-5.8856</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.68</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5323</v>
+        <v>-0.3467</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.9044</v>
+        <v>-9.707599999999999</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.54</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3449</v>
+        <v>1.2174</v>
       </c>
       <c r="J262" t="n">
-        <v>33.6225</v>
+        <v>30.435</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.27</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7706</v>
+        <v>0.7501</v>
       </c>
       <c r="J263" t="n">
-        <v>19.265</v>
+        <v>18.7525</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>0.99</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1463</v>
+        <v>-0.0814</v>
       </c>
       <c r="J264" t="n">
-        <v>-3.6575</v>
+        <v>-2.035</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>0.92</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3899</v>
+        <v>-0.3219</v>
       </c>
       <c r="J265" t="n">
-        <v>-9.7475</v>
+        <v>-8.047499999999999</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>0.85</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.521</v>
       </c>
       <c r="J266" t="n">
-        <v>-14.555</v>
+        <v>-13.025</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.25</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4796</v>
+        <v>0.5585</v>
       </c>
       <c r="J267" t="n">
-        <v>11.99</v>
+        <v>13.9625</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>1.11</v>
       </c>
       <c r="I268" t="n">
-        <v>0.2727</v>
+        <v>0.2888</v>
       </c>
       <c r="J268" t="n">
-        <v>6.8175</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.97</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0429</v>
+        <v>-0.0439</v>
       </c>
       <c r="J269" t="n">
-        <v>-1.0725</v>
+        <v>-1.0975</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5187</v>
+        <v>-0.337</v>
       </c>
       <c r="J270" t="n">
-        <v>-12.9675</v>
+        <v>-8.425000000000001</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.61</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6217</v>
+        <v>-0.4119</v>
       </c>
       <c r="J271" t="n">
-        <v>-15.5425</v>
+        <v>-10.2975</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.34</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9035</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="J272" t="n">
-        <v>22.5875</v>
+        <v>22.4175</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.24</v>
       </c>
       <c r="I273" t="n">
-        <v>0.668</v>
+        <v>0.6626</v>
       </c>
       <c r="J273" t="n">
-        <v>16.7</v>
+        <v>16.565</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>1.22</v>
       </c>
       <c r="I274" t="n">
-        <v>0.6169</v>
+        <v>0.6146</v>
       </c>
       <c r="J274" t="n">
-        <v>15.4225</v>
+        <v>15.365</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>1.18</v>
       </c>
       <c r="I275" t="n">
-        <v>0.5068</v>
+        <v>0.5174</v>
       </c>
       <c r="J275" t="n">
-        <v>12.67</v>
+        <v>12.935</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.84</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.623</v>
+        <v>-0.5611</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.575</v>
+        <v>-14.0275</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.11</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3059</v>
+        <v>0.3237</v>
       </c>
       <c r="J277" t="n">
-        <v>7.6475</v>
+        <v>8.092499999999999</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>0.93</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0848</v>
+        <v>-0.0828</v>
       </c>
       <c r="J278" t="n">
-        <v>-2.12</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>0.92</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1035</v>
+        <v>-0.0948</v>
       </c>
       <c r="J279" t="n">
-        <v>-2.5875</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>0.63</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5782</v>
+        <v>-0.3823</v>
       </c>
       <c r="J280" t="n">
-        <v>-14.455</v>
+        <v>-9.557499999999999</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.61</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.401</v>
       </c>
       <c r="J281" t="n">
-        <v>-15.1075</v>
+        <v>-10.025</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.2</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3767</v>
+        <v>0.4325</v>
       </c>
       <c r="J282" t="n">
-        <v>9.040800000000001</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.07</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1657</v>
+        <v>0.1794</v>
       </c>
       <c r="J283" t="n">
-        <v>3.9768</v>
+        <v>4.3056</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>1.04</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1043</v>
+        <v>0.1126</v>
       </c>
       <c r="J284" t="n">
-        <v>2.5032</v>
+        <v>2.7024</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.92</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1993</v>
+        <v>-0.1138</v>
       </c>
       <c r="J285" t="n">
-        <v>-4.7832</v>
+        <v>-2.7312</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.87</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.283</v>
+        <v>-0.1691</v>
       </c>
       <c r="J286" t="n">
-        <v>-6.792</v>
+        <v>-4.0584</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.25</v>
       </c>
       <c r="I287" t="n">
-        <v>0.7368</v>
+        <v>0.7103</v>
       </c>
       <c r="J287" t="n">
-        <v>17.6832</v>
+        <v>17.0472</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.14</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4505</v>
+        <v>0.4318</v>
       </c>
       <c r="J288" t="n">
-        <v>10.812</v>
+        <v>10.3632</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>1.09</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2872</v>
+        <v>0.2971</v>
       </c>
       <c r="J289" t="n">
-        <v>6.8928</v>
+        <v>7.1304</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>1.03</v>
       </c>
       <c r="I290" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.1119</v>
       </c>
       <c r="J290" t="n">
-        <v>1.656</v>
+        <v>2.6856</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3185</v>
+        <v>-0.2537</v>
       </c>
       <c r="J291" t="n">
-        <v>-7.644</v>
+        <v>-6.0888</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.43</v>
       </c>
       <c r="I292" t="n">
-        <v>0.7496</v>
+        <v>0.944</v>
       </c>
       <c r="J292" t="n">
-        <v>4.4976</v>
+        <v>5.664</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.04</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1889</v>
+        <v>0.1722</v>
       </c>
       <c r="J293" t="n">
-        <v>1.1334</v>
+        <v>1.0332</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>0.59</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.6256</v>
+        <v>-0.4169</v>
       </c>
       <c r="J294" t="n">
-        <v>-3.7536</v>
+        <v>-2.5014</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.57</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.6512</v>
+        <v>-0.4355</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.9072</v>
+        <v>-2.613</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.47</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.7745</v>
+        <v>-0.5275</v>
       </c>
       <c r="J296" t="n">
-        <v>-4.647</v>
+        <v>-3.165</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.83</v>
       </c>
       <c r="I297" t="n">
-        <v>1.7605</v>
+        <v>1.5023</v>
       </c>
       <c r="J297" t="n">
-        <v>10.563</v>
+        <v>9.0138</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.61</v>
       </c>
       <c r="I298" t="n">
-        <v>1.3601</v>
+        <v>1.2425</v>
       </c>
       <c r="J298" t="n">
-        <v>8.160600000000001</v>
+        <v>7.455</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>1.45</v>
       </c>
       <c r="I299" t="n">
-        <v>1.0371</v>
+        <v>1.0471</v>
       </c>
       <c r="J299" t="n">
-        <v>6.2226</v>
+        <v>6.2826</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>1.29</v>
       </c>
       <c r="I300" t="n">
-        <v>0.6438</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="J300" t="n">
-        <v>3.8628</v>
+        <v>4.4424</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.64</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.1073</v>
+        <v>-1.0981</v>
       </c>
       <c r="J301" t="n">
-        <v>-6.6438</v>
+        <v>-6.5886</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.71</v>
       </c>
       <c r="I302" t="n">
-        <v>1.5989</v>
+        <v>1.3905</v>
       </c>
       <c r="J302" t="n">
-        <v>27.1813</v>
+        <v>23.6385</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.4</v>
       </c>
       <c r="I303" t="n">
-        <v>0.9906</v>
+        <v>0.9932</v>
       </c>
       <c r="J303" t="n">
-        <v>16.8402</v>
+        <v>16.8844</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>1.38</v>
       </c>
       <c r="I304" t="n">
-        <v>0.947</v>
+        <v>0.9564</v>
       </c>
       <c r="J304" t="n">
-        <v>16.099</v>
+        <v>16.2588</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.88</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.5432</v>
+        <v>-0.4721</v>
       </c>
       <c r="J305" t="n">
-        <v>-9.234400000000001</v>
+        <v>-8.025700000000001</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.87</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5693</v>
+        <v>-0.4999</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.678100000000001</v>
+        <v>-8.4983</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.09</v>
       </c>
       <c r="I307" t="n">
-        <v>0.246</v>
+        <v>0.253</v>
       </c>
       <c r="J307" t="n">
-        <v>4.182</v>
+        <v>4.301</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>1.08</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2286</v>
+        <v>0.2314</v>
       </c>
       <c r="J308" t="n">
-        <v>3.8862</v>
+        <v>3.9338</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>0.99</v>
       </c>
       <c r="I309" t="n">
-        <v>0.0145</v>
+        <v>-0.0112</v>
       </c>
       <c r="J309" t="n">
-        <v>0.2465</v>
+        <v>-0.1904</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>0.82</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3275</v>
+        <v>-0.2078</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.5675</v>
+        <v>-3.5326</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6803</v>
+        <v>-0.4557</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.5651</v>
+        <v>-7.7469</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.03</v>
       </c>
       <c r="I312" t="n">
-        <v>0.2302</v>
+        <v>0.1614</v>
       </c>
       <c r="J312" t="n">
-        <v>6.906</v>
+        <v>4.842</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>0.95</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1347</v>
+        <v>-0.1764</v>
       </c>
       <c r="J313" t="n">
-        <v>-4.041</v>
+        <v>-5.292</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.1707</v>
+        <v>-0.2083</v>
       </c>
       <c r="J314" t="n">
-        <v>-5.121</v>
+        <v>-6.249</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.86</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.4558</v>
+        <v>-0.4337</v>
       </c>
       <c r="J315" t="n">
-        <v>-13.674</v>
+        <v>-13.011</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.76</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.7265</v>
+        <v>-0.6947</v>
       </c>
       <c r="J316" t="n">
-        <v>-21.795</v>
+        <v>-20.841</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.49</v>
       </c>
       <c r="I317" t="n">
-        <v>0.713</v>
+        <v>0.8848</v>
       </c>
       <c r="J317" t="n">
-        <v>21.39</v>
+        <v>26.544</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.27</v>
       </c>
       <c r="I318" t="n">
-        <v>0.4396</v>
+        <v>0.5273</v>
       </c>
       <c r="J318" t="n">
-        <v>13.188</v>
+        <v>15.819</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>1.11</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1813</v>
+        <v>0.2447</v>
       </c>
       <c r="J319" t="n">
-        <v>5.439</v>
+        <v>7.341</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>1.02</v>
       </c>
       <c r="I320" t="n">
-        <v>0.0062</v>
+        <v>0.047</v>
       </c>
       <c r="J320" t="n">
-        <v>0.186</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.73</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5014</v>
+        <v>-0.3206</v>
       </c>
       <c r="J321" t="n">
-        <v>-15.042</v>
+        <v>-9.618</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.27</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4613</v>
+        <v>0.5453</v>
       </c>
       <c r="J322" t="n">
-        <v>13.3777</v>
+        <v>15.8137</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.1</v>
       </c>
       <c r="I323" t="n">
-        <v>0.2041</v>
+        <v>0.234</v>
       </c>
       <c r="J323" t="n">
-        <v>5.9189</v>
+        <v>6.786</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.08</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1668</v>
+        <v>0.1937</v>
       </c>
       <c r="J324" t="n">
-        <v>4.8372</v>
+        <v>5.6173</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>1.02</v>
       </c>
       <c r="I325" t="n">
-        <v>0.0291</v>
+        <v>0.0585</v>
       </c>
       <c r="J325" t="n">
-        <v>0.8439</v>
+        <v>1.6965</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.82</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.3674</v>
+        <v>-0.2254</v>
       </c>
       <c r="J326" t="n">
-        <v>-10.6546</v>
+        <v>-6.5366</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.32</v>
       </c>
       <c r="I327" t="n">
-        <v>0.9103</v>
+        <v>0.8875</v>
       </c>
       <c r="J327" t="n">
-        <v>26.3987</v>
+        <v>25.7375</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>1.21</v>
       </c>
       <c r="I328" t="n">
-        <v>0.6504</v>
+        <v>0.6183</v>
       </c>
       <c r="J328" t="n">
-        <v>18.8616</v>
+        <v>17.9307</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>1</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0629</v>
+        <v>-0.0152</v>
       </c>
       <c r="J329" t="n">
-        <v>-1.8241</v>
+        <v>-0.4408</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>0.93</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3409</v>
+        <v>-0.2794</v>
       </c>
       <c r="J330" t="n">
-        <v>-9.886100000000001</v>
+        <v>-8.102600000000001</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.89</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4586</v>
+        <v>-0.3976</v>
       </c>
       <c r="J331" t="n">
-        <v>-13.2994</v>
+        <v>-11.5304</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>1.27</v>
       </c>
       <c r="I332" t="n">
-        <v>0.5466</v>
+        <v>0.6515</v>
       </c>
       <c r="J332" t="n">
-        <v>13.1184</v>
+        <v>15.636</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>0.9</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.1315</v>
+        <v>-0.115</v>
       </c>
       <c r="J333" t="n">
-        <v>-3.156</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>0.85</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.2207</v>
+        <v>-0.1689</v>
       </c>
       <c r="J334" t="n">
-        <v>-5.2968</v>
+        <v>-4.0536</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.66</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.5332</v>
+        <v>-0.3516</v>
       </c>
       <c r="J335" t="n">
-        <v>-12.7968</v>
+        <v>-8.4384</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.43</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.8222</v>
+        <v>-0.5641</v>
       </c>
       <c r="J336" t="n">
-        <v>-19.7328</v>
+        <v>-13.5384</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.67</v>
       </c>
       <c r="I337" t="n">
-        <v>1.5191</v>
+        <v>1.338</v>
       </c>
       <c r="J337" t="n">
-        <v>36.4584</v>
+        <v>32.112</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.45</v>
       </c>
       <c r="I338" t="n">
-        <v>1.0895</v>
+        <v>1.0641</v>
       </c>
       <c r="J338" t="n">
-        <v>26.148</v>
+        <v>25.5384</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>1.33</v>
       </c>
       <c r="I339" t="n">
-        <v>0.8256</v>
+        <v>0.8457</v>
       </c>
       <c r="J339" t="n">
-        <v>19.8144</v>
+        <v>20.2968</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>1.03</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.0077</v>
+        <v>0.0693</v>
       </c>
       <c r="J340" t="n">
-        <v>-0.1848</v>
+        <v>1.6632</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>0.83</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6726</v>
+        <v>-0.6111</v>
       </c>
       <c r="J341" t="n">
-        <v>-16.1424</v>
+        <v>-14.6664</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.3</v>
       </c>
       <c r="I342" t="n">
-        <v>0.5004</v>
+        <v>0.5961</v>
       </c>
       <c r="J342" t="n">
-        <v>14.0112</v>
+        <v>16.6908</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.14</v>
       </c>
       <c r="I343" t="n">
-        <v>0.271</v>
+        <v>0.3109</v>
       </c>
       <c r="J343" t="n">
-        <v>7.588</v>
+        <v>8.7052</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>1.12</v>
       </c>
       <c r="I344" t="n">
-        <v>0.238</v>
+        <v>0.2727</v>
       </c>
       <c r="J344" t="n">
-        <v>6.664</v>
+        <v>7.6356</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>0.96</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1362</v>
+        <v>-0.0693</v>
       </c>
       <c r="J345" t="n">
-        <v>-3.8136</v>
+        <v>-1.9404</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.78</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4243</v>
+        <v>-0.2656</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.8804</v>
+        <v>-7.4368</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.26</v>
       </c>
       <c r="I347" t="n">
-        <v>0.771</v>
+        <v>0.7417</v>
       </c>
       <c r="J347" t="n">
-        <v>21.588</v>
+        <v>20.7676</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>1.19</v>
       </c>
       <c r="I348" t="n">
-        <v>0.5982</v>
+        <v>0.5669</v>
       </c>
       <c r="J348" t="n">
-        <v>16.7496</v>
+        <v>15.8732</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>1.09</v>
       </c>
       <c r="I349" t="n">
-        <v>0.3108</v>
+        <v>0.3</v>
       </c>
       <c r="J349" t="n">
-        <v>8.702400000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3102</v>
+        <v>-0.2487</v>
       </c>
       <c r="J350" t="n">
-        <v>-8.685600000000001</v>
+        <v>-6.9636</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.88</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4872</v>
+        <v>-0.4266</v>
       </c>
       <c r="J351" t="n">
-        <v>-13.6416</v>
+        <v>-11.9448</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.3</v>
       </c>
       <c r="I352" t="n">
-        <v>0.5243</v>
+        <v>0.6218</v>
       </c>
       <c r="J352" t="n">
-        <v>15.729</v>
+        <v>18.654</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.08</v>
       </c>
       <c r="I353" t="n">
-        <v>0.1975</v>
+        <v>0.2078</v>
       </c>
       <c r="J353" t="n">
-        <v>5.925</v>
+        <v>6.234</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>0.95</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.1303</v>
+        <v>-0.0747</v>
       </c>
       <c r="J354" t="n">
-        <v>-3.909</v>
+        <v>-2.241</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.3662</v>
+        <v>-0.2276</v>
       </c>
       <c r="J355" t="n">
-        <v>-10.986</v>
+        <v>-6.828</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.8</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.3808</v>
+        <v>-0.2376</v>
       </c>
       <c r="J356" t="n">
-        <v>-11.424</v>
+        <v>-7.128</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.52</v>
       </c>
       <c r="I357" t="n">
-        <v>1.266</v>
+        <v>1.1691</v>
       </c>
       <c r="J357" t="n">
-        <v>37.98</v>
+        <v>35.073</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.41</v>
       </c>
       <c r="I358" t="n">
-        <v>1.041</v>
+        <v>1.0234</v>
       </c>
       <c r="J358" t="n">
-        <v>31.23</v>
+        <v>30.702</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>1.12</v>
       </c>
       <c r="I359" t="n">
-        <v>0.2979</v>
+        <v>0.3596</v>
       </c>
       <c r="J359" t="n">
-        <v>8.936999999999999</v>
+        <v>10.788</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>1.12</v>
       </c>
       <c r="I360" t="n">
-        <v>0.2979</v>
+        <v>0.3596</v>
       </c>
       <c r="J360" t="n">
-        <v>8.936999999999999</v>
+        <v>10.788</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.79</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-0.6989</v>
       </c>
       <c r="J361" t="n">
-        <v>-22.545</v>
+        <v>-20.967</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.21</v>
       </c>
       <c r="I362" t="n">
-        <v>0.6197</v>
+        <v>0.602</v>
       </c>
       <c r="J362" t="n">
-        <v>22.3092</v>
+        <v>21.672</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>1.16</v>
       </c>
       <c r="I363" t="n">
-        <v>0.4854</v>
+        <v>0.4764</v>
       </c>
       <c r="J363" t="n">
-        <v>17.4744</v>
+        <v>17.1504</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>1.1</v>
       </c>
       <c r="I364" t="n">
-        <v>0.2864</v>
+        <v>0.32</v>
       </c>
       <c r="J364" t="n">
-        <v>10.3104</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>1.09</v>
       </c>
       <c r="I365" t="n">
-        <v>0.2541</v>
+        <v>0.2921</v>
       </c>
       <c r="J365" t="n">
-        <v>9.147600000000001</v>
+        <v>10.5156</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>1.04</v>
       </c>
       <c r="I366" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.1391</v>
       </c>
       <c r="J366" t="n">
-        <v>3.168</v>
+        <v>5.0076</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.01</v>
       </c>
       <c r="I367" t="n">
-        <v>0.0886</v>
+        <v>0.0606</v>
       </c>
       <c r="J367" t="n">
-        <v>3.1896</v>
+        <v>2.1816</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>0.97</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.0297</v>
+        <v>-0.0402</v>
       </c>
       <c r="J368" t="n">
-        <v>-1.0692</v>
+        <v>-1.4472</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>0.9</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.1756</v>
+        <v>-0.1242</v>
       </c>
       <c r="J369" t="n">
-        <v>-6.3216</v>
+        <v>-4.4712</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>0.85</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.2746</v>
+        <v>-0.1761</v>
       </c>
       <c r="J370" t="n">
-        <v>-9.8856</v>
+        <v>-6.3396</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.76</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.4147</v>
+        <v>-0.2661</v>
       </c>
       <c r="J371" t="n">
-        <v>-14.9292</v>
+        <v>-9.579599999999999</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>0.93</v>
       </c>
       <c r="I372" t="n">
-        <v>-0.0111</v>
+        <v>-0.0437</v>
       </c>
       <c r="J372" t="n">
-        <v>-0.2442</v>
+        <v>-0.9614</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>0.91</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.0471</v>
+        <v>-0.0693</v>
       </c>
       <c r="J373" t="n">
-        <v>-1.0362</v>
+        <v>-1.5246</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>0.59</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.5825</v>
+        <v>-0.3952</v>
       </c>
       <c r="J374" t="n">
-        <v>-12.815</v>
+        <v>-8.6944</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>0.59</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.5825</v>
+        <v>-0.3952</v>
       </c>
       <c r="J375" t="n">
-        <v>-12.815</v>
+        <v>-8.6944</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>0.38</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.8582</v>
+        <v>-0.592</v>
       </c>
       <c r="J376" t="n">
-        <v>-18.8804</v>
+        <v>-13.024</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.69</v>
       </c>
       <c r="I377" t="n">
-        <v>1.5066</v>
+        <v>1.3363</v>
       </c>
       <c r="J377" t="n">
-        <v>33.1452</v>
+        <v>29.3986</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>1.4</v>
       </c>
       <c r="I378" t="n">
-        <v>0.9194</v>
+        <v>0.9692</v>
       </c>
       <c r="J378" t="n">
-        <v>20.2268</v>
+        <v>21.3224</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>1.34</v>
       </c>
       <c r="I379" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.8495</v>
       </c>
       <c r="J379" t="n">
-        <v>16.6892</v>
+        <v>18.689</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>1.3</v>
       </c>
       <c r="I380" t="n">
-        <v>0.6633</v>
+        <v>0.7614</v>
       </c>
       <c r="J380" t="n">
-        <v>14.5926</v>
+        <v>16.7508</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>1.13</v>
       </c>
       <c r="I381" t="n">
-        <v>0.2513</v>
+        <v>0.3457</v>
       </c>
       <c r="J381" t="n">
-        <v>5.5286</v>
+        <v>7.6054</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.22</v>
       </c>
       <c r="I382" t="n">
-        <v>0.4232</v>
+        <v>0.4865</v>
       </c>
       <c r="J382" t="n">
-        <v>11.8496</v>
+        <v>13.622</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.18</v>
       </c>
       <c r="I383" t="n">
-        <v>0.3658</v>
+        <v>0.4121</v>
       </c>
       <c r="J383" t="n">
-        <v>10.2424</v>
+        <v>11.5388</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.05</v>
       </c>
       <c r="I384" t="n">
-        <v>0.1491</v>
+        <v>0.1464</v>
       </c>
       <c r="J384" t="n">
-        <v>4.1748</v>
+        <v>4.0992</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>0.85</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.2999</v>
+        <v>-0.1842</v>
       </c>
       <c r="J385" t="n">
-        <v>-8.3972</v>
+        <v>-5.1576</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>0.54</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-0.4804</v>
       </c>
       <c r="J386" t="n">
-        <v>-19.9696</v>
+        <v>-13.4512</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.27</v>
       </c>
       <c r="I387" t="n">
-        <v>0.7798</v>
+        <v>0.7559</v>
       </c>
       <c r="J387" t="n">
-        <v>21.8344</v>
+        <v>21.1652</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>1.14</v>
       </c>
       <c r="I388" t="n">
-        <v>0.4445</v>
+        <v>0.4298</v>
       </c>
       <c r="J388" t="n">
-        <v>12.446</v>
+        <v>12.0344</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>1.07</v>
       </c>
       <c r="I389" t="n">
-        <v>0.2053</v>
+        <v>0.2387</v>
       </c>
       <c r="J389" t="n">
-        <v>5.7484</v>
+        <v>6.6836</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>1.04</v>
       </c>
       <c r="I390" t="n">
-        <v>0.1011</v>
+        <v>0.1444</v>
       </c>
       <c r="J390" t="n">
-        <v>2.8308</v>
+        <v>4.0432</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.97</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.22</v>
+        <v>-0.1554</v>
       </c>
       <c r="J391" t="n">
-        <v>-6.16</v>
+        <v>-4.3512</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>1.27</v>
       </c>
       <c r="I392" t="n">
-        <v>0.5474</v>
+        <v>0.6528</v>
       </c>
       <c r="J392" t="n">
-        <v>14.2324</v>
+        <v>16.9728</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>0.85</v>
       </c>
       <c r="I393" t="n">
-        <v>-0.2195</v>
+        <v>-0.1687</v>
       </c>
       <c r="J393" t="n">
-        <v>-5.707</v>
+        <v>-4.3862</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>0.77</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.3711</v>
+        <v>-0.2462</v>
       </c>
       <c r="J394" t="n">
-        <v>-9.6486</v>
+        <v>-6.4012</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.68</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.5049</v>
+        <v>-0.3324</v>
       </c>
       <c r="J395" t="n">
-        <v>-13.1274</v>
+        <v>-8.6424</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.53</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.7014</v>
+        <v>-0.4724</v>
       </c>
       <c r="J396" t="n">
-        <v>-18.2364</v>
+        <v>-12.2824</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>1.41</v>
       </c>
       <c r="I397" t="n">
-        <v>1.0225</v>
+        <v>1.0145</v>
       </c>
       <c r="J397" t="n">
-        <v>26.585</v>
+        <v>26.377</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.32</v>
       </c>
       <c r="I398" t="n">
-        <v>0.8224</v>
+        <v>0.8316</v>
       </c>
       <c r="J398" t="n">
-        <v>21.3824</v>
+        <v>21.6216</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>1.29</v>
       </c>
       <c r="I399" t="n">
-        <v>0.751</v>
+        <v>0.7635</v>
       </c>
       <c r="J399" t="n">
-        <v>19.526</v>
+        <v>19.851</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>1.13</v>
       </c>
       <c r="I400" t="n">
-        <v>0.3072</v>
+        <v>0.3784</v>
       </c>
       <c r="J400" t="n">
-        <v>7.9872</v>
+        <v>9.8384</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>0.99</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.1915</v>
+        <v>-0.1105</v>
       </c>
       <c r="J401" t="n">
-        <v>-4.979</v>
+        <v>-2.873</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.18</v>
       </c>
       <c r="I402" t="n">
-        <v>0.3744</v>
+        <v>0.4207</v>
       </c>
       <c r="J402" t="n">
-        <v>8.9856</v>
+        <v>10.0968</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.08</v>
       </c>
       <c r="I403" t="n">
-        <v>0.2147</v>
+        <v>0.2198</v>
       </c>
       <c r="J403" t="n">
-        <v>5.1528</v>
+        <v>5.2752</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>1.05</v>
       </c>
       <c r="I404" t="n">
-        <v>0.1589</v>
+        <v>0.1526</v>
       </c>
       <c r="J404" t="n">
-        <v>3.8136</v>
+        <v>3.6624</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>0.78</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.3986</v>
+        <v>-0.2522</v>
       </c>
       <c r="J405" t="n">
-        <v>-9.5664</v>
+        <v>-6.0528</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.63</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.5998</v>
+        <v>-0.3954</v>
       </c>
       <c r="J406" t="n">
-        <v>-14.3952</v>
+        <v>-9.489599999999999</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.28</v>
       </c>
       <c r="I407" t="n">
-        <v>0.7702</v>
+        <v>0.7599</v>
       </c>
       <c r="J407" t="n">
-        <v>18.4848</v>
+        <v>18.2376</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.27</v>
       </c>
       <c r="I408" t="n">
-        <v>0.7464</v>
+        <v>0.7363</v>
       </c>
       <c r="J408" t="n">
-        <v>17.9136</v>
+        <v>17.6712</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>1.24</v>
       </c>
       <c r="I409" t="n">
-        <v>0.673</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="J409" t="n">
-        <v>16.152</v>
+        <v>15.9552</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>1.01</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.0469</v>
+        <v>0.0175</v>
       </c>
       <c r="J410" t="n">
-        <v>-1.1256</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.98</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.2071</v>
+        <v>-0.1335</v>
       </c>
       <c r="J411" t="n">
-        <v>-4.9704</v>
+        <v>-3.204</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.34</v>
       </c>
       <c r="I412" t="n">
-        <v>0.5825</v>
+        <v>0.6998</v>
       </c>
       <c r="J412" t="n">
-        <v>30.29</v>
+        <v>36.3896</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.03</v>
       </c>
       <c r="I413" t="n">
-        <v>0.1072</v>
+        <v>0.0982</v>
       </c>
       <c r="J413" t="n">
-        <v>5.5744</v>
+        <v>5.1064</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>0.85</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.2999</v>
+        <v>-0.1842</v>
       </c>
       <c r="J414" t="n">
-        <v>-15.5948</v>
+        <v>-9.5784</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>0.83</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.331</v>
+        <v>-0.2049</v>
       </c>
       <c r="J415" t="n">
-        <v>-17.212</v>
+        <v>-10.6548</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.79</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.3903</v>
+        <v>-0.2452</v>
       </c>
       <c r="J416" t="n">
-        <v>-20.2956</v>
+        <v>-12.7504</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.51</v>
       </c>
       <c r="I417" t="n">
-        <v>1.2571</v>
+        <v>1.162</v>
       </c>
       <c r="J417" t="n">
-        <v>65.36920000000001</v>
+        <v>60.424</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.29</v>
       </c>
       <c r="I418" t="n">
-        <v>0.7857</v>
+        <v>0.779</v>
       </c>
       <c r="J418" t="n">
-        <v>40.8564</v>
+        <v>40.508</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>1.08</v>
       </c>
       <c r="I419" t="n">
-        <v>0.1919</v>
+        <v>0.252</v>
       </c>
       <c r="J419" t="n">
-        <v>9.9788</v>
+        <v>13.104</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>1.02</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.0105</v>
+        <v>0.0549</v>
       </c>
       <c r="J420" t="n">
-        <v>-0.546</v>
+        <v>2.8548</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.95</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3182</v>
+        <v>-0.2428</v>
       </c>
       <c r="J421" t="n">
-        <v>-16.5464</v>
+        <v>-12.6256</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.45</v>
       </c>
       <c r="I422" t="n">
-        <v>1.1829</v>
+        <v>1.1093</v>
       </c>
       <c r="J422" t="n">
-        <v>31.9383</v>
+        <v>29.9511</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.03</v>
       </c>
       <c r="I423" t="n">
-        <v>0.0755</v>
+        <v>0.1143</v>
       </c>
       <c r="J423" t="n">
-        <v>2.0385</v>
+        <v>3.0861</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>0.98</v>
       </c>
       <c r="I424" t="n">
-        <v>-0.1724</v>
+        <v>-0.1134</v>
       </c>
       <c r="J424" t="n">
-        <v>-4.6548</v>
+        <v>-3.0618</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>0.97</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.2111</v>
+        <v>-0.1506</v>
       </c>
       <c r="J425" t="n">
-        <v>-5.6997</v>
+        <v>-4.0662</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>0.97</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.2111</v>
+        <v>-0.1506</v>
       </c>
       <c r="J426" t="n">
-        <v>-5.6997</v>
+        <v>-4.0662</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.65</v>
       </c>
       <c r="I427" t="n">
-        <v>0.9282</v>
+        <v>1.1127</v>
       </c>
       <c r="J427" t="n">
-        <v>25.0614</v>
+        <v>30.0429</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>1.02</v>
       </c>
       <c r="I428" t="n">
-        <v>0.0645</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="J428" t="n">
-        <v>1.7415</v>
+        <v>1.7577</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.9</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.2298</v>
+        <v>-0.1349</v>
       </c>
       <c r="J429" t="n">
-        <v>-6.2046</v>
+        <v>-3.6423</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.74</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.4684</v>
+        <v>-0.2987</v>
       </c>
       <c r="J430" t="n">
-        <v>-12.6468</v>
+        <v>-8.0649</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.72</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.4951</v>
+        <v>-0.3179</v>
       </c>
       <c r="J431" t="n">
-        <v>-13.3677</v>
+        <v>-8.583299999999999</v>
       </c>
     </row>
     <row r="432">
@@ -20549,10 +20549,10 @@
         <v>1.59</v>
       </c>
       <c r="I432" t="n">
-        <v>1.3408</v>
+        <v>1.2265</v>
       </c>
       <c r="J432" t="n">
-        <v>29.4976</v>
+        <v>26.983</v>
       </c>
     </row>
     <row r="433">
@@ -20589,10 +20589,10 @@
         <v>1.5</v>
       </c>
       <c r="I433" t="n">
-        <v>1.1629</v>
+        <v>1.1161</v>
       </c>
       <c r="J433" t="n">
-        <v>25.5838</v>
+        <v>24.5542</v>
       </c>
     </row>
     <row r="434">
@@ -20629,10 +20629,10 @@
         <v>1.36</v>
       </c>
       <c r="I434" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="J434" t="n">
-        <v>18.8848</v>
+        <v>19.7714</v>
       </c>
     </row>
     <row r="435">
@@ -20669,10 +20669,10 @@
         <v>1.15</v>
       </c>
       <c r="I435" t="n">
-        <v>0.3202</v>
+        <v>0.41</v>
       </c>
       <c r="J435" t="n">
-        <v>7.0444</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="436">
@@ -20709,10 +20709,10 @@
         <v>1.01</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.1043</v>
+        <v>-0.023</v>
       </c>
       <c r="J436" t="n">
-        <v>-2.2946</v>
+        <v>-0.506</v>
       </c>
     </row>
     <row r="437">
@@ -20749,10 +20749,10 @@
         <v>1.04</v>
       </c>
       <c r="I437" t="n">
-        <v>0.2198</v>
+        <v>0.209</v>
       </c>
       <c r="J437" t="n">
-        <v>4.8356</v>
+        <v>4.598</v>
       </c>
     </row>
     <row r="438">
@@ -20789,10 +20789,10 @@
         <v>0.84</v>
       </c>
       <c r="I438" t="n">
-        <v>-0.1986</v>
+        <v>-0.1677</v>
       </c>
       <c r="J438" t="n">
-        <v>-4.3692</v>
+        <v>-3.6894</v>
       </c>
     </row>
     <row r="439">
@@ -20829,10 +20829,10 @@
         <v>0.83</v>
       </c>
       <c r="I439" t="n">
-        <v>-0.2152</v>
+        <v>-0.1783</v>
       </c>
       <c r="J439" t="n">
-        <v>-4.7344</v>
+        <v>-3.9226</v>
       </c>
     </row>
     <row r="440">
@@ -20869,10 +20869,10 @@
         <v>0.53</v>
       </c>
       <c r="I440" t="n">
-        <v>-0.6856</v>
+        <v>-0.4623</v>
       </c>
       <c r="J440" t="n">
-        <v>-15.0832</v>
+        <v>-10.1706</v>
       </c>
     </row>
     <row r="441">
@@ -20909,10 +20909,10 @@
         <v>0.5</v>
       </c>
       <c r="I441" t="n">
-        <v>-0.7238</v>
+        <v>-0.4902</v>
       </c>
       <c r="J441" t="n">
-        <v>-15.9236</v>
+        <v>-10.7844</v>
       </c>
     </row>
     <row r="442">
@@ -20949,10 +20949,10 @@
         <v>1.36</v>
       </c>
       <c r="I442" t="n">
-        <v>0.5607</v>
+        <v>0.6803</v>
       </c>
       <c r="J442" t="n">
-        <v>15.6996</v>
+        <v>19.0484</v>
       </c>
     </row>
     <row r="443">
@@ -20989,10 +20989,10 @@
         <v>1.24</v>
       </c>
       <c r="I443" t="n">
-        <v>0.4021</v>
+        <v>0.479</v>
       </c>
       <c r="J443" t="n">
-        <v>11.2588</v>
+        <v>13.412</v>
       </c>
     </row>
     <row r="444">
@@ -21029,10 +21029,10 @@
         <v>1.03</v>
       </c>
       <c r="I444" t="n">
-        <v>0.0322</v>
+        <v>0.0752</v>
       </c>
       <c r="J444" t="n">
-        <v>0.9016</v>
+        <v>2.1056</v>
       </c>
     </row>
     <row r="445">
@@ -21069,10 +21069,10 @@
         <v>0.98</v>
       </c>
       <c r="I445" t="n">
-        <v>-0.1081</v>
+        <v>-0.0469</v>
       </c>
       <c r="J445" t="n">
-        <v>-3.0268</v>
+        <v>-1.3132</v>
       </c>
     </row>
     <row r="446">
@@ -21109,10 +21109,10 @@
         <v>0.95</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.1699</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="J446" t="n">
-        <v>-4.7572</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="447">
@@ -21149,10 +21149,10 @@
         <v>1.39</v>
       </c>
       <c r="I447" t="n">
-        <v>1.0876</v>
+        <v>1.044</v>
       </c>
       <c r="J447" t="n">
-        <v>30.4528</v>
+        <v>29.232</v>
       </c>
     </row>
     <row r="448">
@@ -21189,10 +21189,10 @@
         <v>1.11</v>
       </c>
       <c r="I448" t="n">
-        <v>0.4084</v>
+        <v>0.3686</v>
       </c>
       <c r="J448" t="n">
-        <v>11.4352</v>
+        <v>10.3208</v>
       </c>
     </row>
     <row r="449">
@@ -21229,10 +21229,10 @@
         <v>1.07</v>
       </c>
       <c r="I449" t="n">
-        <v>0.2837</v>
+        <v>0.2524</v>
       </c>
       <c r="J449" t="n">
-        <v>7.9436</v>
+        <v>7.0672</v>
       </c>
     </row>
     <row r="450">
@@ -21269,10 +21269,10 @@
         <v>0.8</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.6776</v>
+        <v>-0.6289</v>
       </c>
       <c r="J450" t="n">
-        <v>-18.9728</v>
+        <v>-17.6092</v>
       </c>
     </row>
     <row r="451">
@@ -21309,10 +21309,10 @@
         <v>0.76</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.7746</v>
+        <v>-0.7316</v>
       </c>
       <c r="J451" t="n">
-        <v>-21.6888</v>
+        <v>-20.4848</v>
       </c>
     </row>
     <row r="452">
@@ -21349,10 +21349,10 @@
         <v>1.69</v>
       </c>
       <c r="I452" t="n">
-        <v>0.9201</v>
+        <v>1.1029</v>
       </c>
       <c r="J452" t="n">
-        <v>27.603</v>
+        <v>33.087</v>
       </c>
     </row>
     <row r="453">
@@ -21389,10 +21389,10 @@
         <v>1.29</v>
       </c>
       <c r="I453" t="n">
-        <v>0.4522</v>
+        <v>0.5506</v>
       </c>
       <c r="J453" t="n">
-        <v>13.566</v>
+        <v>16.518</v>
       </c>
     </row>
     <row r="454">
@@ -21429,10 +21429,10 @@
         <v>1.14</v>
       </c>
       <c r="I454" t="n">
-        <v>0.2133</v>
+        <v>0.295</v>
       </c>
       <c r="J454" t="n">
-        <v>6.399</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="455">
@@ -21469,10 +21469,10 @@
         <v>0.86</v>
       </c>
       <c r="I455" t="n">
-        <v>-0.3295</v>
+        <v>-0.1955</v>
       </c>
       <c r="J455" t="n">
-        <v>-9.885</v>
+        <v>-5.865</v>
       </c>
     </row>
     <row r="456">
@@ -21509,10 +21509,10 @@
         <v>0.86</v>
       </c>
       <c r="I456" t="n">
-        <v>-0.3295</v>
+        <v>-0.1955</v>
       </c>
       <c r="J456" t="n">
-        <v>-9.885</v>
+        <v>-5.865</v>
       </c>
     </row>
     <row r="457">
@@ -21549,10 +21549,10 @@
         <v>1.23</v>
       </c>
       <c r="I457" t="n">
-        <v>0.7188</v>
+        <v>0.6813</v>
       </c>
       <c r="J457" t="n">
-        <v>21.564</v>
+        <v>20.439</v>
       </c>
     </row>
     <row r="458">
@@ -21589,10 +21589,10 @@
         <v>1.17</v>
       </c>
       <c r="I458" t="n">
-        <v>0.5672</v>
+        <v>0.5271</v>
       </c>
       <c r="J458" t="n">
-        <v>17.016</v>
+        <v>15.813</v>
       </c>
     </row>
     <row r="459">
@@ -21629,10 +21629,10 @@
         <v>1.07</v>
       </c>
       <c r="I459" t="n">
-        <v>0.2739</v>
+        <v>0.2494</v>
       </c>
       <c r="J459" t="n">
-        <v>8.217000000000001</v>
+        <v>7.482</v>
       </c>
     </row>
     <row r="460">
@@ -21669,10 +21669,10 @@
         <v>0.98</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.1477</v>
+        <v>-0.1025</v>
       </c>
       <c r="J460" t="n">
-        <v>-4.431</v>
+        <v>-3.075</v>
       </c>
     </row>
     <row r="461">
@@ -21709,10 +21709,10 @@
         <v>0.74</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.8255</v>
+        <v>-0.7854</v>
       </c>
       <c r="J461" t="n">
-        <v>-24.765</v>
+        <v>-23.562</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2637/event_2637_evp_summary.xlsx
+++ b/database/event/2637/event_2637_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6585</v>
+        <v>6.6878</v>
       </c>
       <c r="C2" t="n">
-        <v>4.0536</v>
+        <v>4.0715</v>
       </c>
       <c r="D2" t="n">
-        <v>2.368</v>
+        <v>2.4202</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6585</v>
+        <v>6.6878</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2871</v>
+        <v>3.1765</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3714</v>
+        <v>3.5113</v>
       </c>
       <c r="H2" t="n">
-        <v>6.0953</v>
+        <v>5.5862</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1693</v>
+        <v>3.0165</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3714</v>
+        <v>3.5113</v>
       </c>
       <c r="K2" t="n">
         <v>146</v>
@@ -529,7 +529,7 @@
         <v>161</v>
       </c>
       <c r="M2" t="n">
-        <v>6.540699999999999</v>
+        <v>6.5278</v>
       </c>
       <c r="N2" t="n">
         <v>307</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4318</v>
+        <v>6.484</v>
       </c>
       <c r="C3" t="n">
-        <v>3.9156</v>
+        <v>3.9474</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2656</v>
+        <v>2.3274</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4318</v>
+        <v>6.484</v>
       </c>
       <c r="F3" t="n">
-        <v>3.111</v>
+        <v>2.3746</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3208</v>
+        <v>4.1094</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4715</v>
+        <v>2.4723</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7629</v>
+        <v>2.6014</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3208</v>
+        <v>4.1094</v>
       </c>
       <c r="K3" t="n">
         <v>198</v>
@@ -575,7 +575,7 @@
         <v>211</v>
       </c>
       <c r="M3" t="n">
-        <v>7.0837</v>
+        <v>6.7108</v>
       </c>
       <c r="N3" t="n">
         <v>409</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3558</v>
+        <v>6.2929</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8694</v>
+        <v>3.8311</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2313</v>
+        <v>2.2405</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3558</v>
+        <v>6.2929</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0952</v>
+        <v>2.8289</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2606</v>
+        <v>3.464</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4368</v>
+        <v>3.4666</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7253</v>
+        <v>3.6476</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2606</v>
+        <v>3.464</v>
       </c>
       <c r="K4" t="n">
         <v>198</v>
@@ -621,7 +621,7 @@
         <v>211</v>
       </c>
       <c r="M4" t="n">
-        <v>6.9859</v>
+        <v>7.1116</v>
       </c>
       <c r="N4" t="n">
         <v>409</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.3443</v>
+        <v>6.2568</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8624</v>
+        <v>3.8091</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2261</v>
+        <v>2.224</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3443</v>
+        <v>6.2568</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4439</v>
+        <v>2.7791</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9004</v>
+        <v>3.4777</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4439</v>
+        <v>3.3577</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6491</v>
+        <v>3.533</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9004</v>
+        <v>3.4777</v>
       </c>
       <c r="K5" t="n">
         <v>198</v>
@@ -667,7 +667,7 @@
         <v>211</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5495</v>
+        <v>7.0107</v>
       </c>
       <c r="N5" t="n">
         <v>409</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7178</v>
+        <v>5.682</v>
       </c>
       <c r="C6" t="n">
-        <v>3.481</v>
+        <v>3.4592</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9433</v>
+        <v>1.9624</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7178</v>
+        <v>5.682</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2743</v>
+        <v>4.19</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4435</v>
+        <v>1.492</v>
       </c>
       <c r="H6" t="n">
-        <v>9.5738</v>
+        <v>8.930300000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9779</v>
+        <v>4.8223</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4435</v>
+        <v>1.492</v>
       </c>
       <c r="K6" t="n">
         <v>146</v>
@@ -713,7 +713,7 @@
         <v>161</v>
       </c>
       <c r="M6" t="n">
-        <v>6.4214</v>
+        <v>6.3143</v>
       </c>
       <c r="N6" t="n">
         <v>307</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0107</v>
+        <v>4.1723</v>
       </c>
       <c r="C7" t="n">
-        <v>2.4417</v>
+        <v>2.5401</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1726</v>
+        <v>1.2751</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0107</v>
+        <v>4.1723</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8589</v>
+        <v>1.8148</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1517</v>
+        <v>2.3574</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8589</v>
+        <v>1.8148</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9354</v>
+        <v>1.8616</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1517</v>
+        <v>2.3574</v>
       </c>
       <c r="K7" t="n">
         <v>175</v>
@@ -759,7 +759,7 @@
         <v>137</v>
       </c>
       <c r="M7" t="n">
-        <v>4.0871</v>
+        <v>4.219</v>
       </c>
       <c r="N7" t="n">
         <v>312</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3891</v>
+        <v>3.3349</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0633</v>
+        <v>2.0303</v>
       </c>
       <c r="D8" t="n">
-        <v>0.892</v>
+        <v>0.8939</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3891</v>
+        <v>3.3349</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1993</v>
+        <v>3.119</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1898</v>
+        <v>0.2159</v>
       </c>
       <c r="H8" t="n">
-        <v>5.7861</v>
+        <v>5.3966</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0085</v>
+        <v>2.9141</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1898</v>
+        <v>0.2159</v>
       </c>
       <c r="K8" t="n">
         <v>146</v>
@@ -805,7 +805,7 @@
         <v>161</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1983</v>
+        <v>3.13</v>
       </c>
       <c r="N8" t="n">
         <v>307</v>
@@ -814,277 +814,277 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1563</v>
+        <v>3.1983</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9215</v>
+        <v>1.9471</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7869</v>
+        <v>0.8317</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1563</v>
+        <v>3.1983</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1563</v>
+        <v>0.2476</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2.9507</v>
       </c>
       <c r="H9" t="n">
-        <v>3.571</v>
+        <v>0.2476</v>
       </c>
       <c r="I9" t="n">
-        <v>3.571</v>
+        <v>0.2605</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.9507</v>
       </c>
       <c r="K9" t="n">
-        <v>118</v>
+        <v>198</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="M9" t="n">
-        <v>3.571</v>
+        <v>3.2112</v>
       </c>
       <c r="N9" t="n">
-        <v>118</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0364</v>
+        <v>2.9302</v>
       </c>
       <c r="C10" t="n">
-        <v>1.8485</v>
+        <v>1.7839</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7328</v>
+        <v>0.7097</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0364</v>
+        <v>2.9302</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0364</v>
+        <v>0.2989</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2.6314</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3077</v>
+        <v>0.2989</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3077</v>
+        <v>0.3066</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2.6314</v>
       </c>
       <c r="K10" t="n">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3077</v>
+        <v>2.938</v>
       </c>
       <c r="N10" t="n">
-        <v>128</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9632</v>
+        <v>2.8418</v>
       </c>
       <c r="C11" t="n">
-        <v>1.804</v>
+        <v>1.7301</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6997</v>
+        <v>0.6694</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9632</v>
+        <v>2.8418</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2244</v>
+        <v>2.8418</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7388</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2244</v>
+        <v>3.4948</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2432</v>
+        <v>3.4948</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7388</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>198</v>
+        <v>118</v>
       </c>
       <c r="L11" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.982</v>
+        <v>3.4948</v>
       </c>
       <c r="N11" t="n">
-        <v>409</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7765</v>
+        <v>2.7433</v>
       </c>
       <c r="C12" t="n">
-        <v>1.6903</v>
+        <v>1.6701</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6246</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7765</v>
+        <v>2.7433</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9769</v>
+        <v>2.7433</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2004</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5.0026</v>
+        <v>3.2793</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6011</v>
+        <v>3.2793</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2004</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="L12" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4007</v>
+        <v>3.2793</v>
       </c>
       <c r="N12" t="n">
-        <v>307</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6922</v>
+        <v>2.7</v>
       </c>
       <c r="C13" t="n">
-        <v>1.639</v>
+        <v>1.6437</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5774</v>
+        <v>0.6049</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6922</v>
+        <v>2.7</v>
       </c>
       <c r="F13" t="n">
-        <v>0.276</v>
+        <v>2.8867</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4162</v>
+        <v>-0.1867</v>
       </c>
       <c r="H13" t="n">
-        <v>0.276</v>
+        <v>4.6301</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2873</v>
+        <v>2.5002</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4162</v>
+        <v>-0.1867</v>
       </c>
       <c r="K13" t="n">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="L13" t="n">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7035</v>
+        <v>2.3135</v>
       </c>
       <c r="N13" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6779</v>
+        <v>2.4119</v>
       </c>
       <c r="C14" t="n">
-        <v>1.6303</v>
+        <v>1.4683</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5709</v>
+        <v>0.4737</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6779</v>
+        <v>2.4119</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0233</v>
+        <v>2.4119</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3454</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2788</v>
+        <v>2.5539</v>
       </c>
       <c r="I14" t="n">
-        <v>3.2788</v>
+        <v>2.5539</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3454</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="L14" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9334</v>
+        <v>2.5539</v>
       </c>
       <c r="N14" t="n">
-        <v>231</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6183</v>
+        <v>2.3864</v>
       </c>
       <c r="C15" t="n">
-        <v>1.594</v>
+        <v>1.4528</v>
       </c>
       <c r="D15" t="n">
-        <v>0.544</v>
+        <v>0.4621</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6183</v>
+        <v>2.3864</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6183</v>
+        <v>2.3864</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6183</v>
+        <v>2.4981</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6183</v>
+        <v>2.4981</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.6183</v>
+        <v>2.4981</v>
       </c>
       <c r="N15" t="n">
         <v>149</v>
@@ -1136,32 +1136,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5998</v>
+        <v>2.3463</v>
       </c>
       <c r="C16" t="n">
-        <v>1.5827</v>
+        <v>1.4284</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5357</v>
+        <v>0.4439</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5998</v>
+        <v>2.3463</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5998</v>
+        <v>2.3463</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5998</v>
+        <v>2.4104</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5998</v>
+        <v>2.4104</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5998</v>
+        <v>2.4104</v>
       </c>
       <c r="N16" t="n">
         <v>128</v>
@@ -1182,139 +1182,139 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.5097</v>
+        <v>2.2989</v>
       </c>
       <c r="C17" t="n">
-        <v>1.5279</v>
+        <v>1.3996</v>
       </c>
       <c r="D17" t="n">
-        <v>0.495</v>
+        <v>0.4223</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5097</v>
+        <v>2.2989</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1472</v>
+        <v>2.6839</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6375</v>
+        <v>-0.385</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5509</v>
+        <v>3.1492</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5509</v>
+        <v>3.1492</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6375</v>
+        <v>-0.385</v>
       </c>
       <c r="K17" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="L17" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9134</v>
+        <v>2.7642</v>
       </c>
       <c r="N17" t="n">
-        <v>176</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4934</v>
+        <v>2.2807</v>
       </c>
       <c r="C18" t="n">
-        <v>1.518</v>
+        <v>1.3885</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4876</v>
+        <v>0.414</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4934</v>
+        <v>2.2807</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4934</v>
+        <v>2.3038</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.0231</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4934</v>
+        <v>2.7069</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4934</v>
+        <v>1.4617</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.0231</v>
       </c>
       <c r="K18" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M18" t="n">
-        <v>2.4934</v>
+        <v>1.4386</v>
       </c>
       <c r="N18" t="n">
-        <v>128</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.4026</v>
+        <v>2.1309</v>
       </c>
       <c r="C19" t="n">
-        <v>1.4627</v>
+        <v>1.2973</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4466</v>
+        <v>0.3458</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4026</v>
+        <v>2.1309</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4106</v>
+        <v>2.8068</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.008</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>3.007</v>
+        <v>3.4182</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5635</v>
+        <v>3.4182</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.008</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="L19" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5555</v>
+        <v>2.7423</v>
       </c>
       <c r="N19" t="n">
-        <v>194</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0165</v>
+        <v>2.1041</v>
       </c>
       <c r="C20" t="n">
-        <v>1.2276</v>
+        <v>1.281</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2723</v>
+        <v>0.3336</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0165</v>
+        <v>2.1041</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0165</v>
+        <v>2.1041</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0165</v>
+        <v>2.1041</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0165</v>
+        <v>2.1041</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0165</v>
+        <v>2.1041</v>
       </c>
       <c r="N20" t="n">
         <v>134</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.8173</v>
+        <v>1.7964</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1064</v>
+        <v>1.0936</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1824</v>
+        <v>0.1936</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8173</v>
+        <v>1.7964</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8173</v>
+        <v>2.1625</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.3661</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8173</v>
+        <v>2.2408</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8173</v>
+        <v>1.21</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.3661</v>
       </c>
       <c r="K21" t="n">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="M21" t="n">
-        <v>1.8173</v>
+        <v>0.8439</v>
       </c>
       <c r="N21" t="n">
-        <v>163</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.7588</v>
+        <v>1.7422</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0707</v>
+        <v>1.0606</v>
       </c>
       <c r="D22" t="n">
-        <v>0.156</v>
+        <v>0.1689</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7588</v>
+        <v>1.7422</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1584</v>
+        <v>1.7422</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3996</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1584</v>
+        <v>1.7422</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1223</v>
+        <v>1.7422</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3996</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="L22" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7227000000000001</v>
+        <v>1.7422</v>
       </c>
       <c r="N22" t="n">
-        <v>307</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7176</v>
+        <v>1.6655</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0457</v>
+        <v>1.0139</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1374</v>
+        <v>0.134</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7176</v>
+        <v>1.6655</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7176</v>
+        <v>1.6655</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7176</v>
+        <v>1.6655</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7176</v>
+        <v>1.6655</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.7176</v>
+        <v>1.6655</v>
       </c>
       <c r="N23" t="n">
         <v>135</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.68</v>
+        <v>1.4414</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0228</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1204</v>
+        <v>0.032</v>
       </c>
       <c r="E24" t="n">
-        <v>1.68</v>
+        <v>1.4414</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5546</v>
+        <v>1.325</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1254</v>
+        <v>0.1164</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5546</v>
+        <v>1.325</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8083</v>
+        <v>0.7155</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1254</v>
+        <v>0.1164</v>
       </c>
       <c r="K24" t="n">
         <v>138</v>
@@ -1541,7 +1541,7 @@
         <v>56</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9337</v>
+        <v>0.8319000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>194</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.4856</v>
+        <v>1.4036</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9044</v>
+        <v>0.8545</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0327</v>
+        <v>0.0147</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4856</v>
+        <v>1.4036</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4856</v>
+        <v>1.4036</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.4856</v>
+        <v>1.4036</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4856</v>
+        <v>1.4036</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.4856</v>
+        <v>1.4036</v>
       </c>
       <c r="N25" t="n">
         <v>149</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.269</v>
+        <v>1.2152</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7726</v>
+        <v>0.7398</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>1.269</v>
+        <v>1.2152</v>
       </c>
       <c r="F26" t="n">
-        <v>1.269</v>
+        <v>1.2152</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.269</v>
+        <v>1.2152</v>
       </c>
       <c r="I26" t="n">
-        <v>1.269</v>
+        <v>1.2152</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.269</v>
+        <v>1.2152</v>
       </c>
       <c r="N26" t="n">
         <v>135</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2419</v>
+        <v>1.171</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7561</v>
+        <v>0.7129</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0774</v>
+        <v>-0.0911</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2419</v>
+        <v>1.171</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2419</v>
+        <v>1.171</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2419</v>
+        <v>1.171</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2419</v>
+        <v>1.171</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2419</v>
+        <v>1.171</v>
       </c>
       <c r="N27" t="n">
         <v>134</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1648</v>
+        <v>1.032</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7091</v>
+        <v>0.6283</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1122</v>
+        <v>-0.1544</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1648</v>
+        <v>1.032</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6909</v>
+        <v>0.6516</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.5261</v>
+        <v>0.3804</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6909</v>
+        <v>0.6516</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6909</v>
+        <v>0.6516</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.5261</v>
+        <v>0.3804</v>
       </c>
       <c r="K28" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="L28" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1648</v>
+        <v>1.032</v>
       </c>
       <c r="N28" t="n">
-        <v>176</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.0542</v>
+        <v>1.0152</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6418</v>
+        <v>0.618</v>
       </c>
       <c r="D29" t="n">
         <v>-0.1621</v>
       </c>
       <c r="E29" t="n">
-        <v>1.0542</v>
+        <v>1.0152</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7030999999999999</v>
+        <v>1.5667</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3511</v>
+        <v>-0.5515</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7030999999999999</v>
+        <v>1.5667</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7030999999999999</v>
+        <v>1.5667</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3511</v>
+        <v>-0.5515</v>
       </c>
       <c r="K29" t="n">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="L29" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="M29" t="n">
-        <v>1.0542</v>
+        <v>1.0152</v>
       </c>
       <c r="N29" t="n">
-        <v>231</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.0522</v>
+        <v>1.0075</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.163</v>
+        <v>-0.1656</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0522</v>
+        <v>1.0075</v>
       </c>
       <c r="F30" t="n">
-        <v>1.0522</v>
+        <v>1.0075</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.0522</v>
+        <v>1.0075</v>
       </c>
       <c r="I30" t="n">
-        <v>1.0522</v>
+        <v>1.0075</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.0522</v>
+        <v>1.0075</v>
       </c>
       <c r="N30" t="n">
         <v>134</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9438</v>
+        <v>0.9893</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5746</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2119</v>
+        <v>-0.1739</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9438</v>
+        <v>0.9893</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5505</v>
+        <v>0.5698</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3933</v>
+        <v>0.4195</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5505</v>
+        <v>0.5698</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5505</v>
+        <v>0.5698</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3933</v>
+        <v>0.4195</v>
       </c>
       <c r="K31" t="n">
         <v>131</v>
@@ -1863,7 +1863,7 @@
         <v>45</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9438</v>
+        <v>0.9893</v>
       </c>
       <c r="N31" t="n">
         <v>176</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.7861</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5079</v>
+        <v>0.4786</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2614</v>
+        <v>-0.2664</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.7861</v>
       </c>
       <c r="F32" t="n">
-        <v>1.8342</v>
+        <v>1.7861</v>
       </c>
       <c r="G32" t="n">
         <v>-1</v>
       </c>
       <c r="H32" t="n">
-        <v>1.8342</v>
+        <v>1.7861</v>
       </c>
       <c r="I32" t="n">
-        <v>1.8342</v>
+        <v>1.7861</v>
       </c>
       <c r="J32" t="n">
         <v>-1</v>
@@ -1909,7 +1909,7 @@
         <v>45</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.7861</v>
       </c>
       <c r="N32" t="n">
         <v>176</v>
@@ -1918,461 +1918,461 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8117</v>
+        <v>0.7411</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4942</v>
+        <v>0.4512</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2716</v>
+        <v>-0.2868</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8117</v>
+        <v>0.7411</v>
       </c>
       <c r="F33" t="n">
-        <v>1.2299</v>
+        <v>1.0293</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4182</v>
+        <v>-0.2882</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2299</v>
+        <v>1.0293</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6395</v>
+        <v>1.0558</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4182</v>
+        <v>-0.2882</v>
       </c>
       <c r="K33" t="n">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="L33" t="n">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2212999999999999</v>
+        <v>0.7676000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>194</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7065</v>
+        <v>0.6856</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4301</v>
+        <v>0.4174</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3191</v>
+        <v>-0.3121</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7065</v>
+        <v>0.6856</v>
       </c>
       <c r="F34" t="n">
-        <v>1.0876</v>
+        <v>1.1295</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.3811</v>
+        <v>-0.4439</v>
       </c>
       <c r="H34" t="n">
-        <v>1.0876</v>
+        <v>1.1295</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1323</v>
+        <v>0.6099</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.3811</v>
+        <v>-0.4439</v>
       </c>
       <c r="K34" t="n">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="L34" t="n">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7512000000000001</v>
+        <v>0.166</v>
       </c>
       <c r="N34" t="n">
-        <v>312</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5965</v>
+        <v>0.537</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3631</v>
+        <v>0.3269</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3687</v>
+        <v>-0.3797</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5965</v>
+        <v>0.537</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0469</v>
+        <v>0.537</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.4504</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.0469</v>
+        <v>0.537</v>
       </c>
       <c r="I35" t="n">
-        <v>1.0469</v>
+        <v>0.537</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.4504</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="L35" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5964999999999999</v>
+        <v>0.537</v>
       </c>
       <c r="N35" t="n">
-        <v>231</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.4999</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3465</v>
+        <v>0.3043</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3811</v>
+        <v>-0.3966</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.4999</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.9779</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.478</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.9779</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.9779</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.478</v>
       </c>
       <c r="K36" t="n">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.4999</v>
       </c>
       <c r="N36" t="n">
-        <v>128</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.521</v>
+        <v>0.4913</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3172</v>
+        <v>0.2991</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4028</v>
+        <v>-0.4006</v>
       </c>
       <c r="E37" t="n">
-        <v>0.521</v>
+        <v>0.4913</v>
       </c>
       <c r="F37" t="n">
-        <v>0.521</v>
+        <v>0.4913</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.521</v>
+        <v>0.4913</v>
       </c>
       <c r="I37" t="n">
-        <v>0.521</v>
+        <v>0.4913</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.521</v>
+        <v>0.4913</v>
       </c>
       <c r="N37" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5102</v>
+        <v>0.4856</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3106</v>
+        <v>0.2956</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.4077</v>
+        <v>-0.4031</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5102</v>
+        <v>0.4856</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5102</v>
+        <v>0.5058</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.0202</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5102</v>
+        <v>0.5058</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5102</v>
+        <v>0.5188</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.0202</v>
       </c>
       <c r="K38" t="n">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5102</v>
+        <v>0.4986</v>
       </c>
       <c r="N38" t="n">
-        <v>135</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4876</v>
+        <v>0.4802</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2968</v>
+        <v>0.2923</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4179</v>
+        <v>-0.4056</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4876</v>
+        <v>0.4802</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4876</v>
+        <v>0.4802</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4876</v>
+        <v>0.4802</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4876</v>
+        <v>0.4802</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4876</v>
+        <v>0.4802</v>
       </c>
       <c r="N39" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.46</v>
+        <v>0.4734</v>
       </c>
       <c r="C40" t="n">
-        <v>0.28</v>
+        <v>0.2882</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4303</v>
+        <v>-0.4087</v>
       </c>
       <c r="E40" t="n">
-        <v>0.46</v>
+        <v>0.4734</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5782</v>
+        <v>0.4734</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1182</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5782</v>
+        <v>0.4734</v>
       </c>
       <c r="I40" t="n">
-        <v>0.602</v>
+        <v>0.4734</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1182</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="L40" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4838</v>
+        <v>0.4734</v>
       </c>
       <c r="N40" t="n">
-        <v>312</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4138</v>
+        <v>0.3296</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2519</v>
+        <v>0.2007</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4512</v>
+        <v>-0.4742</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4138</v>
+        <v>0.3296</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4138</v>
+        <v>0.5276</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.198</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4138</v>
+        <v>0.5276</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4138</v>
+        <v>0.5276</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.198</v>
       </c>
       <c r="K41" t="n">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4138</v>
+        <v>0.3295999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>118</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3372</v>
+        <v>0.3277</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2053</v>
+        <v>0.1995</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4858</v>
+        <v>-0.475</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3372</v>
+        <v>0.3277</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5527</v>
+        <v>0.3277</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.2155</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5527</v>
+        <v>0.3277</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5527</v>
+        <v>0.3277</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.2155</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="L42" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3371999999999999</v>
+        <v>0.3277</v>
       </c>
       <c r="N42" t="n">
-        <v>231</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2885</v>
+        <v>0.2786</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1756</v>
+        <v>0.1696</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5078</v>
+        <v>-0.4974</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2885</v>
+        <v>0.2786</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2885</v>
+        <v>0.2786</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2885</v>
+        <v>0.2786</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2885</v>
+        <v>0.2786</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2885</v>
+        <v>0.2786</v>
       </c>
       <c r="N43" t="n">
         <v>149</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2072</v>
+        <v>0.1435</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1261</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5445</v>
+        <v>-0.5589</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2072</v>
+        <v>0.1435</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8032</v>
+        <v>0.7773</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.596</v>
+        <v>-0.6338</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8032</v>
+        <v>0.7773</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8032</v>
+        <v>0.7773</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.596</v>
+        <v>-0.6338</v>
       </c>
       <c r="K44" t="n">
         <v>131</v>
@@ -2461,7 +2461,7 @@
         <v>45</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2072000000000001</v>
+        <v>0.1435</v>
       </c>
       <c r="N44" t="n">
         <v>176</v>
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.1802</v>
+        <v>0.0575</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1097</v>
+        <v>0.035</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5567</v>
+        <v>-0.598</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1802</v>
+        <v>0.0575</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1802</v>
+        <v>0.0575</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1802</v>
+        <v>0.0575</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1802</v>
+        <v>0.0575</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1802</v>
+        <v>0.0575</v>
       </c>
       <c r="N45" t="n">
         <v>163</v>
@@ -2516,47 +2516,47 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.07290000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0444</v>
+        <v>-0.0365</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6051</v>
+        <v>-0.6515</v>
       </c>
       <c r="E46" t="n">
-        <v>0.07290000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5939</v>
+        <v>-0.06</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.521</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5939</v>
+        <v>-0.06</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3088</v>
+        <v>-0.06</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.521</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="L46" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.2122</v>
+        <v>-0.06</v>
       </c>
       <c r="N46" t="n">
-        <v>194</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47">
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0515</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0314</v>
+        <v>-0.0391</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6613</v>
+        <v>-0.6534</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0515</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0515</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0515</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0515</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0515</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="N47" t="n">
         <v>128</v>
@@ -2608,93 +2608,93 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0736</v>
+        <v>-0.1084</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0448</v>
+        <v>-0.066</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6712</v>
+        <v>-0.6735</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0736</v>
+        <v>-0.1084</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0736</v>
+        <v>0.4437</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>-0.5521</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0736</v>
+        <v>0.4437</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0736</v>
+        <v>0.2396</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>-0.5521</v>
       </c>
       <c r="K48" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0736</v>
+        <v>-0.3125</v>
       </c>
       <c r="N48" t="n">
-        <v>163</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.1663</v>
+        <v>-0.16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1012</v>
+        <v>-0.0974</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7131</v>
+        <v>-0.697</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1663</v>
+        <v>-0.16</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1663</v>
+        <v>-0.16</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1663</v>
+        <v>-0.16</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1663</v>
+        <v>-0.16</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.1663</v>
+        <v>-0.16</v>
       </c>
       <c r="N49" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50">
@@ -2704,31 +2704,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1746</v>
+        <v>-0.1939</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1063</v>
+        <v>-0.118</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7168</v>
+        <v>-0.7125</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1746</v>
+        <v>-0.1939</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0436</v>
+        <v>-0.0424</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.131</v>
+        <v>-0.1515</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.0436</v>
+        <v>-0.0424</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0436</v>
+        <v>-0.0424</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.131</v>
+        <v>-0.1515</v>
       </c>
       <c r="K50" t="n">
         <v>145</v>
@@ -2737,7 +2737,7 @@
         <v>86</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1746</v>
+        <v>-0.1939</v>
       </c>
       <c r="N50" t="n">
         <v>231</v>
@@ -2746,93 +2746,93 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1848</v>
+        <v>-0.2193</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1125</v>
+        <v>-0.1335</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.7214</v>
+        <v>-0.724</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1848</v>
+        <v>-0.2193</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1848</v>
+        <v>-0.2193</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1848</v>
+        <v>-0.2193</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1848</v>
+        <v>-0.2193</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1848</v>
+        <v>-0.2193</v>
       </c>
       <c r="N51" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2025</v>
+        <v>-0.2388</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1233</v>
+        <v>-0.1454</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.7294</v>
+        <v>-0.7329</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2025</v>
+        <v>-0.2388</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.2025</v>
+        <v>-0.2388</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2025</v>
+        <v>-0.2388</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2025</v>
+        <v>-0.2388</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.2025</v>
+        <v>-0.2388</v>
       </c>
       <c r="N52" t="n">
-        <v>149</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53">
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.2313</v>
+        <v>-0.3106</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1408</v>
+        <v>-0.1891</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.2313</v>
+        <v>-0.3106</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.2313</v>
+        <v>-0.3106</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.2313</v>
+        <v>-0.3106</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2313</v>
+        <v>-0.3106</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.2313</v>
+        <v>-0.3106</v>
       </c>
       <c r="N53" t="n">
         <v>163</v>
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3075</v>
+        <v>-0.3218</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1872</v>
+        <v>-0.1959</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.7768</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.3075</v>
+        <v>-0.3218</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3075</v>
+        <v>-0.3218</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.3075</v>
+        <v>-0.3218</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3075</v>
+        <v>-0.3218</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.3075</v>
+        <v>-0.3218</v>
       </c>
       <c r="N54" t="n">
         <v>135</v>
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.3635</v>
+        <v>-0.405</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2213</v>
+        <v>-0.2466</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.8021</v>
+        <v>-0.8086</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3635</v>
+        <v>-0.405</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3635</v>
+        <v>-0.405</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3635</v>
+        <v>-0.405</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3635</v>
+        <v>-0.405</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.3635</v>
+        <v>-0.405</v>
       </c>
       <c r="N55" t="n">
         <v>163</v>
@@ -2980,31 +2980,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.4716</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.3838</v>
+        <v>-0.2871</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.9227</v>
+        <v>-0.8389</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.4716</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.9569</v>
+        <v>-1.9165</v>
       </c>
       <c r="G56" t="n">
-        <v>1.3264</v>
+        <v>1.4449</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.9569</v>
+        <v>-1.9165</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.1212</v>
+        <v>-2.0165</v>
       </c>
       <c r="J56" t="n">
-        <v>1.3264</v>
+        <v>1.4449</v>
       </c>
       <c r="K56" t="n">
         <v>198</v>
@@ -3013,7 +3013,7 @@
         <v>211</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.7948</v>
+        <v>-0.5716000000000001</v>
       </c>
       <c r="N56" t="n">
         <v>409</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.7837</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.4943</v>
+        <v>-0.4771</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.0046</v>
+        <v>-0.981</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.7837</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.7837</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.7837</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.7837</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.7837</v>
       </c>
       <c r="N57" t="n">
         <v>118</v>
@@ -3072,31 +3072,31 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.8454</v>
+        <v>-0.8344</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.5147</v>
+        <v>-0.508</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.0197</v>
+        <v>-1.004</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.8454</v>
+        <v>-0.8344</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4569</v>
+        <v>-0.4871</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.3885</v>
+        <v>-0.3473</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.4569</v>
+        <v>-0.4871</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.4757</v>
+        <v>-0.4997</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.3885</v>
+        <v>-0.3473</v>
       </c>
       <c r="K58" t="n">
         <v>175</v>
@@ -3105,7 +3105,7 @@
         <v>137</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.8642000000000001</v>
+        <v>-0.847</v>
       </c>
       <c r="N58" t="n">
         <v>312</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.8597</v>
+        <v>-0.8752</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.5234</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.0261</v>
+        <v>-1.0226</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.8597</v>
+        <v>-0.8752</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.8597</v>
+        <v>-0.8752</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.8597</v>
+        <v>-0.8752</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.8597</v>
+        <v>-0.8752</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.8597</v>
+        <v>-0.8752</v>
       </c>
       <c r="N59" t="n">
         <v>135</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.1738</v>
+        <v>-1.1765</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.7146</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.1679</v>
+        <v>-1.1598</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.1738</v>
+        <v>-1.1765</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.1738</v>
+        <v>-1.1765</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.1738</v>
+        <v>-1.1765</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1738</v>
+        <v>-1.1765</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.1738</v>
+        <v>-1.1765</v>
       </c>
       <c r="N60" t="n">
         <v>118</v>
@@ -3210,31 +3210,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-3.5371</v>
+        <v>-3.3074</v>
       </c>
       <c r="C61" t="n">
-        <v>-2.1534</v>
+        <v>-2.0135</v>
       </c>
       <c r="D61" t="n">
-        <v>-2.2348</v>
+        <v>-2.1298</v>
       </c>
       <c r="E61" t="n">
-        <v>-3.5371</v>
+        <v>-3.3074</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.6272</v>
+        <v>-3.4232</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0901</v>
+        <v>0.1158</v>
       </c>
       <c r="H61" t="n">
-        <v>-3.6272</v>
+        <v>-3.4232</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.886</v>
+        <v>-1.8485</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0901</v>
+        <v>0.1158</v>
       </c>
       <c r="K61" t="n">
         <v>138</v>
@@ -3243,7 +3243,7 @@
         <v>56</v>
       </c>
       <c r="M61" t="n">
-        <v>-1.7959</v>
+        <v>-1.7327</v>
       </c>
       <c r="N61" t="n">
         <v>194</v>
@@ -3349,10 +3349,10 @@
         <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.604</v>
       </c>
       <c r="J2" t="n">
-        <v>15.0825</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4081</v>
+        <v>0.4199</v>
       </c>
       <c r="J3" t="n">
-        <v>10.2025</v>
+        <v>10.4975</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2873</v>
+        <v>0.3033</v>
       </c>
       <c r="J4" t="n">
-        <v>7.1825</v>
+        <v>7.5825</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>1.12</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1861</v>
+        <v>0.2027</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6525</v>
+        <v>5.0675</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.62</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4243</v>
+        <v>-0.4302</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.6075</v>
+        <v>-10.755</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.35</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5453</v>
+        <v>0.5343</v>
       </c>
       <c r="J7" t="n">
-        <v>13.6325</v>
+        <v>13.3575</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>1.3</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4789</v>
+        <v>0.4729</v>
       </c>
       <c r="J8" t="n">
-        <v>11.9725</v>
+        <v>11.8225</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1536</v>
+        <v>-0.1674</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.84</v>
+        <v>-4.185</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.74</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2954</v>
+        <v>-0.3084</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.385</v>
+        <v>-7.71</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.62</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4085</v>
+        <v>-0.4178</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.2125</v>
+        <v>-10.445</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.18</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4358</v>
+        <v>0.4244</v>
       </c>
       <c r="J12" t="n">
-        <v>12.2024</v>
+        <v>11.8832</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>1.16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3969</v>
+        <v>0.3882</v>
       </c>
       <c r="J13" t="n">
-        <v>11.1132</v>
+        <v>10.8696</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1032</v>
+        <v>-0.1172</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.8896</v>
+        <v>-3.2816</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>0.64</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3816</v>
+        <v>-0.3934</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.6848</v>
+        <v>-11.0152</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.63</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3909</v>
+        <v>-0.4023</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.9452</v>
+        <v>-11.2644</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.42</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0402</v>
+        <v>0.9929</v>
       </c>
       <c r="J17" t="n">
-        <v>29.1256</v>
+        <v>27.8012</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8212</v>
+        <v>0.7764</v>
       </c>
       <c r="J18" t="n">
-        <v>22.9936</v>
+        <v>21.7392</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.15</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4403</v>
+        <v>0.4358</v>
       </c>
       <c r="J19" t="n">
-        <v>12.3284</v>
+        <v>12.2024</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1232</v>
+        <v>0.1406</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4496</v>
+        <v>3.9368</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0446</v>
+        <v>-0.0307</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2488</v>
+        <v>-0.8596</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.7901</v>
       </c>
       <c r="J22" t="n">
-        <v>23.5256</v>
+        <v>22.1228</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4002</v>
+        <v>0.3906</v>
       </c>
       <c r="J23" t="n">
-        <v>11.2056</v>
+        <v>10.9368</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>0.76</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2661</v>
+        <v>-0.2816</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.4508</v>
+        <v>-7.8848</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.63</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3899</v>
+        <v>-0.4015</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.9172</v>
+        <v>-11.242</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.54</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4729</v>
+        <v>-0.4805</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.2412</v>
+        <v>-13.454</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1418</v>
+        <v>1.1401</v>
       </c>
       <c r="J27" t="n">
-        <v>31.9704</v>
+        <v>31.9228</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.27</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7246</v>
+        <v>0.6921</v>
       </c>
       <c r="J28" t="n">
-        <v>20.2888</v>
+        <v>19.3788</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.5877</v>
       </c>
       <c r="J29" t="n">
-        <v>17.0072</v>
+        <v>16.4556</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>1.15</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4375</v>
+        <v>0.4339</v>
       </c>
       <c r="J30" t="n">
-        <v>12.25</v>
+        <v>12.1492</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.85</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5427</v>
+        <v>-0.5069</v>
       </c>
       <c r="J31" t="n">
-        <v>-15.1956</v>
+        <v>-14.1932</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.25</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5364</v>
+        <v>0.5224</v>
       </c>
       <c r="J32" t="n">
-        <v>15.5556</v>
+        <v>15.1496</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.03</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0956</v>
+        <v>0.1027</v>
       </c>
       <c r="J33" t="n">
-        <v>2.7724</v>
+        <v>2.9783</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>0.99</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0194</v>
+        <v>-0.0244</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.5626</v>
+        <v>-0.7076</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.83</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2063</v>
+        <v>-0.2204</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.9827</v>
+        <v>-6.3916</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.8</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2367</v>
+        <v>-0.2506</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.8643</v>
+        <v>-7.2674</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.24</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7099</v>
+        <v>0.6683</v>
       </c>
       <c r="J37" t="n">
-        <v>20.5871</v>
+        <v>19.3807</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.2</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6082</v>
+        <v>0.5784</v>
       </c>
       <c r="J38" t="n">
-        <v>17.6378</v>
+        <v>16.7736</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1897</v>
+        <v>0.1951</v>
       </c>
       <c r="J39" t="n">
-        <v>5.5013</v>
+        <v>5.6579</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>0.89</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3862</v>
+        <v>-0.3743</v>
       </c>
       <c r="J40" t="n">
-        <v>-11.1998</v>
+        <v>-10.8547</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7073</v>
+        <v>-0.662</v>
       </c>
       <c r="J41" t="n">
-        <v>-20.5117</v>
+        <v>-19.198</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.06</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1866</v>
+        <v>0.1882</v>
       </c>
       <c r="J42" t="n">
-        <v>5.2248</v>
+        <v>5.2696</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1633</v>
+        <v>0.1653</v>
       </c>
       <c r="J43" t="n">
-        <v>4.5724</v>
+        <v>4.6284</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>0.95</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0679</v>
+        <v>-0.08</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.9012</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>0.8</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2279</v>
+        <v>-0.2437</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.3812</v>
+        <v>-6.8236</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>0.68</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3442</v>
+        <v>-0.3574</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.637600000000001</v>
+        <v>-10.0072</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.31</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6334</v>
+        <v>0.6992</v>
       </c>
       <c r="J47" t="n">
-        <v>17.7352</v>
+        <v>19.5776</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>1.3</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>17.346</v>
+        <v>19.152</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>1.27</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5775</v>
+        <v>0.6377</v>
       </c>
       <c r="J49" t="n">
-        <v>16.17</v>
+        <v>17.8556</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3539</v>
+        <v>-0.3389</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.9092</v>
+        <v>-9.4892</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6034</v>
+        <v>-0.5651</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.8952</v>
+        <v>-15.8228</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.21</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4343</v>
+        <v>0.4732</v>
       </c>
       <c r="J52" t="n">
-        <v>12.1604</v>
+        <v>13.2496</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>0.97</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0379</v>
+        <v>-0.0489</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.0612</v>
+        <v>-1.3692</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>0.83</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1946</v>
+        <v>-0.2113</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.4488</v>
+        <v>-5.9164</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.73</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2931</v>
+        <v>-0.3084</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.206799999999999</v>
+        <v>-8.635199999999999</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.67</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3503</v>
+        <v>-0.3639</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.808400000000001</v>
+        <v>-10.1892</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.4</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7542</v>
+        <v>0.8312</v>
       </c>
       <c r="J57" t="n">
-        <v>21.1176</v>
+        <v>23.2736</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5047</v>
+        <v>0.5571</v>
       </c>
       <c r="J58" t="n">
-        <v>14.1316</v>
+        <v>15.5988</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>1.1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3171</v>
+        <v>0.3209</v>
       </c>
       <c r="J59" t="n">
-        <v>8.8788</v>
+        <v>8.985200000000001</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>1.09</v>
       </c>
       <c r="I60" t="n">
-        <v>0.29</v>
+        <v>0.2949</v>
       </c>
       <c r="J60" t="n">
-        <v>8.119999999999999</v>
+        <v>8.257199999999999</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5523</v>
+        <v>-0.519</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.4644</v>
+        <v>-14.532</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.66</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0748</v>
+        <v>1.1766</v>
       </c>
       <c r="J62" t="n">
-        <v>26.87</v>
+        <v>29.415</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.28</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5804</v>
+        <v>0.6434</v>
       </c>
       <c r="J63" t="n">
-        <v>14.51</v>
+        <v>16.085</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>1.05</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1567</v>
+        <v>0.1726</v>
       </c>
       <c r="J64" t="n">
-        <v>3.9175</v>
+        <v>4.315</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.98</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1402</v>
+        <v>-0.1317</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.505</v>
+        <v>-3.2925</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2781</v>
+        <v>-0.2646</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.9525</v>
+        <v>-6.615</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.306</v>
+        <v>0.3096</v>
       </c>
       <c r="J67" t="n">
-        <v>7.65</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>1.01</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0377</v>
+        <v>0.0433</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9425</v>
+        <v>1.0825</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>0.96</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0725</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.58</v>
+        <v>-1.8125</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.96</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0725</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.58</v>
+        <v>-1.8125</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.0881</v>
+        <v>-0.099</v>
       </c>
       <c r="J71" t="n">
-        <v>-2.2025</v>
+        <v>-2.475</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.52</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8969</v>
+        <v>0.9875</v>
       </c>
       <c r="J72" t="n">
-        <v>23.3194</v>
+        <v>25.675</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.24</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5244</v>
+        <v>0.5813</v>
       </c>
       <c r="J73" t="n">
-        <v>13.6344</v>
+        <v>15.1138</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4404</v>
+        <v>0.4865</v>
       </c>
       <c r="J74" t="n">
-        <v>11.4504</v>
+        <v>12.649</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0451</v>
+        <v>-0.0311</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.1726</v>
+        <v>-0.8086</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.99</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>-2.6</v>
+        <v>-2.3634</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.15</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3696</v>
+        <v>0.3824</v>
       </c>
       <c r="J77" t="n">
-        <v>9.6096</v>
+        <v>9.942399999999999</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>0.91</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1101</v>
+        <v>-0.1255</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.8626</v>
+        <v>-3.263</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>0.79</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2325</v>
+        <v>-0.2495</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.045</v>
+        <v>-6.487</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.77</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2521</v>
+        <v>-0.2688</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.5546</v>
+        <v>-6.9888</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.71</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3101</v>
+        <v>-0.3254</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.0626</v>
+        <v>-8.4604</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.46</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8126</v>
+        <v>0.8984</v>
       </c>
       <c r="J82" t="n">
-        <v>21.9402</v>
+        <v>24.2568</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.24</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5782</v>
       </c>
       <c r="J83" t="n">
-        <v>14.0589</v>
+        <v>15.6114</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.14</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3774</v>
+        <v>0.4072</v>
       </c>
       <c r="J84" t="n">
-        <v>10.1898</v>
+        <v>10.9944</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>1.12</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3453</v>
+        <v>0.3586</v>
       </c>
       <c r="J85" t="n">
-        <v>9.3231</v>
+        <v>9.6822</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>1.12</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3453</v>
+        <v>0.3586</v>
       </c>
       <c r="J86" t="n">
-        <v>9.3231</v>
+        <v>9.6822</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5632</v>
+        <v>0.6182</v>
       </c>
       <c r="J87" t="n">
-        <v>15.2064</v>
+        <v>16.6914</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0336</v>
+        <v>-0.0456</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.9072</v>
+        <v>-1.2312</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2313</v>
+        <v>-0.2485</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.2451</v>
+        <v>-6.7095</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.6</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4124</v>
+        <v>-0.424</v>
       </c>
       <c r="J90" t="n">
-        <v>-11.1348</v>
+        <v>-11.448</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.6</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4124</v>
+        <v>-0.424</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.1348</v>
+        <v>-11.448</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>1.83</v>
       </c>
       <c r="I92" t="n">
-        <v>1.1859</v>
+        <v>1.3096</v>
       </c>
       <c r="J92" t="n">
-        <v>21.3462</v>
+        <v>23.5728</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>1.7</v>
       </c>
       <c r="I93" t="n">
-        <v>1.0406</v>
+        <v>1.155</v>
       </c>
       <c r="J93" t="n">
-        <v>18.7308</v>
+        <v>20.79</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>1.57</v>
       </c>
       <c r="I94" t="n">
-        <v>0.8949</v>
+        <v>0.998</v>
       </c>
       <c r="J94" t="n">
-        <v>16.1082</v>
+        <v>17.964</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>1.55</v>
       </c>
       <c r="I95" t="n">
-        <v>0.8723</v>
+        <v>0.9735</v>
       </c>
       <c r="J95" t="n">
-        <v>15.7014</v>
+        <v>17.523</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>1.24</v>
       </c>
       <c r="I96" t="n">
-        <v>0.4796</v>
+        <v>0.5425</v>
       </c>
       <c r="J96" t="n">
-        <v>8.6328</v>
+        <v>9.765000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>0.8</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.1699</v>
+        <v>-0.1987</v>
       </c>
       <c r="J97" t="n">
-        <v>-3.0582</v>
+        <v>-3.5766</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>0.75</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2251</v>
+        <v>-0.2519</v>
       </c>
       <c r="J98" t="n">
-        <v>-4.0518</v>
+        <v>-4.5342</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>0.61</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3647</v>
+        <v>-0.3853</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.5646</v>
+        <v>-6.9354</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>0.47</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4925</v>
+        <v>-0.5059</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.865</v>
+        <v>-9.106199999999999</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>0.35</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6072</v>
+        <v>-0.6119</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.9296</v>
+        <v>-11.0142</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.63</v>
       </c>
       <c r="I102" t="n">
-        <v>1.0391</v>
+        <v>1.1385</v>
       </c>
       <c r="J102" t="n">
-        <v>31.173</v>
+        <v>34.155</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>1.3</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6088</v>
+        <v>0.6746</v>
       </c>
       <c r="J103" t="n">
-        <v>18.264</v>
+        <v>20.238</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>1.27</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5676</v>
+        <v>0.629</v>
       </c>
       <c r="J104" t="n">
-        <v>17.028</v>
+        <v>18.87</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.88</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4545</v>
+        <v>-0.4281</v>
       </c>
       <c r="J105" t="n">
-        <v>-13.635</v>
+        <v>-12.843</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.8</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6693</v>
+        <v>-0.6213</v>
       </c>
       <c r="J106" t="n">
-        <v>-20.079</v>
+        <v>-18.639</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>1.2</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4025</v>
+        <v>0.4389</v>
       </c>
       <c r="J107" t="n">
-        <v>12.075</v>
+        <v>13.167</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0435</v>
+        <v>0.0475</v>
       </c>
       <c r="J108" t="n">
-        <v>1.305</v>
+        <v>1.425</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>0.99</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0182</v>
+        <v>-0.0235</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.546</v>
+        <v>-0.705</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>0.83</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2046</v>
+        <v>-0.2191</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.138</v>
+        <v>-6.573</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.8</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.235</v>
+        <v>-0.2493</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.05</v>
+        <v>-7.479</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.33</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4274</v>
+        <v>0.4767</v>
       </c>
       <c r="J112" t="n">
-        <v>14.5316</v>
+        <v>16.2078</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.13</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2218</v>
+        <v>0.2332</v>
       </c>
       <c r="J113" t="n">
-        <v>7.5412</v>
+        <v>7.9288</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.04</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0815</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="J114" t="n">
-        <v>2.771</v>
+        <v>3.1382</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0955</v>
+        <v>-0.1047</v>
       </c>
       <c r="J115" t="n">
-        <v>-3.247</v>
+        <v>-3.5598</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1307</v>
+        <v>-0.1414</v>
       </c>
       <c r="J116" t="n">
-        <v>-4.4438</v>
+        <v>-4.8076</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3603</v>
+        <v>0.388</v>
       </c>
       <c r="J117" t="n">
-        <v>12.2502</v>
+        <v>13.192</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2236</v>
+        <v>0.2374</v>
       </c>
       <c r="J118" t="n">
-        <v>7.6024</v>
+        <v>8.0716</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>1.06</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1094</v>
+        <v>0.1221</v>
       </c>
       <c r="J119" t="n">
-        <v>3.7196</v>
+        <v>4.1514</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0545</v>
+        <v>-0.0616</v>
       </c>
       <c r="J120" t="n">
-        <v>-1.853</v>
+        <v>-2.0944</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.8</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2442</v>
+        <v>-0.2565</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.3028</v>
+        <v>-8.721</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.79</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1868</v>
+        <v>1.3024</v>
       </c>
       <c r="J122" t="n">
-        <v>26.1096</v>
+        <v>28.6528</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.53</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8754</v>
+        <v>0.9711</v>
       </c>
       <c r="J123" t="n">
-        <v>19.2588</v>
+        <v>21.3642</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.4</v>
       </c>
       <c r="I124" t="n">
-        <v>0.7146</v>
+        <v>0.7965</v>
       </c>
       <c r="J124" t="n">
-        <v>15.7212</v>
+        <v>17.523</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>1.15</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3759</v>
+        <v>0.411</v>
       </c>
       <c r="J125" t="n">
-        <v>8.2698</v>
+        <v>9.042</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.85</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5755</v>
+        <v>-0.5301</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.661</v>
+        <v>-11.6622</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.0559</v>
+        <v>-0.0741</v>
       </c>
       <c r="J127" t="n">
-        <v>-1.2298</v>
+        <v>-1.6302</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>0.86</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.15</v>
+        <v>-0.1698</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.3</v>
+        <v>-3.7356</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1608</v>
+        <v>-0.1806</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.5376</v>
+        <v>-3.9732</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2497</v>
+        <v>-0.269</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.4934</v>
+        <v>-5.918</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.43</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5576</v>
+        <v>-0.5625</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.2672</v>
+        <v>-12.375</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.14</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4493</v>
+        <v>0.436</v>
       </c>
       <c r="J132" t="n">
-        <v>13.479</v>
+        <v>13.08</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.14</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4493</v>
+        <v>0.436</v>
       </c>
       <c r="J133" t="n">
-        <v>13.479</v>
+        <v>13.08</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>1.06</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2205</v>
+        <v>0.2246</v>
       </c>
       <c r="J134" t="n">
-        <v>6.615</v>
+        <v>6.738</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>1.01</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0481</v>
+        <v>0.0552</v>
       </c>
       <c r="J135" t="n">
-        <v>1.443</v>
+        <v>1.656</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6046</v>
+        <v>-0.5709</v>
       </c>
       <c r="J136" t="n">
-        <v>-18.138</v>
+        <v>-17.127</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.23</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4695</v>
+        <v>0.4667</v>
       </c>
       <c r="J137" t="n">
-        <v>14.085</v>
+        <v>14.001</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4164</v>
+        <v>0.4175</v>
       </c>
       <c r="J138" t="n">
-        <v>12.492</v>
+        <v>12.525</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.171</v>
+        <v>0.1826</v>
       </c>
       <c r="J139" t="n">
-        <v>5.13</v>
+        <v>5.478</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.95</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0842</v>
+        <v>-0.0925</v>
       </c>
       <c r="J140" t="n">
-        <v>-2.526</v>
+        <v>-2.775</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.95</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.0842</v>
+        <v>-0.0925</v>
       </c>
       <c r="J141" t="n">
-        <v>-2.526</v>
+        <v>-2.775</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.02</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1008</v>
+        <v>0.0985</v>
       </c>
       <c r="J142" t="n">
-        <v>2.2176</v>
+        <v>2.167</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.01</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0709</v>
+        <v>0.0673</v>
       </c>
       <c r="J143" t="n">
-        <v>1.5598</v>
+        <v>1.4806</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>0.92</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.1137</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.1692</v>
+        <v>-2.5014</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>0.86</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1628</v>
+        <v>-0.1796</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.5816</v>
+        <v>-3.9512</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>0.52</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4874</v>
+        <v>-0.4948</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.7228</v>
+        <v>-10.8856</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>1.54</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1632</v>
+        <v>1.1331</v>
       </c>
       <c r="J147" t="n">
-        <v>25.5904</v>
+        <v>24.9282</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>1.47</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0769</v>
+        <v>1.0382</v>
       </c>
       <c r="J148" t="n">
-        <v>23.6918</v>
+        <v>22.8404</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>1.32</v>
       </c>
       <c r="I149" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7745</v>
       </c>
       <c r="J149" t="n">
-        <v>17.864</v>
+        <v>17.039</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>1.25</v>
       </c>
       <c r="I150" t="n">
-        <v>0.6543</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="J150" t="n">
-        <v>14.3946</v>
+        <v>13.9612</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>1.09</v>
       </c>
       <c r="I151" t="n">
-        <v>0.2426</v>
+        <v>0.2619</v>
       </c>
       <c r="J151" t="n">
-        <v>5.3372</v>
+        <v>5.7618</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.1</v>
       </c>
       <c r="I152" t="n">
-        <v>0.362</v>
+        <v>0.3375</v>
       </c>
       <c r="J152" t="n">
-        <v>8.688000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>0.72</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2829</v>
+        <v>-0.3025</v>
       </c>
       <c r="J153" t="n">
-        <v>-6.7896</v>
+        <v>-7.26</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.71</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.292</v>
+        <v>-0.3114</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.008</v>
+        <v>-7.4736</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.7</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3013</v>
+        <v>-0.3204</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.2312</v>
+        <v>-7.6896</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.44</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5438</v>
+        <v>-0.5503</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.0512</v>
+        <v>-13.2072</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.72</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3807</v>
+        <v>1.3649</v>
       </c>
       <c r="J157" t="n">
-        <v>33.1368</v>
+        <v>32.7576</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.61</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2488</v>
+        <v>1.2247</v>
       </c>
       <c r="J158" t="n">
-        <v>29.9712</v>
+        <v>29.3928</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.38</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9379</v>
+        <v>0.8871</v>
       </c>
       <c r="J159" t="n">
-        <v>22.5096</v>
+        <v>21.2904</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.08</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2137</v>
+        <v>0.235</v>
       </c>
       <c r="J160" t="n">
-        <v>5.1288</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.479</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.4464</v>
+        <v>-11.496</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.28</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.5804</v>
       </c>
       <c r="J162" t="n">
-        <v>16.8644</v>
+        <v>16.2512</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.25</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5482</v>
+        <v>0.5311</v>
       </c>
       <c r="J163" t="n">
-        <v>15.3496</v>
+        <v>14.8708</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>0.78</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2529</v>
+        <v>-0.2674</v>
       </c>
       <c r="J164" t="n">
-        <v>-7.0812</v>
+        <v>-7.4872</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>0.74</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2921</v>
+        <v>-0.3058</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.178800000000001</v>
+        <v>-8.5624</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3304</v>
+        <v>-0.3431</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.251200000000001</v>
+        <v>-9.6068</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.42</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0485</v>
+        <v>0.9958</v>
       </c>
       <c r="J167" t="n">
-        <v>29.358</v>
+        <v>27.8824</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1.27</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7375</v>
+        <v>0.701</v>
       </c>
       <c r="J168" t="n">
-        <v>20.65</v>
+        <v>19.628</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>1.21</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5933</v>
+        <v>0.573</v>
       </c>
       <c r="J169" t="n">
-        <v>16.6124</v>
+        <v>16.044</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.97</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1697</v>
+        <v>-0.1629</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.7516</v>
+        <v>-4.5612</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.89</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.42</v>
+        <v>-0.3979</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.76</v>
+        <v>-11.1412</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.14</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3411</v>
+        <v>0.3393</v>
       </c>
       <c r="J172" t="n">
-        <v>9.550800000000001</v>
+        <v>9.500400000000001</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.08</v>
       </c>
       <c r="I173" t="n">
-        <v>0.218</v>
+        <v>0.2219</v>
       </c>
       <c r="J173" t="n">
-        <v>6.104</v>
+        <v>6.2132</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0058</v>
       </c>
       <c r="J174" t="n">
-        <v>0.2296</v>
+        <v>0.1624</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>0.87</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1611</v>
+        <v>-0.1758</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.5108</v>
+        <v>-4.9224</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>0.66</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3682</v>
+        <v>-0.3796</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.3096</v>
+        <v>-10.6288</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.46</v>
       </c>
       <c r="I177" t="n">
-        <v>1.09</v>
+        <v>1.0478</v>
       </c>
       <c r="J177" t="n">
-        <v>30.52</v>
+        <v>29.3384</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.2</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5602</v>
+        <v>0.5452</v>
       </c>
       <c r="J178" t="n">
-        <v>15.6856</v>
+        <v>15.2656</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.19</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5366</v>
+        <v>0.5239</v>
       </c>
       <c r="J179" t="n">
-        <v>15.0248</v>
+        <v>14.6692</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>1.16</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4626</v>
+        <v>0.4568</v>
       </c>
       <c r="J180" t="n">
-        <v>12.9528</v>
+        <v>12.7904</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1036</v>
+        <v>-0.0934</v>
       </c>
       <c r="J181" t="n">
-        <v>-2.9008</v>
+        <v>-2.6152</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.24</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5014</v>
+        <v>0.4934</v>
       </c>
       <c r="J182" t="n">
-        <v>15.042</v>
+        <v>14.802</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>1.04</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1112</v>
+        <v>0.1212</v>
       </c>
       <c r="J183" t="n">
-        <v>3.336</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>1.04</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1112</v>
+        <v>0.1212</v>
       </c>
       <c r="J184" t="n">
-        <v>3.336</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1014</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.739</v>
+        <v>-3.042</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.89</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1486</v>
+        <v>-0.1608</v>
       </c>
       <c r="J186" t="n">
-        <v>-4.458</v>
+        <v>-4.824</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.18</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5393</v>
+        <v>0.5203</v>
       </c>
       <c r="J187" t="n">
-        <v>16.179</v>
+        <v>15.609</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.15</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4614</v>
+        <v>0.4501</v>
       </c>
       <c r="J188" t="n">
-        <v>13.842</v>
+        <v>13.503</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.435</v>
+        <v>0.4261</v>
       </c>
       <c r="J189" t="n">
-        <v>13.05</v>
+        <v>12.783</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>1.05</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1815</v>
+        <v>0.1896</v>
       </c>
       <c r="J190" t="n">
-        <v>5.445</v>
+        <v>5.688</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.87</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4562</v>
+        <v>-0.4351</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.686</v>
+        <v>-13.053</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.63</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0761</v>
+        <v>1.0424</v>
       </c>
       <c r="J192" t="n">
-        <v>30.1308</v>
+        <v>29.1872</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>1.22</v>
       </c>
       <c r="I193" t="n">
-        <v>0.456</v>
+        <v>0.4535</v>
       </c>
       <c r="J193" t="n">
-        <v>12.768</v>
+        <v>12.698</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>0.92</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1186</v>
+        <v>-0.129</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.3208</v>
+        <v>-3.612</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.79</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2562</v>
+        <v>-0.2679</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.1736</v>
+        <v>-7.5012</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.76</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2857</v>
+        <v>-0.297</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.9996</v>
+        <v>-8.316000000000001</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.42</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0658</v>
+        <v>1.013</v>
       </c>
       <c r="J197" t="n">
-        <v>29.8424</v>
+        <v>28.364</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.38</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0049</v>
+        <v>0.9415</v>
       </c>
       <c r="J198" t="n">
-        <v>28.1372</v>
+        <v>26.362</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.07</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2402</v>
+        <v>0.2461</v>
       </c>
       <c r="J199" t="n">
-        <v>6.7256</v>
+        <v>6.8908</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>0.84</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5415</v>
+        <v>-0.5114</v>
       </c>
       <c r="J200" t="n">
-        <v>-15.162</v>
+        <v>-14.3192</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>0.74</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7996</v>
+        <v>-0.7402</v>
       </c>
       <c r="J201" t="n">
-        <v>-22.3888</v>
+        <v>-20.7256</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>1.09</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3793</v>
+        <v>0.3458</v>
       </c>
       <c r="J202" t="n">
-        <v>7.586</v>
+        <v>6.916</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>0.62</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.3673</v>
+        <v>-0.3856</v>
       </c>
       <c r="J203" t="n">
-        <v>-7.346</v>
+        <v>-7.712</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>0.58</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.4046</v>
+        <v>-0.4209</v>
       </c>
       <c r="J204" t="n">
-        <v>-8.092000000000001</v>
+        <v>-8.417999999999999</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4232</v>
+        <v>-0.4386</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.464</v>
+        <v>-8.772</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.55</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4326</v>
+        <v>-0.4474</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.651999999999999</v>
+        <v>-8.948</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>2.12</v>
       </c>
       <c r="I207" t="n">
-        <v>1.8041</v>
+        <v>1.8139</v>
       </c>
       <c r="J207" t="n">
-        <v>36.082</v>
+        <v>36.278</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>1.71</v>
       </c>
       <c r="I208" t="n">
-        <v>1.342</v>
+        <v>1.3287</v>
       </c>
       <c r="J208" t="n">
-        <v>26.84</v>
+        <v>26.574</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>1.57</v>
       </c>
       <c r="I209" t="n">
-        <v>1.1789</v>
+        <v>1.1541</v>
       </c>
       <c r="J209" t="n">
-        <v>23.578</v>
+        <v>23.082</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1631</v>
+        <v>-0.1352</v>
       </c>
       <c r="J210" t="n">
-        <v>-3.262</v>
+        <v>-2.704</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3413</v>
+        <v>-0.309</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.826</v>
+        <v>-6.18</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.95</v>
       </c>
       <c r="I212" t="n">
-        <v>1.6037</v>
+        <v>1.6068</v>
       </c>
       <c r="J212" t="n">
-        <v>33.6777</v>
+        <v>33.7428</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.68</v>
       </c>
       <c r="I213" t="n">
-        <v>1.2994</v>
+        <v>1.2849</v>
       </c>
       <c r="J213" t="n">
-        <v>27.2874</v>
+        <v>26.9829</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>1.38</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9093</v>
+        <v>0.8665</v>
       </c>
       <c r="J214" t="n">
-        <v>19.0953</v>
+        <v>18.1965</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>1.36</v>
       </c>
       <c r="I215" t="n">
-        <v>0.8663</v>
+        <v>0.8285</v>
       </c>
       <c r="J215" t="n">
-        <v>18.1923</v>
+        <v>17.3985</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>1.22</v>
       </c>
       <c r="I216" t="n">
-        <v>0.5447</v>
+        <v>0.5444</v>
       </c>
       <c r="J216" t="n">
-        <v>11.4387</v>
+        <v>11.4324</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>0.73</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.2364</v>
+        <v>-0.2645</v>
       </c>
       <c r="J217" t="n">
-        <v>-4.9644</v>
+        <v>-5.5545</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>0.55</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.4125</v>
+        <v>-0.4318</v>
       </c>
       <c r="J218" t="n">
-        <v>-8.6625</v>
+        <v>-9.0678</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>0.55</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4125</v>
+        <v>-0.4318</v>
       </c>
       <c r="J219" t="n">
-        <v>-8.6625</v>
+        <v>-9.0678</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>0.52</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4397</v>
+        <v>-0.4575</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.233700000000001</v>
+        <v>-9.6075</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.48</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.477</v>
+        <v>-0.4924</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.017</v>
+        <v>-10.3404</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.3</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7882</v>
+        <v>0.7493</v>
       </c>
       <c r="J222" t="n">
-        <v>22.8578</v>
+        <v>21.7297</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.25</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6733</v>
+        <v>0.6475</v>
       </c>
       <c r="J223" t="n">
-        <v>19.5257</v>
+        <v>18.7775</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.23</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6271</v>
+        <v>0.6062</v>
       </c>
       <c r="J224" t="n">
-        <v>18.1859</v>
+        <v>17.5798</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.17</v>
       </c>
       <c r="I225" t="n">
-        <v>0.4838</v>
+        <v>0.4769</v>
       </c>
       <c r="J225" t="n">
-        <v>14.0302</v>
+        <v>13.8301</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>1.15</v>
       </c>
       <c r="I226" t="n">
-        <v>0.4328</v>
+        <v>0.4307</v>
       </c>
       <c r="J226" t="n">
-        <v>12.5512</v>
+        <v>12.4903</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.14</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3732</v>
+        <v>0.3629</v>
       </c>
       <c r="J227" t="n">
-        <v>10.8228</v>
+        <v>10.5241</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>0.89</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1323</v>
+        <v>-0.1483</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.8367</v>
+        <v>-4.3007</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>0.85</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1729</v>
+        <v>-0.1899</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.0141</v>
+        <v>-5.5071</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.82</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.203</v>
+        <v>-0.2201</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.887</v>
+        <v>-6.3829</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.64</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3767</v>
+        <v>-0.3895</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.9243</v>
+        <v>-11.2955</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.91</v>
       </c>
       <c r="I232" t="n">
-        <v>1.623</v>
+        <v>1.6166</v>
       </c>
       <c r="J232" t="n">
-        <v>37.329</v>
+        <v>37.1818</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>1.47</v>
       </c>
       <c r="I233" t="n">
-        <v>1.088</v>
+        <v>1.0487</v>
       </c>
       <c r="J233" t="n">
-        <v>25.024</v>
+        <v>24.1201</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>1.15</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4217</v>
+        <v>0.423</v>
       </c>
       <c r="J234" t="n">
-        <v>9.6991</v>
+        <v>9.728999999999999</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.97</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1991</v>
+        <v>-0.1835</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.5793</v>
+        <v>-4.2205</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5596</v>
+        <v>-0.5188</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.8708</v>
+        <v>-11.9324</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.06</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2184</v>
+        <v>0.2115</v>
       </c>
       <c r="J237" t="n">
-        <v>5.0232</v>
+        <v>4.8645</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.01</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0859</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="J238" t="n">
-        <v>1.9757</v>
+        <v>1.8009</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>0.82</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1986</v>
+        <v>-0.2168</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.5678</v>
+        <v>-4.9864</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3237</v>
+        <v>-0.3396</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.4451</v>
+        <v>-7.8108</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.55</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4548</v>
+        <v>-0.4648</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.4604</v>
+        <v>-10.6904</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.17</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3697</v>
+        <v>0.3722</v>
       </c>
       <c r="J242" t="n">
-        <v>13.3092</v>
+        <v>13.3992</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>1.15</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3325</v>
+        <v>0.3371</v>
       </c>
       <c r="J243" t="n">
-        <v>11.97</v>
+        <v>12.1356</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>1.15</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3325</v>
+        <v>0.3371</v>
       </c>
       <c r="J244" t="n">
-        <v>11.97</v>
+        <v>12.1356</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>1.04</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1095</v>
+        <v>0.12</v>
       </c>
       <c r="J245" t="n">
-        <v>3.942</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.73</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3129</v>
+        <v>-0.324</v>
       </c>
       <c r="J246" t="n">
-        <v>-11.2644</v>
+        <v>-11.664</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.3</v>
       </c>
       <c r="I247" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.7827</v>
       </c>
       <c r="J247" t="n">
-        <v>30.1032</v>
+        <v>28.1772</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.27</v>
       </c>
       <c r="I248" t="n">
-        <v>0.7637</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="J248" t="n">
-        <v>27.4932</v>
+        <v>25.8948</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.06</v>
       </c>
       <c r="I249" t="n">
-        <v>0.2126</v>
+        <v>0.2193</v>
       </c>
       <c r="J249" t="n">
-        <v>7.6536</v>
+        <v>7.8948</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>0.95</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2182</v>
+        <v>-0.2148</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.8552</v>
+        <v>-7.7328</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6177</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="J251" t="n">
-        <v>-22.2372</v>
+        <v>-20.8836</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.49</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1443</v>
+        <v>1.1043</v>
       </c>
       <c r="J252" t="n">
-        <v>32.0404</v>
+        <v>30.9204</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.38</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9879</v>
+        <v>0.9266</v>
       </c>
       <c r="J253" t="n">
-        <v>27.6612</v>
+        <v>25.9448</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>1.37</v>
       </c>
       <c r="I254" t="n">
-        <v>0.9689</v>
+        <v>0.9072</v>
       </c>
       <c r="J254" t="n">
-        <v>27.1292</v>
+        <v>25.4016</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>0.83</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5816</v>
+        <v>-0.5448</v>
       </c>
       <c r="J255" t="n">
-        <v>-16.2848</v>
+        <v>-15.2544</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.63</v>
       </c>
       <c r="I256" t="n">
-        <v>-1.0786</v>
+        <v>-0.9806</v>
       </c>
       <c r="J256" t="n">
-        <v>-30.2008</v>
+        <v>-27.4568</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.14</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3488</v>
+        <v>0.3449</v>
       </c>
       <c r="J257" t="n">
-        <v>9.766400000000001</v>
+        <v>9.6572</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>1.09</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2462</v>
+        <v>0.2475</v>
       </c>
       <c r="J258" t="n">
-        <v>6.8936</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>0.91</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1156</v>
+        <v>-0.1297</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.2368</v>
+        <v>-3.6316</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>0.82</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2102</v>
+        <v>-0.2257</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.8856</v>
+        <v>-6.3196</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.68</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3467</v>
+        <v>-0.3593</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.707599999999999</v>
+        <v>-10.0604</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.54</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2174</v>
+        <v>1.1809</v>
       </c>
       <c r="J262" t="n">
-        <v>30.435</v>
+        <v>29.5225</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.27</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7501</v>
+        <v>0.7098</v>
       </c>
       <c r="J263" t="n">
-        <v>18.7525</v>
+        <v>17.745</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>0.99</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0814</v>
+        <v>-0.0779</v>
       </c>
       <c r="J264" t="n">
-        <v>-2.035</v>
+        <v>-1.9475</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>0.92</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3219</v>
+        <v>-0.3098</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.047499999999999</v>
+        <v>-7.745</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>0.85</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.521</v>
+        <v>-0.4917</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.025</v>
+        <v>-12.2925</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.25</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5585</v>
+        <v>0.5387</v>
       </c>
       <c r="J267" t="n">
-        <v>13.9625</v>
+        <v>13.4675</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>1.11</v>
       </c>
       <c r="I268" t="n">
-        <v>0.2888</v>
+        <v>0.2881</v>
       </c>
       <c r="J268" t="n">
-        <v>7.22</v>
+        <v>7.2025</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.97</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0439</v>
+        <v>-0.0535</v>
       </c>
       <c r="J269" t="n">
-        <v>-1.0975</v>
+        <v>-1.3375</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.337</v>
+        <v>-0.35</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.425000000000001</v>
+        <v>-8.75</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.61</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4119</v>
+        <v>-0.422</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.2975</v>
+        <v>-10.55</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.34</v>
       </c>
       <c r="I272" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.8413</v>
       </c>
       <c r="J272" t="n">
-        <v>22.4175</v>
+        <v>21.0325</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.24</v>
       </c>
       <c r="I273" t="n">
-        <v>0.6626</v>
+        <v>0.6354</v>
       </c>
       <c r="J273" t="n">
-        <v>16.565</v>
+        <v>15.885</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>1.22</v>
       </c>
       <c r="I274" t="n">
-        <v>0.6146</v>
+        <v>0.5927</v>
       </c>
       <c r="J274" t="n">
-        <v>15.365</v>
+        <v>14.8175</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>1.18</v>
       </c>
       <c r="I275" t="n">
-        <v>0.5174</v>
+        <v>0.5053</v>
       </c>
       <c r="J275" t="n">
-        <v>12.935</v>
+        <v>12.6325</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.84</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5611</v>
+        <v>-0.5252</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.0275</v>
+        <v>-13.13</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.11</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3237</v>
+        <v>0.3137</v>
       </c>
       <c r="J277" t="n">
-        <v>8.092499999999999</v>
+        <v>7.8425</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>0.93</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0828</v>
+        <v>-0.0984</v>
       </c>
       <c r="J278" t="n">
-        <v>-2.07</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>0.92</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0948</v>
+        <v>-0.1107</v>
       </c>
       <c r="J279" t="n">
-        <v>-2.37</v>
+        <v>-2.7675</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>0.63</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3823</v>
+        <v>-0.3956</v>
       </c>
       <c r="J280" t="n">
-        <v>-9.557499999999999</v>
+        <v>-9.890000000000001</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.61</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.401</v>
+        <v>-0.4134</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.025</v>
+        <v>-10.335</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.2</v>
       </c>
       <c r="I282" t="n">
-        <v>0.4325</v>
+        <v>0.4292</v>
       </c>
       <c r="J282" t="n">
-        <v>10.38</v>
+        <v>10.3008</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.07</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1794</v>
+        <v>0.1886</v>
       </c>
       <c r="J283" t="n">
-        <v>4.3056</v>
+        <v>4.5264</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>1.04</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1126</v>
+        <v>0.1222</v>
       </c>
       <c r="J284" t="n">
-        <v>2.7024</v>
+        <v>2.9328</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.92</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1138</v>
+        <v>-0.1253</v>
       </c>
       <c r="J285" t="n">
-        <v>-2.7312</v>
+        <v>-3.0072</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.87</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.1691</v>
+        <v>-0.182</v>
       </c>
       <c r="J286" t="n">
-        <v>-4.0584</v>
+        <v>-4.368</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.25</v>
       </c>
       <c r="I287" t="n">
-        <v>0.7103</v>
+        <v>0.6731</v>
       </c>
       <c r="J287" t="n">
-        <v>17.0472</v>
+        <v>16.1544</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.14</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4318</v>
+        <v>0.424</v>
       </c>
       <c r="J288" t="n">
-        <v>10.3632</v>
+        <v>10.176</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>1.09</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2971</v>
+        <v>0.2997</v>
       </c>
       <c r="J289" t="n">
-        <v>7.1304</v>
+        <v>7.1928</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>1.03</v>
       </c>
       <c r="I290" t="n">
-        <v>0.1119</v>
+        <v>0.1232</v>
       </c>
       <c r="J290" t="n">
-        <v>2.6856</v>
+        <v>2.9568</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2537</v>
+        <v>-0.2475</v>
       </c>
       <c r="J291" t="n">
-        <v>-6.0888</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.43</v>
       </c>
       <c r="I292" t="n">
-        <v>0.944</v>
+        <v>0.8766</v>
       </c>
       <c r="J292" t="n">
-        <v>5.664</v>
+        <v>5.2596</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.04</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1722</v>
+        <v>0.1655</v>
       </c>
       <c r="J293" t="n">
-        <v>1.0332</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>0.59</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.4169</v>
+        <v>-0.429</v>
       </c>
       <c r="J294" t="n">
-        <v>-2.5014</v>
+        <v>-2.574</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.57</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4355</v>
+        <v>-0.4467</v>
       </c>
       <c r="J295" t="n">
-        <v>-2.613</v>
+        <v>-2.6802</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.47</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5275</v>
+        <v>-0.5334</v>
       </c>
       <c r="J296" t="n">
-        <v>-3.165</v>
+        <v>-3.2004</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.83</v>
       </c>
       <c r="I297" t="n">
-        <v>1.5023</v>
+        <v>1.4945</v>
       </c>
       <c r="J297" t="n">
-        <v>9.0138</v>
+        <v>8.967000000000001</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.61</v>
       </c>
       <c r="I298" t="n">
-        <v>1.2425</v>
+        <v>1.2192</v>
       </c>
       <c r="J298" t="n">
-        <v>7.455</v>
+        <v>7.3152</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>1.45</v>
       </c>
       <c r="I299" t="n">
-        <v>1.0471</v>
+        <v>1.0039</v>
       </c>
       <c r="J299" t="n">
-        <v>6.2826</v>
+        <v>6.0234</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>1.29</v>
       </c>
       <c r="I300" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="J300" t="n">
-        <v>4.4424</v>
+        <v>4.2732</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.64</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.0981</v>
+        <v>-0.9908</v>
       </c>
       <c r="J301" t="n">
-        <v>-6.5886</v>
+        <v>-5.9448</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.71</v>
       </c>
       <c r="I302" t="n">
-        <v>1.3905</v>
+        <v>1.3715</v>
       </c>
       <c r="J302" t="n">
-        <v>23.6385</v>
+        <v>23.3155</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.4</v>
       </c>
       <c r="I303" t="n">
-        <v>0.9932</v>
+        <v>0.9384</v>
       </c>
       <c r="J303" t="n">
-        <v>16.8844</v>
+        <v>15.9528</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>1.38</v>
       </c>
       <c r="I304" t="n">
-        <v>0.9564</v>
+        <v>0.901</v>
       </c>
       <c r="J304" t="n">
-        <v>16.2588</v>
+        <v>15.317</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.88</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4721</v>
+        <v>-0.4405</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.025700000000001</v>
+        <v>-7.4885</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.87</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4999</v>
+        <v>-0.4658</v>
       </c>
       <c r="J306" t="n">
-        <v>-8.4983</v>
+        <v>-7.9186</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.09</v>
       </c>
       <c r="I307" t="n">
-        <v>0.253</v>
+        <v>0.2525</v>
       </c>
       <c r="J307" t="n">
-        <v>4.301</v>
+        <v>4.2925</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>1.08</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2314</v>
+        <v>0.2317</v>
       </c>
       <c r="J308" t="n">
-        <v>3.9338</v>
+        <v>3.9389</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>0.99</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0112</v>
+        <v>-0.0181</v>
       </c>
       <c r="J309" t="n">
-        <v>-0.1904</v>
+        <v>-0.3077</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>0.82</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2078</v>
+        <v>-0.2238</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.5326</v>
+        <v>-3.8046</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4557</v>
+        <v>-0.4641</v>
       </c>
       <c r="J311" t="n">
-        <v>-7.7469</v>
+        <v>-7.8897</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.03</v>
       </c>
       <c r="I312" t="n">
-        <v>0.1614</v>
+        <v>0.1571</v>
       </c>
       <c r="J312" t="n">
-        <v>4.842</v>
+        <v>4.713</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>0.95</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1764</v>
+        <v>-0.1862</v>
       </c>
       <c r="J313" t="n">
-        <v>-5.292</v>
+        <v>-5.586</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2083</v>
+        <v>-0.2163</v>
       </c>
       <c r="J314" t="n">
-        <v>-6.249</v>
+        <v>-6.489</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.86</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.4337</v>
+        <v>-0.4253</v>
       </c>
       <c r="J315" t="n">
-        <v>-13.011</v>
+        <v>-12.759</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.76</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6947</v>
+        <v>-0.6577</v>
       </c>
       <c r="J316" t="n">
-        <v>-20.841</v>
+        <v>-19.731</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.49</v>
       </c>
       <c r="I317" t="n">
-        <v>0.8848</v>
+        <v>0.8455</v>
       </c>
       <c r="J317" t="n">
-        <v>26.544</v>
+        <v>25.365</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.27</v>
       </c>
       <c r="I318" t="n">
-        <v>0.5273</v>
+        <v>0.5222</v>
       </c>
       <c r="J318" t="n">
-        <v>15.819</v>
+        <v>15.666</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>1.11</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2447</v>
+        <v>0.2562</v>
       </c>
       <c r="J319" t="n">
-        <v>7.341</v>
+        <v>7.686</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>1.02</v>
       </c>
       <c r="I320" t="n">
-        <v>0.047</v>
+        <v>0.0598</v>
       </c>
       <c r="J320" t="n">
-        <v>1.41</v>
+        <v>1.794</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.73</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3206</v>
+        <v>-0.3301</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.618</v>
+        <v>-9.903</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.27</v>
       </c>
       <c r="I322" t="n">
-        <v>0.5453</v>
+        <v>0.5354</v>
       </c>
       <c r="J322" t="n">
-        <v>15.8137</v>
+        <v>15.5266</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.1</v>
       </c>
       <c r="I323" t="n">
-        <v>0.234</v>
+        <v>0.2435</v>
       </c>
       <c r="J323" t="n">
-        <v>6.786</v>
+        <v>7.0615</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.08</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1937</v>
+        <v>0.2044</v>
       </c>
       <c r="J324" t="n">
-        <v>5.6173</v>
+        <v>5.9276</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>1.02</v>
       </c>
       <c r="I325" t="n">
-        <v>0.0585</v>
+        <v>0.068</v>
       </c>
       <c r="J325" t="n">
-        <v>1.6965</v>
+        <v>1.972</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.82</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2254</v>
+        <v>-0.2375</v>
       </c>
       <c r="J326" t="n">
-        <v>-6.5366</v>
+        <v>-6.8875</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.32</v>
       </c>
       <c r="I327" t="n">
-        <v>0.8875</v>
+        <v>0.8268</v>
       </c>
       <c r="J327" t="n">
-        <v>25.7375</v>
+        <v>23.9772</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>1.21</v>
       </c>
       <c r="I328" t="n">
-        <v>0.6183</v>
+        <v>0.5903</v>
       </c>
       <c r="J328" t="n">
-        <v>17.9307</v>
+        <v>17.1187</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>1</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0152</v>
+        <v>-0.0104</v>
       </c>
       <c r="J329" t="n">
-        <v>-0.4408</v>
+        <v>-0.3016</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>0.93</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2794</v>
+        <v>-0.273</v>
       </c>
       <c r="J330" t="n">
-        <v>-8.102600000000001</v>
+        <v>-7.917</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.89</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3976</v>
+        <v>-0.3823</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.5304</v>
+        <v>-11.0867</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>1.27</v>
       </c>
       <c r="I332" t="n">
-        <v>0.6515</v>
+        <v>0.6138</v>
       </c>
       <c r="J332" t="n">
-        <v>15.636</v>
+        <v>14.7312</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>0.9</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.115</v>
+        <v>-0.1322</v>
       </c>
       <c r="J333" t="n">
-        <v>-2.76</v>
+        <v>-3.1728</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>0.85</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.1689</v>
+        <v>-0.1869</v>
       </c>
       <c r="J334" t="n">
-        <v>-4.0536</v>
+        <v>-4.4856</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.66</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3516</v>
+        <v>-0.3665</v>
       </c>
       <c r="J335" t="n">
-        <v>-8.4384</v>
+        <v>-8.795999999999999</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.43</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5641</v>
+        <v>-0.5677</v>
       </c>
       <c r="J336" t="n">
-        <v>-13.5384</v>
+        <v>-13.6248</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.67</v>
       </c>
       <c r="I337" t="n">
-        <v>1.338</v>
+        <v>1.3166</v>
       </c>
       <c r="J337" t="n">
-        <v>32.112</v>
+        <v>31.5984</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.45</v>
       </c>
       <c r="I338" t="n">
-        <v>1.0641</v>
+        <v>1.0202</v>
       </c>
       <c r="J338" t="n">
-        <v>25.5384</v>
+        <v>24.4848</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>1.33</v>
       </c>
       <c r="I339" t="n">
-        <v>0.8457</v>
+        <v>0.8018</v>
       </c>
       <c r="J339" t="n">
-        <v>20.2968</v>
+        <v>19.2432</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>1.03</v>
       </c>
       <c r="I340" t="n">
-        <v>0.0693</v>
+        <v>0.0936</v>
       </c>
       <c r="J340" t="n">
-        <v>1.6632</v>
+        <v>2.2464</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>0.83</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6111</v>
+        <v>-0.5655</v>
       </c>
       <c r="J341" t="n">
-        <v>-14.6664</v>
+        <v>-13.572</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.3</v>
       </c>
       <c r="I342" t="n">
-        <v>0.5961</v>
+        <v>0.582</v>
       </c>
       <c r="J342" t="n">
-        <v>16.6908</v>
+        <v>16.296</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.14</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3109</v>
+        <v>0.3173</v>
       </c>
       <c r="J343" t="n">
-        <v>8.7052</v>
+        <v>8.884399999999999</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>1.12</v>
       </c>
       <c r="I344" t="n">
-        <v>0.2727</v>
+        <v>0.2809</v>
       </c>
       <c r="J344" t="n">
-        <v>7.6356</v>
+        <v>7.8652</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>0.96</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.0693</v>
+        <v>-0.0772</v>
       </c>
       <c r="J345" t="n">
-        <v>-1.9404</v>
+        <v>-2.1616</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.78</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2656</v>
+        <v>-0.2774</v>
       </c>
       <c r="J346" t="n">
-        <v>-7.4368</v>
+        <v>-7.7672</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.26</v>
       </c>
       <c r="I347" t="n">
-        <v>0.7417</v>
+        <v>0.6995</v>
       </c>
       <c r="J347" t="n">
-        <v>20.7676</v>
+        <v>19.586</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>1.19</v>
       </c>
       <c r="I348" t="n">
-        <v>0.5669</v>
+        <v>0.5446</v>
       </c>
       <c r="J348" t="n">
-        <v>15.8732</v>
+        <v>15.2488</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>1.09</v>
       </c>
       <c r="I349" t="n">
-        <v>0.3</v>
+        <v>0.3015</v>
       </c>
       <c r="J349" t="n">
-        <v>8.4</v>
+        <v>8.442</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2487</v>
+        <v>-0.2441</v>
       </c>
       <c r="J350" t="n">
-        <v>-6.9636</v>
+        <v>-6.8348</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.88</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4266</v>
+        <v>-0.4085</v>
       </c>
       <c r="J351" t="n">
-        <v>-11.9448</v>
+        <v>-11.438</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.3</v>
       </c>
       <c r="I352" t="n">
-        <v>0.6218</v>
+        <v>0.6008</v>
       </c>
       <c r="J352" t="n">
-        <v>18.654</v>
+        <v>18.024</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.08</v>
       </c>
       <c r="I353" t="n">
-        <v>0.2078</v>
+        <v>0.2145</v>
       </c>
       <c r="J353" t="n">
-        <v>6.234</v>
+        <v>6.435</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>0.95</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.0747</v>
+        <v>-0.0852</v>
       </c>
       <c r="J354" t="n">
-        <v>-2.241</v>
+        <v>-2.556</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.2276</v>
+        <v>-0.2414</v>
       </c>
       <c r="J355" t="n">
-        <v>-6.828</v>
+        <v>-7.242</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.8</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.2376</v>
+        <v>-0.2513</v>
       </c>
       <c r="J356" t="n">
-        <v>-7.128</v>
+        <v>-7.539</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.52</v>
       </c>
       <c r="I357" t="n">
-        <v>1.1691</v>
+        <v>1.1334</v>
       </c>
       <c r="J357" t="n">
-        <v>35.073</v>
+        <v>34.002</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.41</v>
       </c>
       <c r="I358" t="n">
-        <v>1.0234</v>
+        <v>0.9687</v>
       </c>
       <c r="J358" t="n">
-        <v>30.702</v>
+        <v>29.061</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>1.12</v>
       </c>
       <c r="I359" t="n">
-        <v>0.3596</v>
+        <v>0.3624</v>
       </c>
       <c r="J359" t="n">
-        <v>10.788</v>
+        <v>10.872</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>1.12</v>
       </c>
       <c r="I360" t="n">
-        <v>0.3596</v>
+        <v>0.3624</v>
       </c>
       <c r="J360" t="n">
-        <v>10.788</v>
+        <v>10.872</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.79</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.6989</v>
+        <v>-0.6469</v>
       </c>
       <c r="J361" t="n">
-        <v>-20.967</v>
+        <v>-19.407</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.21</v>
       </c>
       <c r="I362" t="n">
-        <v>0.602</v>
+        <v>0.579</v>
       </c>
       <c r="J362" t="n">
-        <v>21.672</v>
+        <v>20.844</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>1.16</v>
       </c>
       <c r="I363" t="n">
-        <v>0.4764</v>
+        <v>0.4661</v>
       </c>
       <c r="J363" t="n">
-        <v>17.1504</v>
+        <v>16.7796</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>1.1</v>
       </c>
       <c r="I364" t="n">
-        <v>0.32</v>
+        <v>0.3223</v>
       </c>
       <c r="J364" t="n">
-        <v>11.52</v>
+        <v>11.6028</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>1.09</v>
       </c>
       <c r="I365" t="n">
-        <v>0.2921</v>
+        <v>0.2963</v>
       </c>
       <c r="J365" t="n">
-        <v>10.5156</v>
+        <v>10.6668</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>1.04</v>
       </c>
       <c r="I366" t="n">
-        <v>0.1391</v>
+        <v>0.1516</v>
       </c>
       <c r="J366" t="n">
-        <v>5.0076</v>
+        <v>5.4576</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.01</v>
       </c>
       <c r="I367" t="n">
-        <v>0.0606</v>
+        <v>0.0598</v>
       </c>
       <c r="J367" t="n">
-        <v>2.1816</v>
+        <v>2.1528</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>0.97</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.0402</v>
+        <v>-0.0508</v>
       </c>
       <c r="J368" t="n">
-        <v>-1.4472</v>
+        <v>-1.8288</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>0.9</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.1242</v>
+        <v>-0.1393</v>
       </c>
       <c r="J369" t="n">
-        <v>-4.4712</v>
+        <v>-5.0148</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>0.85</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.1761</v>
+        <v>-0.1923</v>
       </c>
       <c r="J370" t="n">
-        <v>-6.3396</v>
+        <v>-6.9228</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.76</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.2661</v>
+        <v>-0.2816</v>
       </c>
       <c r="J371" t="n">
-        <v>-9.579599999999999</v>
+        <v>-10.1376</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>0.93</v>
       </c>
       <c r="I372" t="n">
-        <v>-0.0437</v>
+        <v>-0.0677</v>
       </c>
       <c r="J372" t="n">
-        <v>-0.9614</v>
+        <v>-1.4894</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>0.91</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.0693</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="J373" t="n">
-        <v>-1.5246</v>
+        <v>-2.0614</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>0.59</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.3952</v>
+        <v>-0.4121</v>
       </c>
       <c r="J374" t="n">
-        <v>-8.6944</v>
+        <v>-9.0662</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>0.59</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.3952</v>
+        <v>-0.4121</v>
       </c>
       <c r="J375" t="n">
-        <v>-8.6944</v>
+        <v>-9.0662</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>0.38</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.592</v>
+        <v>-0.5961</v>
       </c>
       <c r="J376" t="n">
-        <v>-13.024</v>
+        <v>-13.1142</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.69</v>
       </c>
       <c r="I377" t="n">
-        <v>1.3363</v>
+        <v>1.3194</v>
       </c>
       <c r="J377" t="n">
-        <v>29.3986</v>
+        <v>29.0268</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>1.4</v>
       </c>
       <c r="I378" t="n">
-        <v>0.9692</v>
+        <v>0.9188</v>
       </c>
       <c r="J378" t="n">
-        <v>21.3224</v>
+        <v>20.2136</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>1.34</v>
       </c>
       <c r="I379" t="n">
-        <v>0.8495</v>
+        <v>0.8087</v>
       </c>
       <c r="J379" t="n">
-        <v>18.689</v>
+        <v>17.7914</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>1.3</v>
       </c>
       <c r="I380" t="n">
-        <v>0.7614</v>
+        <v>0.731</v>
       </c>
       <c r="J380" t="n">
-        <v>16.7508</v>
+        <v>16.082</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>1.13</v>
       </c>
       <c r="I381" t="n">
-        <v>0.3457</v>
+        <v>0.3587</v>
       </c>
       <c r="J381" t="n">
-        <v>7.6054</v>
+        <v>7.8914</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.22</v>
       </c>
       <c r="I382" t="n">
-        <v>0.4865</v>
+        <v>0.4758</v>
       </c>
       <c r="J382" t="n">
-        <v>13.622</v>
+        <v>13.3224</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.18</v>
       </c>
       <c r="I383" t="n">
-        <v>0.4121</v>
+        <v>0.4069</v>
       </c>
       <c r="J383" t="n">
-        <v>11.5388</v>
+        <v>11.3932</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.05</v>
       </c>
       <c r="I384" t="n">
-        <v>0.1464</v>
+        <v>0.153</v>
       </c>
       <c r="J384" t="n">
-        <v>4.0992</v>
+        <v>4.284</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>0.85</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.1842</v>
+        <v>-0.1986</v>
       </c>
       <c r="J385" t="n">
-        <v>-5.1576</v>
+        <v>-5.5608</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>0.54</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.4804</v>
+        <v>-0.4865</v>
       </c>
       <c r="J386" t="n">
-        <v>-13.4512</v>
+        <v>-13.622</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.27</v>
       </c>
       <c r="I387" t="n">
-        <v>0.7559</v>
+        <v>0.7138</v>
       </c>
       <c r="J387" t="n">
-        <v>21.1652</v>
+        <v>19.9864</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>1.14</v>
       </c>
       <c r="I388" t="n">
-        <v>0.4298</v>
+        <v>0.4226</v>
       </c>
       <c r="J388" t="n">
-        <v>12.0344</v>
+        <v>11.8328</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>1.07</v>
       </c>
       <c r="I389" t="n">
-        <v>0.2387</v>
+        <v>0.245</v>
       </c>
       <c r="J389" t="n">
-        <v>6.6836</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>1.04</v>
       </c>
       <c r="I390" t="n">
-        <v>0.1444</v>
+        <v>0.1552</v>
       </c>
       <c r="J390" t="n">
-        <v>4.0432</v>
+        <v>4.3456</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.97</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.1554</v>
+        <v>-0.1529</v>
       </c>
       <c r="J391" t="n">
-        <v>-4.3512</v>
+        <v>-4.2812</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>1.27</v>
       </c>
       <c r="I392" t="n">
-        <v>0.6528</v>
+        <v>0.6148</v>
       </c>
       <c r="J392" t="n">
-        <v>16.9728</v>
+        <v>15.9848</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>0.85</v>
       </c>
       <c r="I393" t="n">
-        <v>-0.1687</v>
+        <v>-0.1867</v>
       </c>
       <c r="J393" t="n">
-        <v>-4.3862</v>
+        <v>-4.8542</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>0.77</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.2462</v>
+        <v>-0.2643</v>
       </c>
       <c r="J394" t="n">
-        <v>-6.4012</v>
+        <v>-6.8718</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.68</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.3324</v>
+        <v>-0.3481</v>
       </c>
       <c r="J395" t="n">
-        <v>-8.6424</v>
+        <v>-9.050599999999999</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.53</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.4724</v>
+        <v>-0.4816</v>
       </c>
       <c r="J396" t="n">
-        <v>-12.2824</v>
+        <v>-12.5216</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>1.41</v>
       </c>
       <c r="I397" t="n">
-        <v>1.0145</v>
+        <v>0.9606</v>
       </c>
       <c r="J397" t="n">
-        <v>26.377</v>
+        <v>24.9756</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.32</v>
       </c>
       <c r="I398" t="n">
-        <v>0.8316</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="J398" t="n">
-        <v>21.6216</v>
+        <v>20.4828</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>1.29</v>
       </c>
       <c r="I399" t="n">
-        <v>0.7635</v>
+        <v>0.7279</v>
       </c>
       <c r="J399" t="n">
-        <v>19.851</v>
+        <v>18.9254</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>1.13</v>
       </c>
       <c r="I400" t="n">
-        <v>0.3784</v>
+        <v>0.3815</v>
       </c>
       <c r="J400" t="n">
-        <v>9.8384</v>
+        <v>9.919</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>0.99</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.1105</v>
+        <v>-0.0983</v>
       </c>
       <c r="J401" t="n">
-        <v>-2.873</v>
+        <v>-2.5558</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.18</v>
       </c>
       <c r="I402" t="n">
-        <v>0.4207</v>
+        <v>0.4132</v>
       </c>
       <c r="J402" t="n">
-        <v>10.0968</v>
+        <v>9.9168</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.08</v>
       </c>
       <c r="I403" t="n">
-        <v>0.2198</v>
+        <v>0.2232</v>
       </c>
       <c r="J403" t="n">
-        <v>5.2752</v>
+        <v>5.3568</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>1.05</v>
       </c>
       <c r="I404" t="n">
-        <v>0.1526</v>
+        <v>0.1575</v>
       </c>
       <c r="J404" t="n">
-        <v>3.6624</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>0.78</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.2522</v>
+        <v>-0.2668</v>
       </c>
       <c r="J405" t="n">
-        <v>-6.0528</v>
+        <v>-6.4032</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.63</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.3954</v>
+        <v>-0.4059</v>
       </c>
       <c r="J406" t="n">
-        <v>-9.489599999999999</v>
+        <v>-9.7416</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.28</v>
       </c>
       <c r="I407" t="n">
-        <v>0.7599</v>
+        <v>0.721</v>
       </c>
       <c r="J407" t="n">
-        <v>18.2376</v>
+        <v>17.304</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.27</v>
       </c>
       <c r="I408" t="n">
-        <v>0.7363</v>
+        <v>0.7002</v>
       </c>
       <c r="J408" t="n">
-        <v>17.6712</v>
+        <v>16.8048</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>1.24</v>
       </c>
       <c r="I409" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6369</v>
       </c>
       <c r="J409" t="n">
-        <v>15.9552</v>
+        <v>15.2856</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>1.01</v>
       </c>
       <c r="I410" t="n">
-        <v>0.0175</v>
+        <v>0.034</v>
       </c>
       <c r="J410" t="n">
-        <v>0.42</v>
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.98</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.1335</v>
+        <v>-0.127</v>
       </c>
       <c r="J411" t="n">
-        <v>-3.204</v>
+        <v>-3.048</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.34</v>
       </c>
       <c r="I412" t="n">
-        <v>0.6998</v>
+        <v>0.67</v>
       </c>
       <c r="J412" t="n">
-        <v>36.3896</v>
+        <v>34.84</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.03</v>
       </c>
       <c r="I413" t="n">
-        <v>0.0982</v>
+        <v>0.1046</v>
       </c>
       <c r="J413" t="n">
-        <v>5.1064</v>
+        <v>5.4392</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>0.85</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.1842</v>
+        <v>-0.1986</v>
       </c>
       <c r="J414" t="n">
-        <v>-9.5784</v>
+        <v>-10.3272</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>0.83</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.2049</v>
+        <v>-0.2193</v>
       </c>
       <c r="J415" t="n">
-        <v>-10.6548</v>
+        <v>-11.4036</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.79</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.2452</v>
+        <v>-0.2593</v>
       </c>
       <c r="J416" t="n">
-        <v>-12.7504</v>
+        <v>-13.4836</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.51</v>
       </c>
       <c r="I417" t="n">
-        <v>1.162</v>
+        <v>1.1248</v>
       </c>
       <c r="J417" t="n">
-        <v>60.424</v>
+        <v>58.4896</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.29</v>
       </c>
       <c r="I418" t="n">
-        <v>0.779</v>
+        <v>0.7386</v>
       </c>
       <c r="J418" t="n">
-        <v>40.508</v>
+        <v>38.4072</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>1.08</v>
       </c>
       <c r="I419" t="n">
-        <v>0.252</v>
+        <v>0.2616</v>
       </c>
       <c r="J419" t="n">
-        <v>13.104</v>
+        <v>13.6032</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>1.02</v>
       </c>
       <c r="I420" t="n">
-        <v>0.0549</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="J420" t="n">
-        <v>2.8548</v>
+        <v>3.7908</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.95</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.2428</v>
+        <v>-0.2319</v>
       </c>
       <c r="J421" t="n">
-        <v>-12.6256</v>
+        <v>-12.0588</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.45</v>
       </c>
       <c r="I422" t="n">
-        <v>1.1093</v>
+        <v>1.063</v>
       </c>
       <c r="J422" t="n">
-        <v>29.9511</v>
+        <v>28.701</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.03</v>
       </c>
       <c r="I423" t="n">
-        <v>0.1143</v>
+        <v>0.1248</v>
       </c>
       <c r="J423" t="n">
-        <v>3.0861</v>
+        <v>3.3696</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>0.98</v>
       </c>
       <c r="I424" t="n">
-        <v>-0.1134</v>
+        <v>-0.1131</v>
       </c>
       <c r="J424" t="n">
-        <v>-3.0618</v>
+        <v>-3.0537</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>0.97</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.1506</v>
+        <v>-0.1496</v>
       </c>
       <c r="J425" t="n">
-        <v>-4.0662</v>
+        <v>-4.0392</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>0.97</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.1506</v>
+        <v>-0.1496</v>
       </c>
       <c r="J426" t="n">
-        <v>-4.0662</v>
+        <v>-4.0392</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.65</v>
       </c>
       <c r="I427" t="n">
-        <v>1.1127</v>
+        <v>1.0811</v>
       </c>
       <c r="J427" t="n">
-        <v>30.0429</v>
+        <v>29.1897</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>1.02</v>
       </c>
       <c r="I428" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0727</v>
       </c>
       <c r="J428" t="n">
-        <v>1.7577</v>
+        <v>1.9629</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.9</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.1349</v>
+        <v>-0.1475</v>
       </c>
       <c r="J429" t="n">
-        <v>-3.6423</v>
+        <v>-3.9825</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.74</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.2987</v>
+        <v>-0.311</v>
       </c>
       <c r="J430" t="n">
-        <v>-8.0649</v>
+        <v>-8.397</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.72</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.3179</v>
+        <v>-0.3297</v>
       </c>
       <c r="J431" t="n">
-        <v>-8.583299999999999</v>
+        <v>-8.901899999999999</v>
       </c>
     </row>
     <row r="432">
@@ -20549,10 +20549,10 @@
         <v>1.59</v>
       </c>
       <c r="I432" t="n">
-        <v>1.2265</v>
+        <v>1.2005</v>
       </c>
       <c r="J432" t="n">
-        <v>26.983</v>
+        <v>26.411</v>
       </c>
     </row>
     <row r="433">
@@ -20589,10 +20589,10 @@
         <v>1.5</v>
       </c>
       <c r="I433" t="n">
-        <v>1.1161</v>
+        <v>1.0819</v>
       </c>
       <c r="J433" t="n">
-        <v>24.5542</v>
+        <v>23.8018</v>
       </c>
     </row>
     <row r="434">
@@ -20629,10 +20629,10 @@
         <v>1.36</v>
       </c>
       <c r="I434" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.8508</v>
       </c>
       <c r="J434" t="n">
-        <v>19.7714</v>
+        <v>18.7176</v>
       </c>
     </row>
     <row r="435">
@@ -20669,10 +20669,10 @@
         <v>1.15</v>
       </c>
       <c r="I435" t="n">
-        <v>0.41</v>
+        <v>0.4149</v>
       </c>
       <c r="J435" t="n">
-        <v>9.02</v>
+        <v>9.127800000000001</v>
       </c>
     </row>
     <row r="436">
@@ -20709,10 +20709,10 @@
         <v>1.01</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.023</v>
+        <v>0.0058</v>
       </c>
       <c r="J436" t="n">
-        <v>-0.506</v>
+        <v>0.1276</v>
       </c>
     </row>
     <row r="437">
@@ -20749,10 +20749,10 @@
         <v>1.04</v>
       </c>
       <c r="I437" t="n">
-        <v>0.209</v>
+        <v>0.1926</v>
       </c>
       <c r="J437" t="n">
-        <v>4.598</v>
+        <v>4.2372</v>
       </c>
     </row>
     <row r="438">
@@ -20789,10 +20789,10 @@
         <v>0.84</v>
       </c>
       <c r="I438" t="n">
-        <v>-0.1677</v>
+        <v>-0.1884</v>
       </c>
       <c r="J438" t="n">
-        <v>-3.6894</v>
+        <v>-4.1448</v>
       </c>
     </row>
     <row r="439">
@@ -20829,10 +20829,10 @@
         <v>0.83</v>
       </c>
       <c r="I439" t="n">
-        <v>-0.1783</v>
+        <v>-0.1989</v>
       </c>
       <c r="J439" t="n">
-        <v>-3.9226</v>
+        <v>-4.3758</v>
       </c>
     </row>
     <row r="440">
@@ -20869,10 +20869,10 @@
         <v>0.53</v>
       </c>
       <c r="I440" t="n">
-        <v>-0.4623</v>
+        <v>-0.4736</v>
       </c>
       <c r="J440" t="n">
-        <v>-10.1706</v>
+        <v>-10.4192</v>
       </c>
     </row>
     <row r="441">
@@ -20909,10 +20909,10 @@
         <v>0.5</v>
       </c>
       <c r="I441" t="n">
-        <v>-0.4902</v>
+        <v>-0.4999</v>
       </c>
       <c r="J441" t="n">
-        <v>-10.7844</v>
+        <v>-10.9978</v>
       </c>
     </row>
     <row r="442">
@@ -20949,10 +20949,10 @@
         <v>1.36</v>
       </c>
       <c r="I442" t="n">
-        <v>0.6803</v>
+        <v>0.6612</v>
       </c>
       <c r="J442" t="n">
-        <v>19.0484</v>
+        <v>18.5136</v>
       </c>
     </row>
     <row r="443">
@@ -20989,10 +20989,10 @@
         <v>1.24</v>
       </c>
       <c r="I443" t="n">
-        <v>0.479</v>
+        <v>0.4771</v>
       </c>
       <c r="J443" t="n">
-        <v>13.412</v>
+        <v>13.3588</v>
       </c>
     </row>
     <row r="444">
@@ -21029,10 +21029,10 @@
         <v>1.03</v>
       </c>
       <c r="I444" t="n">
-        <v>0.0752</v>
+        <v>0.0882</v>
       </c>
       <c r="J444" t="n">
-        <v>2.1056</v>
+        <v>2.4696</v>
       </c>
     </row>
     <row r="445">
@@ -21069,10 +21069,10 @@
         <v>0.98</v>
       </c>
       <c r="I445" t="n">
-        <v>-0.0469</v>
+        <v>-0.0511</v>
       </c>
       <c r="J445" t="n">
-        <v>-1.3132</v>
+        <v>-1.4308</v>
       </c>
     </row>
     <row r="446">
@@ -21109,10 +21109,10 @@
         <v>0.95</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.0951</v>
       </c>
       <c r="J446" t="n">
-        <v>-2.45</v>
+        <v>-2.6628</v>
       </c>
     </row>
     <row r="447">
@@ -21149,10 +21149,10 @@
         <v>1.39</v>
       </c>
       <c r="I447" t="n">
-        <v>1.044</v>
+        <v>0.9819</v>
       </c>
       <c r="J447" t="n">
-        <v>29.232</v>
+        <v>27.4932</v>
       </c>
     </row>
     <row r="448">
@@ -21189,10 +21189,10 @@
         <v>1.11</v>
       </c>
       <c r="I448" t="n">
-        <v>0.3686</v>
+        <v>0.3621</v>
       </c>
       <c r="J448" t="n">
-        <v>10.3208</v>
+        <v>10.1388</v>
       </c>
     </row>
     <row r="449">
@@ -21229,10 +21229,10 @@
         <v>1.07</v>
       </c>
       <c r="I449" t="n">
-        <v>0.2524</v>
+        <v>0.2543</v>
       </c>
       <c r="J449" t="n">
-        <v>7.0672</v>
+        <v>7.1204</v>
       </c>
     </row>
     <row r="450">
@@ -21269,10 +21269,10 @@
         <v>0.8</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.6289</v>
+        <v>-0.5929</v>
       </c>
       <c r="J450" t="n">
-        <v>-17.6092</v>
+        <v>-16.6012</v>
       </c>
     </row>
     <row r="451">
@@ -21309,10 +21309,10 @@
         <v>0.76</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.7316</v>
+        <v>-0.6835</v>
       </c>
       <c r="J451" t="n">
-        <v>-20.4848</v>
+        <v>-19.138</v>
       </c>
     </row>
     <row r="452">
@@ -21349,10 +21349,10 @@
         <v>1.69</v>
       </c>
       <c r="I452" t="n">
-        <v>1.1029</v>
+        <v>1.0779</v>
       </c>
       <c r="J452" t="n">
-        <v>33.087</v>
+        <v>32.337</v>
       </c>
     </row>
     <row r="453">
@@ -21389,10 +21389,10 @@
         <v>1.29</v>
       </c>
       <c r="I453" t="n">
-        <v>0.5506</v>
+        <v>0.5457</v>
       </c>
       <c r="J453" t="n">
-        <v>16.518</v>
+        <v>16.371</v>
       </c>
     </row>
     <row r="454">
@@ -21429,10 +21429,10 @@
         <v>1.14</v>
       </c>
       <c r="I454" t="n">
-        <v>0.295</v>
+        <v>0.306</v>
       </c>
       <c r="J454" t="n">
-        <v>8.85</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="455">
@@ -21469,10 +21469,10 @@
         <v>0.86</v>
       </c>
       <c r="I455" t="n">
-        <v>-0.1955</v>
+        <v>-0.205</v>
       </c>
       <c r="J455" t="n">
-        <v>-5.865</v>
+        <v>-6.15</v>
       </c>
     </row>
     <row r="456">
@@ -21509,10 +21509,10 @@
         <v>0.86</v>
       </c>
       <c r="I456" t="n">
-        <v>-0.1955</v>
+        <v>-0.205</v>
       </c>
       <c r="J456" t="n">
-        <v>-5.865</v>
+        <v>-6.15</v>
       </c>
     </row>
     <row r="457">
@@ -21549,10 +21549,10 @@
         <v>1.23</v>
       </c>
       <c r="I457" t="n">
-        <v>0.6813</v>
+        <v>0.6437</v>
       </c>
       <c r="J457" t="n">
-        <v>20.439</v>
+        <v>19.311</v>
       </c>
     </row>
     <row r="458">
@@ -21589,10 +21589,10 @@
         <v>1.17</v>
       </c>
       <c r="I458" t="n">
-        <v>0.5271</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="J458" t="n">
-        <v>15.813</v>
+        <v>15.198</v>
       </c>
     </row>
     <row r="459">
@@ -21629,10 +21629,10 @@
         <v>1.07</v>
       </c>
       <c r="I459" t="n">
-        <v>0.2494</v>
+        <v>0.2522</v>
       </c>
       <c r="J459" t="n">
-        <v>7.482</v>
+        <v>7.566</v>
       </c>
     </row>
     <row r="460">
@@ -21669,10 +21669,10 @@
         <v>0.98</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.1025</v>
+        <v>-0.1056</v>
       </c>
       <c r="J460" t="n">
-        <v>-3.075</v>
+        <v>-3.168</v>
       </c>
     </row>
     <row r="461">
@@ -21709,10 +21709,10 @@
         <v>0.74</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.7854</v>
+        <v>-0.7302</v>
       </c>
       <c r="J461" t="n">
-        <v>-23.562</v>
+        <v>-21.906</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2637/event_2637_evp_summary.xlsx
+++ b/database/event/2637/event_2637_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6878</v>
+        <v>6.5653</v>
       </c>
       <c r="C2" t="n">
-        <v>4.0715</v>
+        <v>3.9969</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4202</v>
+        <v>2.385</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6878</v>
+        <v>6.5653</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1765</v>
+        <v>3.1974</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5113</v>
+        <v>3.3679</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5862</v>
+        <v>5.5617</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0165</v>
+        <v>3.1227</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5113</v>
+        <v>3.3679</v>
       </c>
       <c r="K2" t="n">
         <v>146</v>
@@ -529,7 +529,7 @@
         <v>161</v>
       </c>
       <c r="M2" t="n">
-        <v>6.5278</v>
+        <v>6.490600000000001</v>
       </c>
       <c r="N2" t="n">
         <v>307</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.484</v>
+        <v>6.1793</v>
       </c>
       <c r="C3" t="n">
-        <v>3.9474</v>
+        <v>3.7619</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3274</v>
+        <v>2.2092</v>
       </c>
       <c r="E3" t="n">
-        <v>6.484</v>
+        <v>6.1793</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3746</v>
+        <v>2.2186</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1094</v>
+        <v>3.9607</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4723</v>
+        <v>2.2186</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6014</v>
+        <v>2.3387</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1094</v>
+        <v>3.9607</v>
       </c>
       <c r="K3" t="n">
         <v>198</v>
@@ -575,7 +575,7 @@
         <v>211</v>
       </c>
       <c r="M3" t="n">
-        <v>6.7108</v>
+        <v>6.2994</v>
       </c>
       <c r="N3" t="n">
         <v>409</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2929</v>
+        <v>6.1158</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8311</v>
+        <v>3.7233</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2405</v>
+        <v>2.1803</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2929</v>
+        <v>6.1158</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8289</v>
+        <v>2.7148</v>
       </c>
       <c r="G4" t="n">
-        <v>3.464</v>
+        <v>3.401</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4666</v>
+        <v>3.2713</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6476</v>
+        <v>3.4485</v>
       </c>
       <c r="J4" t="n">
-        <v>3.464</v>
+        <v>3.401</v>
       </c>
       <c r="K4" t="n">
         <v>198</v>
@@ -621,7 +621,7 @@
         <v>211</v>
       </c>
       <c r="M4" t="n">
-        <v>7.1116</v>
+        <v>6.8495</v>
       </c>
       <c r="N4" t="n">
         <v>409</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.2568</v>
+        <v>6.0952</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8091</v>
+        <v>3.7107</v>
       </c>
       <c r="D5" t="n">
-        <v>2.224</v>
+        <v>2.1709</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2568</v>
+        <v>6.0952</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7791</v>
+        <v>2.7265</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4777</v>
+        <v>3.3687</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3577</v>
+        <v>3.2983</v>
       </c>
       <c r="I5" t="n">
-        <v>3.533</v>
+        <v>3.4769</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4777</v>
+        <v>3.3687</v>
       </c>
       <c r="K5" t="n">
         <v>198</v>
@@ -667,7 +667,7 @@
         <v>211</v>
       </c>
       <c r="M5" t="n">
-        <v>7.0107</v>
+        <v>6.8456</v>
       </c>
       <c r="N5" t="n">
         <v>409</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.682</v>
+        <v>5.3172</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4592</v>
+        <v>3.2371</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9624</v>
+        <v>1.8165</v>
       </c>
       <c r="E6" t="n">
-        <v>5.682</v>
+        <v>5.3172</v>
       </c>
       <c r="F6" t="n">
-        <v>4.19</v>
+        <v>3.9821</v>
       </c>
       <c r="G6" t="n">
-        <v>1.492</v>
+        <v>1.3351</v>
       </c>
       <c r="H6" t="n">
-        <v>8.930300000000001</v>
+        <v>8.507999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8223</v>
+        <v>4.777</v>
       </c>
       <c r="J6" t="n">
-        <v>1.492</v>
+        <v>1.3351</v>
       </c>
       <c r="K6" t="n">
         <v>146</v>
@@ -713,7 +713,7 @@
         <v>161</v>
       </c>
       <c r="M6" t="n">
-        <v>6.3143</v>
+        <v>6.1121</v>
       </c>
       <c r="N6" t="n">
         <v>307</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1723</v>
+        <v>4.0543</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5401</v>
+        <v>2.4682</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2751</v>
+        <v>1.2411</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1723</v>
+        <v>4.0543</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8148</v>
+        <v>1.7366</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3574</v>
+        <v>2.3178</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8148</v>
+        <v>1.7366</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8616</v>
+        <v>1.783</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3574</v>
+        <v>2.3178</v>
       </c>
       <c r="K7" t="n">
         <v>175</v>
@@ -759,7 +759,7 @@
         <v>137</v>
       </c>
       <c r="M7" t="n">
-        <v>4.219</v>
+        <v>4.1008</v>
       </c>
       <c r="N7" t="n">
         <v>312</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3349</v>
+        <v>3.2589</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0303</v>
+        <v>1.984</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8939</v>
+        <v>0.8788</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3349</v>
+        <v>3.2589</v>
       </c>
       <c r="F8" t="n">
-        <v>3.119</v>
+        <v>3.0902</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2159</v>
+        <v>0.1687</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3966</v>
+        <v>5.1593</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9141</v>
+        <v>2.8968</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2159</v>
+        <v>0.1687</v>
       </c>
       <c r="K8" t="n">
         <v>146</v>
@@ -805,7 +805,7 @@
         <v>161</v>
       </c>
       <c r="M8" t="n">
-        <v>3.13</v>
+        <v>3.0655</v>
       </c>
       <c r="N8" t="n">
         <v>307</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1983</v>
+        <v>3.2072</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9471</v>
+        <v>1.9525</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8317</v>
+        <v>0.8552</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1983</v>
+        <v>3.2072</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2476</v>
+        <v>0.2266</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9507</v>
+        <v>2.9806</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2476</v>
+        <v>0.2266</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2605</v>
+        <v>0.2389</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9507</v>
+        <v>2.9806</v>
       </c>
       <c r="K9" t="n">
         <v>198</v>
@@ -851,7 +851,7 @@
         <v>211</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2112</v>
+        <v>3.2195</v>
       </c>
       <c r="N9" t="n">
         <v>409</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9302</v>
+        <v>2.8064</v>
       </c>
       <c r="C10" t="n">
-        <v>1.7839</v>
+        <v>1.7085</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7097</v>
+        <v>0.6727</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9302</v>
+        <v>2.8064</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2989</v>
+        <v>2.8064</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6314</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2989</v>
+        <v>3.4813</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3066</v>
+        <v>3.4813</v>
       </c>
       <c r="J10" t="n">
-        <v>2.6314</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="L10" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.938</v>
+        <v>3.4813</v>
       </c>
       <c r="N10" t="n">
-        <v>312</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8418</v>
+        <v>2.7697</v>
       </c>
       <c r="C11" t="n">
-        <v>1.7301</v>
+        <v>1.6862</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6694</v>
+        <v>0.6559</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8418</v>
+        <v>2.7697</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8418</v>
+        <v>0.1741</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2.5956</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4948</v>
+        <v>0.1741</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4948</v>
+        <v>0.1787</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2.5956</v>
       </c>
       <c r="K11" t="n">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4948</v>
+        <v>2.7743</v>
       </c>
       <c r="N11" t="n">
-        <v>118</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7433</v>
+        <v>2.7344</v>
       </c>
       <c r="C12" t="n">
-        <v>1.6701</v>
+        <v>1.6647</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6246</v>
+        <v>0.6399</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7433</v>
+        <v>2.7344</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7433</v>
+        <v>2.7344</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2793</v>
+        <v>3.3163</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2793</v>
+        <v>3.3163</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2793</v>
+        <v>3.3163</v>
       </c>
       <c r="N12" t="n">
         <v>128</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7</v>
+        <v>2.6899</v>
       </c>
       <c r="C13" t="n">
-        <v>1.6437</v>
+        <v>1.6376</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6049</v>
+        <v>0.6196</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7</v>
+        <v>2.6899</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8867</v>
+        <v>2.9122</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1867</v>
+        <v>-0.2223</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6301</v>
+        <v>4.4909</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5002</v>
+        <v>2.5215</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1867</v>
+        <v>-0.2223</v>
       </c>
       <c r="K13" t="n">
         <v>146</v>
@@ -1035,7 +1035,7 @@
         <v>161</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3135</v>
+        <v>2.2992</v>
       </c>
       <c r="N13" t="n">
         <v>307</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4119</v>
+        <v>2.3504</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4683</v>
+        <v>1.4309</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4737</v>
+        <v>0.4649</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4119</v>
+        <v>2.3504</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4119</v>
+        <v>2.3504</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5539</v>
+        <v>2.4364</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5539</v>
+        <v>2.4364</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5539</v>
+        <v>2.4364</v>
       </c>
       <c r="N14" t="n">
         <v>128</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3864</v>
+        <v>2.3468</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4528</v>
+        <v>1.4287</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4621</v>
+        <v>0.4633</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3864</v>
+        <v>2.3468</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3864</v>
+        <v>2.3468</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4981</v>
+        <v>2.4279</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4981</v>
+        <v>2.4279</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4981</v>
+        <v>2.4279</v>
       </c>
       <c r="N15" t="n">
         <v>149</v>
@@ -1136,47 +1136,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3463</v>
+        <v>2.2983</v>
       </c>
       <c r="C16" t="n">
-        <v>1.4284</v>
+        <v>1.3992</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4439</v>
+        <v>0.4412</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3463</v>
+        <v>2.2983</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3463</v>
+        <v>2.342</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.0437</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4104</v>
+        <v>2.3503</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4104</v>
+        <v>1.3196</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.0437</v>
       </c>
       <c r="K16" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4104</v>
+        <v>1.2759</v>
       </c>
       <c r="N16" t="n">
-        <v>128</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2989</v>
+        <v>2.2639</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3996</v>
+        <v>1.3782</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4223</v>
+        <v>0.4255</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2989</v>
+        <v>2.2639</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6839</v>
+        <v>2.6024</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.385</v>
+        <v>-0.3385</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1492</v>
+        <v>3.0137</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1492</v>
+        <v>3.0137</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.385</v>
+        <v>-0.3385</v>
       </c>
       <c r="K17" t="n">
         <v>145</v>
@@ -1219,7 +1219,7 @@
         <v>86</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7642</v>
+        <v>2.6752</v>
       </c>
       <c r="N17" t="n">
         <v>231</v>
@@ -1228,139 +1228,139 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2807</v>
+        <v>2.2631</v>
       </c>
       <c r="C18" t="n">
-        <v>1.3885</v>
+        <v>1.3778</v>
       </c>
       <c r="D18" t="n">
-        <v>0.414</v>
+        <v>0.4252</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2807</v>
+        <v>2.2631</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3038</v>
+        <v>2.2631</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0231</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7069</v>
+        <v>2.2631</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4617</v>
+        <v>2.2631</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0231</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="L18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4386</v>
+        <v>2.2631</v>
       </c>
       <c r="N18" t="n">
-        <v>194</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1309</v>
+        <v>2.1192</v>
       </c>
       <c r="C19" t="n">
-        <v>1.2973</v>
+        <v>1.2902</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3458</v>
+        <v>0.3596</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1309</v>
+        <v>2.1192</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8068</v>
+        <v>2.1192</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4182</v>
+        <v>2.1192</v>
       </c>
       <c r="I19" t="n">
-        <v>3.4182</v>
+        <v>2.1192</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L19" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7423</v>
+        <v>2.1192</v>
       </c>
       <c r="N19" t="n">
-        <v>176</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1041</v>
+        <v>2.0599</v>
       </c>
       <c r="C20" t="n">
-        <v>1.281</v>
+        <v>1.2541</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3336</v>
+        <v>0.3326</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1041</v>
+        <v>2.0599</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1041</v>
+        <v>2.7126</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1041</v>
+        <v>3.2664</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1041</v>
+        <v>3.2664</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1041</v>
+        <v>2.6137</v>
       </c>
       <c r="N20" t="n">
-        <v>134</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.7964</v>
+        <v>1.7528</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0936</v>
+        <v>1.0671</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1936</v>
+        <v>0.1927</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7964</v>
+        <v>1.7528</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1625</v>
+        <v>2.1221</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3661</v>
+        <v>-0.3693</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2408</v>
+        <v>2.1221</v>
       </c>
       <c r="I21" t="n">
-        <v>1.21</v>
+        <v>1.1915</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3661</v>
+        <v>-0.3693</v>
       </c>
       <c r="K21" t="n">
         <v>146</v>
@@ -1403,7 +1403,7 @@
         <v>161</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8439</v>
+        <v>0.8222</v>
       </c>
       <c r="N21" t="n">
         <v>307</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.7422</v>
+        <v>1.5834</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0606</v>
+        <v>0.964</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1689</v>
+        <v>0.1155</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7422</v>
+        <v>1.5834</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7422</v>
+        <v>1.5834</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7422</v>
+        <v>1.5834</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7422</v>
+        <v>1.5834</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.7422</v>
+        <v>1.5834</v>
       </c>
       <c r="N22" t="n">
         <v>163</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.6655</v>
+        <v>1.4759</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0139</v>
+        <v>0.8985</v>
       </c>
       <c r="D23" t="n">
-        <v>0.134</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6655</v>
+        <v>1.4759</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6655</v>
+        <v>1.4759</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6655</v>
+        <v>1.4759</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6655</v>
+        <v>1.4759</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.6655</v>
+        <v>1.4759</v>
       </c>
       <c r="N23" t="n">
         <v>135</v>
@@ -1504,265 +1504,265 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4414</v>
+        <v>1.3276</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.8082</v>
       </c>
       <c r="D24" t="n">
-        <v>0.032</v>
+        <v>-0.001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4414</v>
+        <v>1.3276</v>
       </c>
       <c r="F24" t="n">
-        <v>1.325</v>
+        <v>1.3276</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1164</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.325</v>
+        <v>1.3276</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7155</v>
+        <v>1.3276</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1164</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="L24" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8319000000000001</v>
+        <v>1.3276</v>
       </c>
       <c r="N24" t="n">
-        <v>194</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.4036</v>
+        <v>1.2002</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8545</v>
+        <v>0.7307</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0147</v>
+        <v>-0.059</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4036</v>
+        <v>1.2002</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4036</v>
+        <v>1.2002</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.4036</v>
+        <v>1.2002</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4036</v>
+        <v>1.2002</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.4036</v>
+        <v>1.2002</v>
       </c>
       <c r="N25" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.2152</v>
+        <v>1.1869</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7398</v>
+        <v>0.7226</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2152</v>
+        <v>1.1869</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2152</v>
+        <v>1.098</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>1.2152</v>
+        <v>1.098</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2152</v>
+        <v>0.6165</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2152</v>
+        <v>0.7054</v>
       </c>
       <c r="N26" t="n">
-        <v>135</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.171</v>
+        <v>1.0602</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7129</v>
+        <v>0.6454</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0911</v>
+        <v>-0.1228</v>
       </c>
       <c r="E27" t="n">
-        <v>1.171</v>
+        <v>1.0602</v>
       </c>
       <c r="F27" t="n">
-        <v>1.171</v>
+        <v>1.0602</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.171</v>
+        <v>1.0602</v>
       </c>
       <c r="I27" t="n">
-        <v>1.171</v>
+        <v>1.0602</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.171</v>
+        <v>1.0602</v>
       </c>
       <c r="N27" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.032</v>
+        <v>0.9938</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6283</v>
+        <v>0.605</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1544</v>
+        <v>-0.1531</v>
       </c>
       <c r="E28" t="n">
-        <v>1.032</v>
+        <v>0.9938</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6516</v>
+        <v>1.5348</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3804</v>
+        <v>-0.541</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6516</v>
+        <v>1.5348</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6516</v>
+        <v>1.5348</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3804</v>
+        <v>-0.541</v>
       </c>
       <c r="K28" t="n">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="L28" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="M28" t="n">
-        <v>1.032</v>
+        <v>0.9937999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>231</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.0152</v>
+        <v>0.973</v>
       </c>
       <c r="C29" t="n">
-        <v>0.618</v>
+        <v>0.5924</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1621</v>
+        <v>-0.1625</v>
       </c>
       <c r="E29" t="n">
-        <v>1.0152</v>
+        <v>0.973</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5667</v>
+        <v>0.5611</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.5515</v>
+        <v>0.4119</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5667</v>
+        <v>0.5611</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5667</v>
+        <v>0.5611</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5515</v>
+        <v>0.4119</v>
       </c>
       <c r="K29" t="n">
         <v>131</v>
@@ -1771,7 +1771,7 @@
         <v>45</v>
       </c>
       <c r="M29" t="n">
-        <v>1.0152</v>
+        <v>0.9730000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>176</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.0075</v>
+        <v>0.9563</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1656</v>
+        <v>-0.1701</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0075</v>
+        <v>0.9563</v>
       </c>
       <c r="F30" t="n">
-        <v>1.0075</v>
+        <v>0.9563</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.0075</v>
+        <v>0.9563</v>
       </c>
       <c r="I30" t="n">
-        <v>1.0075</v>
+        <v>0.9563</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.0075</v>
+        <v>0.9563</v>
       </c>
       <c r="N30" t="n">
         <v>134</v>
@@ -1826,47 +1826,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9893</v>
+        <v>0.888</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.5406</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1739</v>
+        <v>-0.2013</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9893</v>
+        <v>0.888</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5698</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4195</v>
+        <v>0.3089</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5698</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5698</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4195</v>
+        <v>0.3089</v>
       </c>
       <c r="K31" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="L31" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9893</v>
+        <v>0.8879999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>176</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7861</v>
+        <v>0.8031</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4786</v>
+        <v>0.4889</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2664</v>
+        <v>-0.2399</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7861</v>
+        <v>0.8031</v>
       </c>
       <c r="F32" t="n">
-        <v>1.7861</v>
+        <v>1.8031</v>
       </c>
       <c r="G32" t="n">
         <v>-1</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7861</v>
+        <v>1.8031</v>
       </c>
       <c r="I32" t="n">
-        <v>1.7861</v>
+        <v>1.8031</v>
       </c>
       <c r="J32" t="n">
         <v>-1</v>
@@ -1909,7 +1909,7 @@
         <v>45</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7861</v>
+        <v>0.8030999999999999</v>
       </c>
       <c r="N32" t="n">
         <v>176</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7411</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4512</v>
+        <v>0.4637</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2868</v>
+        <v>-0.2588</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7411</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>1.0293</v>
+        <v>0.9737</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.2882</v>
+        <v>-0.2121</v>
       </c>
       <c r="H33" t="n">
-        <v>1.0293</v>
+        <v>0.9737</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0558</v>
+        <v>0.9998</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.2882</v>
+        <v>-0.2121</v>
       </c>
       <c r="K33" t="n">
         <v>175</v>
@@ -1955,7 +1955,7 @@
         <v>137</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7676000000000001</v>
+        <v>0.7877000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>312</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6856</v>
+        <v>0.5111</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4174</v>
+        <v>0.3112</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3121</v>
+        <v>-0.373</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6856</v>
+        <v>0.5111</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1295</v>
+        <v>0.494</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.4439</v>
+        <v>0.0171</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1295</v>
+        <v>0.494</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6099</v>
+        <v>0.5072</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.4439</v>
+        <v>0.0171</v>
       </c>
       <c r="K34" t="n">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="L34" t="n">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="M34" t="n">
-        <v>0.166</v>
+        <v>0.5243</v>
       </c>
       <c r="N34" t="n">
-        <v>194</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.537</v>
+        <v>0.4972</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3269</v>
+        <v>0.3027</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3797</v>
+        <v>-0.3793</v>
       </c>
       <c r="E35" t="n">
-        <v>0.537</v>
+        <v>0.4972</v>
       </c>
       <c r="F35" t="n">
-        <v>0.537</v>
+        <v>0.4972</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.537</v>
+        <v>0.4972</v>
       </c>
       <c r="I35" t="n">
-        <v>0.537</v>
+        <v>0.4972</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.537</v>
+        <v>0.4972</v>
       </c>
       <c r="N35" t="n">
         <v>128</v>
@@ -2056,323 +2056,323 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4999</v>
+        <v>0.4625</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3043</v>
+        <v>0.2816</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3966</v>
+        <v>-0.3951</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4999</v>
+        <v>0.4625</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9779</v>
+        <v>0.8789</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.478</v>
+        <v>-0.4164</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9779</v>
+        <v>0.8789</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9779</v>
+        <v>0.4935</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.478</v>
+        <v>-0.4164</v>
       </c>
       <c r="K36" t="n">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="L36" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="M36" t="n">
-        <v>0.4999</v>
+        <v>0.0771</v>
       </c>
       <c r="N36" t="n">
-        <v>231</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4913</v>
+        <v>0.4589</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2991</v>
+        <v>0.2794</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4006</v>
+        <v>-0.3967</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4913</v>
+        <v>0.4589</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4913</v>
+        <v>0.9166</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.4577</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4913</v>
+        <v>0.9166</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4913</v>
+        <v>0.9166</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.4577</v>
       </c>
       <c r="K37" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4913</v>
+        <v>0.4589</v>
       </c>
       <c r="N37" t="n">
-        <v>135</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4856</v>
+        <v>0.4321</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2956</v>
+        <v>0.2631</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.4031</v>
+        <v>-0.4089</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4856</v>
+        <v>0.4321</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5058</v>
+        <v>0.4321</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0202</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5058</v>
+        <v>0.4321</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5188</v>
+        <v>0.4321</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.0202</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="L38" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4986</v>
+        <v>0.4321</v>
       </c>
       <c r="N38" t="n">
-        <v>312</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4802</v>
+        <v>0.421</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2923</v>
+        <v>0.2563</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4056</v>
+        <v>-0.414</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4802</v>
+        <v>0.421</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4802</v>
+        <v>0.421</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4802</v>
+        <v>0.421</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4802</v>
+        <v>0.421</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4802</v>
+        <v>0.421</v>
       </c>
       <c r="N39" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4734</v>
+        <v>0.3814</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2882</v>
+        <v>0.2322</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4087</v>
+        <v>-0.432</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4734</v>
+        <v>0.3814</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4734</v>
+        <v>0.3814</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4734</v>
+        <v>0.3814</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4734</v>
+        <v>0.3814</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4734</v>
+        <v>0.3814</v>
       </c>
       <c r="N40" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3296</v>
+        <v>0.3072</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2007</v>
+        <v>0.187</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4742</v>
+        <v>-0.4658</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3296</v>
+        <v>0.3072</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5276</v>
+        <v>0.3072</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.198</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5276</v>
+        <v>0.3072</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5276</v>
+        <v>0.3072</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.198</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="L41" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3295999999999999</v>
+        <v>0.3072</v>
       </c>
       <c r="N41" t="n">
-        <v>231</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3277</v>
+        <v>0.2221</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1995</v>
+        <v>0.1352</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.475</v>
+        <v>-0.5046</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3277</v>
+        <v>0.2221</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3277</v>
+        <v>0.4843</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-0.2622</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3277</v>
+        <v>0.4843</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3277</v>
+        <v>0.4843</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-0.2622</v>
       </c>
       <c r="K42" t="n">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3277</v>
+        <v>0.2221</v>
       </c>
       <c r="N42" t="n">
-        <v>118</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2786</v>
+        <v>0.1986</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1696</v>
+        <v>0.1209</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4974</v>
+        <v>-0.5153</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2786</v>
+        <v>0.1986</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2786</v>
+        <v>0.1986</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2786</v>
+        <v>0.1986</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2786</v>
+        <v>0.1986</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2786</v>
+        <v>0.1986</v>
       </c>
       <c r="N43" t="n">
         <v>149</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.1435</v>
+        <v>0.1165</v>
       </c>
       <c r="C44" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0709</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5589</v>
+        <v>-0.5527</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1435</v>
+        <v>0.1165</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7773</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.6338</v>
+        <v>-0.6068</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7773</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7773</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.6338</v>
+        <v>-0.6068</v>
       </c>
       <c r="K44" t="n">
         <v>131</v>
@@ -2461,7 +2461,7 @@
         <v>45</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1435</v>
+        <v>0.1165</v>
       </c>
       <c r="N44" t="n">
         <v>176</v>
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0575</v>
+        <v>0.1103</v>
       </c>
       <c r="C45" t="n">
-        <v>0.035</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.598</v>
+        <v>-0.5555</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0575</v>
+        <v>0.1103</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0575</v>
+        <v>0.1103</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0575</v>
+        <v>0.1103</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0575</v>
+        <v>0.1103</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.0575</v>
+        <v>0.1103</v>
       </c>
       <c r="N45" t="n">
         <v>163</v>
@@ -2516,139 +2516,139 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.06</v>
+        <v>0.0433</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0365</v>
+        <v>0.0264</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6515</v>
+        <v>-0.5861</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.06</v>
+        <v>0.0433</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.06</v>
+        <v>0.0433</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.06</v>
+        <v>0.0433</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.06</v>
+        <v>0.0433</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.06</v>
+        <v>0.0433</v>
       </c>
       <c r="N46" t="n">
-        <v>163</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0.0029</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0391</v>
+        <v>0.0018</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6534</v>
+        <v>-0.6045</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0.0029</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0.5177</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-0.5148</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0.5177</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0.2907</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>-0.5148</v>
       </c>
       <c r="K47" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.2241</v>
       </c>
       <c r="N47" t="n">
-        <v>128</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.1084</v>
+        <v>-0.1303</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.066</v>
+        <v>-0.0793</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6735</v>
+        <v>-0.6651</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.1084</v>
+        <v>-0.1303</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4437</v>
+        <v>-0.1303</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.5521</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4437</v>
+        <v>-0.1303</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2396</v>
+        <v>-0.1303</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.5521</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="L48" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.3125</v>
+        <v>-0.1303</v>
       </c>
       <c r="N48" t="n">
-        <v>194</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.16</v>
+        <v>-0.1731</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0974</v>
+        <v>-0.1054</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.697</v>
+        <v>-0.6846</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.16</v>
+        <v>-0.1731</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.16</v>
+        <v>-0.1731</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.16</v>
+        <v>-0.1731</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.16</v>
+        <v>-0.1731</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.16</v>
+        <v>-0.1731</v>
       </c>
       <c r="N49" t="n">
         <v>134</v>
@@ -2700,139 +2700,139 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1939</v>
+        <v>-0.1845</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.118</v>
+        <v>-0.1123</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7125</v>
+        <v>-0.6898</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1939</v>
+        <v>-0.1845</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0424</v>
+        <v>-0.1845</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.1515</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.0424</v>
+        <v>-0.1845</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0424</v>
+        <v>-0.1845</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.1515</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L50" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1939</v>
+        <v>-0.1845</v>
       </c>
       <c r="N50" t="n">
-        <v>231</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.2193</v>
+        <v>-0.1851</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1335</v>
+        <v>-0.1127</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.724</v>
+        <v>-0.6901</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.2193</v>
+        <v>-0.1851</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2193</v>
+        <v>-0.1851</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.2193</v>
+        <v>-0.1851</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2193</v>
+        <v>-0.1851</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.2193</v>
+        <v>-0.1851</v>
       </c>
       <c r="N51" t="n">
-        <v>149</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2388</v>
+        <v>-0.2048</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1454</v>
+        <v>-0.1247</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.7329</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2388</v>
+        <v>-0.2048</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.2388</v>
+        <v>-0.0408</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-0.164</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2388</v>
+        <v>-0.0408</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2388</v>
+        <v>-0.0408</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-0.164</v>
       </c>
       <c r="K52" t="n">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.2388</v>
+        <v>-0.2048</v>
       </c>
       <c r="N52" t="n">
-        <v>118</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53">
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3106</v>
+        <v>-0.2836</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1891</v>
+        <v>-0.1727</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.735</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3106</v>
+        <v>-0.2836</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3106</v>
+        <v>-0.2836</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3106</v>
+        <v>-0.2836</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3106</v>
+        <v>-0.2836</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3106</v>
+        <v>-0.2836</v>
       </c>
       <c r="N53" t="n">
         <v>163</v>
@@ -2884,93 +2884,93 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3218</v>
+        <v>-0.3673</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1959</v>
+        <v>-0.2236</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.7731</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.3218</v>
+        <v>-0.3673</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3218</v>
+        <v>-0.3673</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.3218</v>
+        <v>-0.3673</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3218</v>
+        <v>-0.3673</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.3218</v>
+        <v>-0.3673</v>
       </c>
       <c r="N54" t="n">
-        <v>135</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.405</v>
+        <v>-0.3761</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2466</v>
+        <v>-0.229</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.8086</v>
+        <v>-0.7771</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.405</v>
+        <v>-0.3761</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.405</v>
+        <v>-0.3761</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.405</v>
+        <v>-0.3761</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.405</v>
+        <v>-0.3761</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.405</v>
+        <v>-0.3761</v>
       </c>
       <c r="N55" t="n">
-        <v>163</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56">
@@ -2980,31 +2980,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.4716</v>
+        <v>-0.4518</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2871</v>
+        <v>-0.2751</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.8389</v>
+        <v>-0.8116</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.4716</v>
+        <v>-0.4518</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.9165</v>
+        <v>-1.8571</v>
       </c>
       <c r="G56" t="n">
-        <v>1.4449</v>
+        <v>1.4053</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.9165</v>
+        <v>-1.8571</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.0165</v>
+        <v>-1.9577</v>
       </c>
       <c r="J56" t="n">
-        <v>1.4449</v>
+        <v>1.4053</v>
       </c>
       <c r="K56" t="n">
         <v>198</v>
@@ -3013,7 +3013,7 @@
         <v>211</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.5716000000000001</v>
+        <v>-0.5524</v>
       </c>
       <c r="N56" t="n">
         <v>409</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.7837</v>
+        <v>-0.7766</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.4771</v>
+        <v>-0.4728</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.981</v>
+        <v>-0.9596</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.7837</v>
+        <v>-0.7766</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.7837</v>
+        <v>-0.7766</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.7837</v>
+        <v>-0.7766</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.7837</v>
+        <v>-0.7766</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.7837</v>
+        <v>-0.7766</v>
       </c>
       <c r="N57" t="n">
         <v>118</v>
@@ -3072,31 +3072,31 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.8344</v>
+        <v>-0.783</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.508</v>
+        <v>-0.4767</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.004</v>
+        <v>-0.9625</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.8344</v>
+        <v>-0.783</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4871</v>
+        <v>-0.4685</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.3473</v>
+        <v>-0.3145</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.4871</v>
+        <v>-0.4685</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.4997</v>
+        <v>-0.481</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.3473</v>
+        <v>-0.3145</v>
       </c>
       <c r="K58" t="n">
         <v>175</v>
@@ -3105,7 +3105,7 @@
         <v>137</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.847</v>
+        <v>-0.7955</v>
       </c>
       <c r="N58" t="n">
         <v>312</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.8752</v>
+        <v>-0.8714</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.5305</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.0226</v>
+        <v>-1.0028</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.8752</v>
+        <v>-0.8714</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.8752</v>
+        <v>-0.8714</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.8752</v>
+        <v>-0.8714</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.8752</v>
+        <v>-0.8714</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.8752</v>
+        <v>-0.8714</v>
       </c>
       <c r="N59" t="n">
         <v>135</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.1765</v>
+        <v>-1.1075</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.6742</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.1598</v>
+        <v>-1.1103</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.1765</v>
+        <v>-1.1075</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.1765</v>
+        <v>-1.1075</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.1765</v>
+        <v>-1.1075</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1765</v>
+        <v>-1.1075</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.1765</v>
+        <v>-1.1075</v>
       </c>
       <c r="N60" t="n">
         <v>118</v>
@@ -3210,31 +3210,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-3.3074</v>
+        <v>-2.9747</v>
       </c>
       <c r="C61" t="n">
-        <v>-2.0135</v>
+        <v>-1.811</v>
       </c>
       <c r="D61" t="n">
-        <v>-2.1298</v>
+        <v>-1.9609</v>
       </c>
       <c r="E61" t="n">
-        <v>-3.3074</v>
+        <v>-2.9747</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.4232</v>
+        <v>-3.0625</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1158</v>
+        <v>0.0878</v>
       </c>
       <c r="H61" t="n">
-        <v>-3.4232</v>
+        <v>-3.0625</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.8485</v>
+        <v>-1.7195</v>
       </c>
       <c r="J61" t="n">
-        <v>0.1158</v>
+        <v>0.0878</v>
       </c>
       <c r="K61" t="n">
         <v>138</v>
@@ -3243,7 +3243,7 @@
         <v>56</v>
       </c>
       <c r="M61" t="n">
-        <v>-1.7327</v>
+        <v>-1.6317</v>
       </c>
       <c r="N61" t="n">
         <v>194</v>
@@ -3349,10 +3349,10 @@
         <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>0.604</v>
+        <v>0.5329</v>
       </c>
       <c r="J2" t="n">
-        <v>15.1</v>
+        <v>13.3225</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4199</v>
+        <v>0.3557</v>
       </c>
       <c r="J3" t="n">
-        <v>10.4975</v>
+        <v>8.8925</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3033</v>
+        <v>0.2489</v>
       </c>
       <c r="J4" t="n">
-        <v>7.5825</v>
+        <v>6.2225</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>1.12</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2027</v>
+        <v>0.1608</v>
       </c>
       <c r="J5" t="n">
-        <v>5.0675</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.62</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4302</v>
+        <v>-0.425</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.755</v>
+        <v>-10.625</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.35</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5343</v>
+        <v>0.5505</v>
       </c>
       <c r="J7" t="n">
-        <v>13.3575</v>
+        <v>13.7625</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>1.3</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4729</v>
+        <v>0.4797</v>
       </c>
       <c r="J8" t="n">
-        <v>11.8225</v>
+        <v>11.9925</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1674</v>
+        <v>-0.1473</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.185</v>
+        <v>-3.6825</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.74</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3084</v>
+        <v>-0.2909</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.71</v>
+        <v>-7.2725</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.62</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4178</v>
+        <v>-0.4092</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.445</v>
+        <v>-10.23</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.18</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4244</v>
+        <v>0.369</v>
       </c>
       <c r="J12" t="n">
-        <v>11.8832</v>
+        <v>10.332</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>1.16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3882</v>
+        <v>0.3338</v>
       </c>
       <c r="J13" t="n">
-        <v>10.8696</v>
+        <v>9.346399999999999</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1172</v>
+        <v>-0.1009</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.2816</v>
+        <v>-2.8252</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>0.64</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3934</v>
+        <v>-0.3817</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.0152</v>
+        <v>-10.6876</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.63</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4023</v>
+        <v>-0.3914</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.2644</v>
+        <v>-10.9592</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.42</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9929</v>
+        <v>0.984</v>
       </c>
       <c r="J17" t="n">
-        <v>27.8012</v>
+        <v>27.552</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7764</v>
+        <v>0.75</v>
       </c>
       <c r="J18" t="n">
-        <v>21.7392</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.15</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4358</v>
+        <v>0.4004</v>
       </c>
       <c r="J19" t="n">
-        <v>12.2024</v>
+        <v>11.2112</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1406</v>
+        <v>0.1167</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9368</v>
+        <v>3.2676</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0307</v>
+        <v>-0.0252</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8596</v>
+        <v>-0.7056</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7901</v>
+        <v>0.7456</v>
       </c>
       <c r="J22" t="n">
-        <v>22.1228</v>
+        <v>20.8768</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3906</v>
+        <v>0.3365</v>
       </c>
       <c r="J23" t="n">
-        <v>10.9368</v>
+        <v>9.422000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>0.76</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2816</v>
+        <v>-0.2629</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.8848</v>
+        <v>-7.3612</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.63</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4015</v>
+        <v>-0.3905</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.242</v>
+        <v>-10.934</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.54</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4805</v>
+        <v>-0.4783</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.454</v>
+        <v>-13.3924</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1401</v>
+        <v>1.1476</v>
       </c>
       <c r="J27" t="n">
-        <v>31.9228</v>
+        <v>32.1328</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.27</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6921</v>
+        <v>0.6619</v>
       </c>
       <c r="J28" t="n">
-        <v>19.3788</v>
+        <v>18.5332</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5877</v>
+        <v>0.5542</v>
       </c>
       <c r="J29" t="n">
-        <v>16.4556</v>
+        <v>15.5176</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>1.15</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4339</v>
+        <v>0.3992</v>
       </c>
       <c r="J30" t="n">
-        <v>12.1492</v>
+        <v>11.1776</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.85</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5069</v>
+        <v>-0.4676</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.1932</v>
+        <v>-13.0928</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.25</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5224</v>
+        <v>0.4636</v>
       </c>
       <c r="J32" t="n">
-        <v>15.1496</v>
+        <v>13.4444</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.03</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1027</v>
+        <v>0.0756</v>
       </c>
       <c r="J33" t="n">
-        <v>2.9783</v>
+        <v>2.1924</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>0.99</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0244</v>
+        <v>-0.0178</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7076</v>
+        <v>-0.5162</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.83</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2204</v>
+        <v>-0.1999</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.3916</v>
+        <v>-5.7971</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.8</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2506</v>
+        <v>-0.2306</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.2674</v>
+        <v>-6.6874</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.24</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6683</v>
+        <v>0.6328</v>
       </c>
       <c r="J37" t="n">
-        <v>19.3807</v>
+        <v>18.3512</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.2</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5784</v>
+        <v>0.5387</v>
       </c>
       <c r="J38" t="n">
-        <v>16.7736</v>
+        <v>15.6223</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1951</v>
+        <v>0.1624</v>
       </c>
       <c r="J39" t="n">
-        <v>5.6579</v>
+        <v>4.7096</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>0.89</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3743</v>
+        <v>-0.3314</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.8547</v>
+        <v>-9.6106</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.662</v>
+        <v>-0.6268</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.198</v>
+        <v>-18.1772</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.06</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1882</v>
+        <v>0.1482</v>
       </c>
       <c r="J42" t="n">
-        <v>5.2696</v>
+        <v>4.1496</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1653</v>
+        <v>0.1282</v>
       </c>
       <c r="J43" t="n">
-        <v>4.6284</v>
+        <v>3.5896</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>0.95</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.08</v>
+        <v>-0.0668</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.24</v>
+        <v>-1.8704</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>0.8</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2437</v>
+        <v>-0.224</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.8236</v>
+        <v>-6.272</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>0.68</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3574</v>
+        <v>-0.3427</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.0072</v>
+        <v>-9.595599999999999</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.31</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6992</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>19.5776</v>
+        <v>19.152</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>1.3</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.669</v>
       </c>
       <c r="J48" t="n">
-        <v>19.152</v>
+        <v>18.732</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>1.27</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6377</v>
+        <v>0.6241</v>
       </c>
       <c r="J49" t="n">
-        <v>17.8556</v>
+        <v>17.4748</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3389</v>
+        <v>-0.297</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.4892</v>
+        <v>-8.316000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5651</v>
+        <v>-0.5263</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.8228</v>
+        <v>-14.7364</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.21</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4732</v>
+        <v>0.4305</v>
       </c>
       <c r="J52" t="n">
-        <v>13.2496</v>
+        <v>12.054</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>0.97</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0489</v>
+        <v>-0.0393</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.3692</v>
+        <v>-1.1004</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>0.83</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2113</v>
+        <v>-0.1919</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.9164</v>
+        <v>-5.3732</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.73</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3084</v>
+        <v>-0.2908</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.635199999999999</v>
+        <v>-8.1424</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.67</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3639</v>
+        <v>-0.3496</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.1892</v>
+        <v>-9.7888</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.4</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8312</v>
+        <v>0.8152</v>
       </c>
       <c r="J57" t="n">
-        <v>23.2736</v>
+        <v>22.8256</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5571</v>
+        <v>0.5473</v>
       </c>
       <c r="J58" t="n">
-        <v>15.5988</v>
+        <v>15.3244</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>1.1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3209</v>
+        <v>0.2855</v>
       </c>
       <c r="J59" t="n">
-        <v>8.985200000000001</v>
+        <v>7.994</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>1.09</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2949</v>
+        <v>0.2605</v>
       </c>
       <c r="J60" t="n">
-        <v>8.257199999999999</v>
+        <v>7.294</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.519</v>
+        <v>-0.4786</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.532</v>
+        <v>-13.4008</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.66</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1766</v>
+        <v>1.1735</v>
       </c>
       <c r="J62" t="n">
-        <v>29.415</v>
+        <v>29.3375</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.28</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6434</v>
+        <v>0.631</v>
       </c>
       <c r="J63" t="n">
-        <v>16.085</v>
+        <v>15.775</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>1.05</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1726</v>
+        <v>0.1462</v>
       </c>
       <c r="J64" t="n">
-        <v>4.315</v>
+        <v>3.655</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.98</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1317</v>
+        <v>-0.1044</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.2925</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2646</v>
+        <v>-0.2261</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.615</v>
+        <v>-5.6525</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3096</v>
+        <v>0.2584</v>
       </c>
       <c r="J67" t="n">
-        <v>7.74</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>1.01</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0433</v>
+        <v>0.0293</v>
       </c>
       <c r="J68" t="n">
-        <v>1.0825</v>
+        <v>0.7325</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>0.96</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0725</v>
+        <v>-0.0582</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.8125</v>
+        <v>-1.455</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.96</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0725</v>
+        <v>-0.0582</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.8125</v>
+        <v>-1.455</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.099</v>
+        <v>-0.0822</v>
       </c>
       <c r="J71" t="n">
-        <v>-2.475</v>
+        <v>-2.055</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.52</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9875</v>
+        <v>0.9746</v>
       </c>
       <c r="J72" t="n">
-        <v>25.675</v>
+        <v>25.3396</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.24</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5813</v>
+        <v>0.572</v>
       </c>
       <c r="J73" t="n">
-        <v>15.1138</v>
+        <v>14.872</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4865</v>
+        <v>0.468</v>
       </c>
       <c r="J74" t="n">
-        <v>12.649</v>
+        <v>12.168</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0311</v>
+        <v>-0.0255</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.8086</v>
+        <v>-0.663</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.99</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>-2.3634</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.15</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3824</v>
+        <v>0.33</v>
       </c>
       <c r="J77" t="n">
-        <v>9.942399999999999</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>0.91</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1255</v>
+        <v>-0.1097</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.263</v>
+        <v>-2.8522</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>0.79</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2495</v>
+        <v>-0.2303</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.487</v>
+        <v>-5.9878</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.77</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2688</v>
+        <v>-0.25</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.9888</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.71</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3254</v>
+        <v>-0.3087</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.4604</v>
+        <v>-8.026199999999999</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.46</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8984</v>
+        <v>0.8835</v>
       </c>
       <c r="J82" t="n">
-        <v>24.2568</v>
+        <v>23.8545</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.24</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5782</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>15.6114</v>
+        <v>15.3927</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.14</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4072</v>
+        <v>0.3736</v>
       </c>
       <c r="J84" t="n">
-        <v>10.9944</v>
+        <v>10.0872</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>1.12</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3586</v>
+        <v>0.3253</v>
       </c>
       <c r="J85" t="n">
-        <v>9.6822</v>
+        <v>8.783099999999999</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>1.12</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3586</v>
+        <v>0.3253</v>
       </c>
       <c r="J86" t="n">
-        <v>9.6822</v>
+        <v>8.783099999999999</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6182</v>
+        <v>0.5961</v>
       </c>
       <c r="J87" t="n">
-        <v>16.6914</v>
+        <v>16.0947</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0456</v>
+        <v>-0.0363</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.2312</v>
+        <v>-0.9801</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2485</v>
+        <v>-0.2295</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.7095</v>
+        <v>-6.1965</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.6</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.424</v>
+        <v>-0.4148</v>
       </c>
       <c r="J90" t="n">
-        <v>-11.448</v>
+        <v>-11.1996</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.6</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.424</v>
+        <v>-0.4148</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.448</v>
+        <v>-11.1996</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>1.83</v>
       </c>
       <c r="I92" t="n">
-        <v>1.3096</v>
+        <v>1.3142</v>
       </c>
       <c r="J92" t="n">
-        <v>23.5728</v>
+        <v>23.6556</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>1.7</v>
       </c>
       <c r="I93" t="n">
-        <v>1.155</v>
+        <v>1.1531</v>
       </c>
       <c r="J93" t="n">
-        <v>20.79</v>
+        <v>20.7558</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>1.57</v>
       </c>
       <c r="I94" t="n">
-        <v>0.998</v>
+        <v>0.9932</v>
       </c>
       <c r="J94" t="n">
-        <v>17.964</v>
+        <v>17.8776</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>1.55</v>
       </c>
       <c r="I95" t="n">
-        <v>0.9735</v>
+        <v>0.9685</v>
       </c>
       <c r="J95" t="n">
-        <v>17.523</v>
+        <v>17.433</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>1.24</v>
       </c>
       <c r="I96" t="n">
-        <v>0.5425</v>
+        <v>0.5412</v>
       </c>
       <c r="J96" t="n">
-        <v>9.765000000000001</v>
+        <v>9.7416</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>0.8</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.1987</v>
+        <v>-0.1813</v>
       </c>
       <c r="J97" t="n">
-        <v>-3.5766</v>
+        <v>-3.2634</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>0.75</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2519</v>
+        <v>-0.2379</v>
       </c>
       <c r="J98" t="n">
-        <v>-4.5342</v>
+        <v>-4.2822</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>0.61</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3853</v>
+        <v>-0.3773</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.9354</v>
+        <v>-6.7914</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>0.47</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5059</v>
+        <v>-0.5047</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.106199999999999</v>
+        <v>-9.0846</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>0.35</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6119</v>
+        <v>-0.6251</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.0142</v>
+        <v>-11.2518</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.63</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1385</v>
+        <v>1.1331</v>
       </c>
       <c r="J102" t="n">
-        <v>34.155</v>
+        <v>33.993</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>1.3</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6746</v>
+        <v>0.6609</v>
       </c>
       <c r="J103" t="n">
-        <v>20.238</v>
+        <v>19.827</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>1.27</v>
       </c>
       <c r="I104" t="n">
-        <v>0.629</v>
+        <v>0.617</v>
       </c>
       <c r="J104" t="n">
-        <v>18.87</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.88</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4281</v>
+        <v>-0.3867</v>
       </c>
       <c r="J105" t="n">
-        <v>-12.843</v>
+        <v>-11.601</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.8</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6213</v>
+        <v>-0.5866</v>
       </c>
       <c r="J106" t="n">
-        <v>-18.639</v>
+        <v>-17.598</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>1.2</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4389</v>
+        <v>0.3848</v>
       </c>
       <c r="J107" t="n">
-        <v>13.167</v>
+        <v>11.544</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0475</v>
+        <v>0.0317</v>
       </c>
       <c r="J108" t="n">
-        <v>1.425</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>0.99</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0235</v>
+        <v>-0.0173</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.705</v>
+        <v>-0.519</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>0.83</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2191</v>
+        <v>-0.1986</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.573</v>
+        <v>-5.958</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.8</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2493</v>
+        <v>-0.2293</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.479</v>
+        <v>-6.879</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.33</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4767</v>
+        <v>0.496</v>
       </c>
       <c r="J112" t="n">
-        <v>16.2078</v>
+        <v>16.864</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.13</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2332</v>
+        <v>0.2188</v>
       </c>
       <c r="J113" t="n">
-        <v>7.9288</v>
+        <v>7.4392</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.04</v>
       </c>
       <c r="I114" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0798</v>
       </c>
       <c r="J114" t="n">
-        <v>3.1382</v>
+        <v>2.7132</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1047</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J115" t="n">
-        <v>-3.5598</v>
+        <v>-2.958</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1414</v>
+        <v>-0.1217</v>
       </c>
       <c r="J116" t="n">
-        <v>-4.8076</v>
+        <v>-4.1378</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.388</v>
+        <v>0.3253</v>
       </c>
       <c r="J117" t="n">
-        <v>13.192</v>
+        <v>11.0602</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2374</v>
+        <v>0.1886</v>
       </c>
       <c r="J118" t="n">
-        <v>8.0716</v>
+        <v>6.4124</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>1.06</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1221</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="J119" t="n">
-        <v>4.1514</v>
+        <v>3.0906</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0616</v>
+        <v>-0.0481</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.0944</v>
+        <v>-1.6354</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.8</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2565</v>
+        <v>-0.2369</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.721</v>
+        <v>-8.054600000000001</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.79</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3024</v>
+        <v>1.3051</v>
       </c>
       <c r="J122" t="n">
-        <v>28.6528</v>
+        <v>28.7122</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.53</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9711</v>
+        <v>0.959</v>
       </c>
       <c r="J123" t="n">
-        <v>21.3642</v>
+        <v>21.098</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.4</v>
       </c>
       <c r="I124" t="n">
-        <v>0.7965</v>
+        <v>0.7847</v>
       </c>
       <c r="J124" t="n">
-        <v>17.523</v>
+        <v>17.2634</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>1.15</v>
       </c>
       <c r="I125" t="n">
-        <v>0.411</v>
+        <v>0.3799</v>
       </c>
       <c r="J125" t="n">
-        <v>9.042</v>
+        <v>8.357799999999999</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.85</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5301</v>
+        <v>-0.4957</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.6622</v>
+        <v>-10.9054</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.0741</v>
+        <v>-0.0611</v>
       </c>
       <c r="J127" t="n">
-        <v>-1.6302</v>
+        <v>-1.3442</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>0.86</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1698</v>
+        <v>-0.154</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.7356</v>
+        <v>-3.388</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1806</v>
+        <v>-0.1647</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.9732</v>
+        <v>-3.6234</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.269</v>
+        <v>-0.2525</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.918</v>
+        <v>-5.555</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.43</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5625</v>
+        <v>-0.5702</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.375</v>
+        <v>-12.5444</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.14</v>
       </c>
       <c r="I132" t="n">
-        <v>0.436</v>
+        <v>0.3937</v>
       </c>
       <c r="J132" t="n">
-        <v>13.08</v>
+        <v>11.811</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.14</v>
       </c>
       <c r="I133" t="n">
-        <v>0.436</v>
+        <v>0.3937</v>
       </c>
       <c r="J133" t="n">
-        <v>13.08</v>
+        <v>11.811</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>1.06</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2246</v>
+        <v>0.1896</v>
       </c>
       <c r="J134" t="n">
-        <v>6.738</v>
+        <v>5.688</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>1.01</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0552</v>
+        <v>0.0411</v>
       </c>
       <c r="J135" t="n">
-        <v>1.656</v>
+        <v>1.233</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5709</v>
+        <v>-0.5311</v>
       </c>
       <c r="J136" t="n">
-        <v>-17.127</v>
+        <v>-15.933</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.23</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4667</v>
+        <v>0.4086</v>
       </c>
       <c r="J137" t="n">
-        <v>14.001</v>
+        <v>12.258</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4175</v>
+        <v>0.3612</v>
       </c>
       <c r="J138" t="n">
-        <v>12.525</v>
+        <v>10.836</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1826</v>
+        <v>0.1463</v>
       </c>
       <c r="J139" t="n">
-        <v>5.478</v>
+        <v>4.389</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.95</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0925</v>
+        <v>-0.0757</v>
       </c>
       <c r="J140" t="n">
-        <v>-2.775</v>
+        <v>-2.271</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.95</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.0925</v>
+        <v>-0.0757</v>
       </c>
       <c r="J141" t="n">
-        <v>-2.775</v>
+        <v>-2.271</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.02</v>
       </c>
       <c r="I142" t="n">
-        <v>0.0985</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>2.167</v>
+        <v>1.6038</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.01</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0673</v>
+        <v>0.0482</v>
       </c>
       <c r="J143" t="n">
-        <v>1.4806</v>
+        <v>1.0604</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>0.92</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1137</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.5014</v>
+        <v>-2.1692</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>0.86</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1796</v>
+        <v>-0.1613</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.9512</v>
+        <v>-3.5486</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>0.52</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4948</v>
+        <v>-0.4941</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.8856</v>
+        <v>-10.8702</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>1.54</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1331</v>
+        <v>1.1467</v>
       </c>
       <c r="J147" t="n">
-        <v>24.9282</v>
+        <v>25.2274</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>1.47</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0382</v>
+        <v>1.0446</v>
       </c>
       <c r="J148" t="n">
-        <v>22.8404</v>
+        <v>22.9812</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>1.32</v>
       </c>
       <c r="I149" t="n">
-        <v>0.7745</v>
+        <v>0.7551</v>
       </c>
       <c r="J149" t="n">
-        <v>17.039</v>
+        <v>16.6122</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>1.25</v>
       </c>
       <c r="I150" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.609</v>
       </c>
       <c r="J150" t="n">
-        <v>13.9612</v>
+        <v>13.398</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>1.09</v>
       </c>
       <c r="I151" t="n">
-        <v>0.2619</v>
+        <v>0.2309</v>
       </c>
       <c r="J151" t="n">
-        <v>5.7618</v>
+        <v>5.0798</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.1</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3375</v>
+        <v>0.299</v>
       </c>
       <c r="J152" t="n">
-        <v>8.1</v>
+        <v>7.176</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>0.72</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3025</v>
+        <v>-0.2873</v>
       </c>
       <c r="J153" t="n">
-        <v>-7.26</v>
+        <v>-6.8952</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.71</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3114</v>
+        <v>-0.2964</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.4736</v>
+        <v>-7.1136</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.7</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3204</v>
+        <v>-0.3055</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.6896</v>
+        <v>-7.332</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.44</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5503</v>
+        <v>-0.5556</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.2072</v>
+        <v>-13.3344</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.72</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3649</v>
+        <v>1.3877</v>
       </c>
       <c r="J157" t="n">
-        <v>32.7576</v>
+        <v>33.3048</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.61</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2247</v>
+        <v>1.2408</v>
       </c>
       <c r="J158" t="n">
-        <v>29.3928</v>
+        <v>29.7792</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.38</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8871</v>
+        <v>0.8743</v>
       </c>
       <c r="J159" t="n">
-        <v>21.2904</v>
+        <v>20.9832</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.08</v>
       </c>
       <c r="I160" t="n">
-        <v>0.235</v>
+        <v>0.2046</v>
       </c>
       <c r="J160" t="n">
-        <v>5.64</v>
+        <v>4.9104</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.479</v>
+        <v>-0.4427</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.496</v>
+        <v>-10.6248</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.28</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5804</v>
+        <v>0.5228</v>
       </c>
       <c r="J162" t="n">
-        <v>16.2512</v>
+        <v>14.6384</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.25</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5311</v>
+        <v>0.4732</v>
       </c>
       <c r="J163" t="n">
-        <v>14.8708</v>
+        <v>13.2496</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>0.78</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2674</v>
+        <v>-0.248</v>
       </c>
       <c r="J164" t="n">
-        <v>-7.4872</v>
+        <v>-6.944</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>0.74</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3058</v>
+        <v>-0.288</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.5624</v>
+        <v>-8.064</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3431</v>
+        <v>-0.3276</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.6068</v>
+        <v>-9.172800000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.42</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9958</v>
+        <v>0.9918</v>
       </c>
       <c r="J167" t="n">
-        <v>27.8824</v>
+        <v>27.7704</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1.27</v>
       </c>
       <c r="I168" t="n">
-        <v>0.701</v>
+        <v>0.6693</v>
       </c>
       <c r="J168" t="n">
-        <v>19.628</v>
+        <v>18.7404</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>1.21</v>
       </c>
       <c r="I169" t="n">
-        <v>0.573</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="J169" t="n">
-        <v>16.044</v>
+        <v>15.0304</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.97</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1629</v>
+        <v>-0.1313</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.5612</v>
+        <v>-3.6764</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.89</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3979</v>
+        <v>-0.3558</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.1412</v>
+        <v>-9.962400000000001</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.14</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3393</v>
+        <v>0.2861</v>
       </c>
       <c r="J172" t="n">
-        <v>9.500400000000001</v>
+        <v>8.0108</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.08</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2219</v>
+        <v>0.178</v>
       </c>
       <c r="J173" t="n">
-        <v>6.2132</v>
+        <v>4.984</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0058</v>
+        <v>0.0033</v>
       </c>
       <c r="J174" t="n">
-        <v>0.1624</v>
+        <v>0.0924</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>0.87</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1758</v>
+        <v>-0.1558</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.9224</v>
+        <v>-4.3624</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>0.66</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3796</v>
+        <v>-0.367</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.6288</v>
+        <v>-10.276</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.46</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0478</v>
+        <v>1.0529</v>
       </c>
       <c r="J177" t="n">
-        <v>29.3384</v>
+        <v>29.4812</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.2</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5452</v>
+        <v>0.5111</v>
       </c>
       <c r="J178" t="n">
-        <v>15.2656</v>
+        <v>14.3108</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.19</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5239</v>
+        <v>0.4895</v>
       </c>
       <c r="J179" t="n">
-        <v>14.6692</v>
+        <v>13.706</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>1.16</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4568</v>
+        <v>0.4221</v>
       </c>
       <c r="J180" t="n">
-        <v>12.7904</v>
+        <v>11.8188</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.0934</v>
+        <v>-0.0725</v>
       </c>
       <c r="J181" t="n">
-        <v>-2.6152</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.24</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4934</v>
+        <v>0.4344</v>
       </c>
       <c r="J182" t="n">
-        <v>14.802</v>
+        <v>13.032</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>1.04</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1212</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="J183" t="n">
-        <v>3.636</v>
+        <v>2.769</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>1.04</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1212</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="J184" t="n">
-        <v>3.636</v>
+        <v>2.769</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1014</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.042</v>
+        <v>-2.523</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.89</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1608</v>
+        <v>-0.1406</v>
       </c>
       <c r="J186" t="n">
-        <v>-4.824</v>
+        <v>-4.218</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.18</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5203</v>
+        <v>0.4801</v>
       </c>
       <c r="J187" t="n">
-        <v>15.609</v>
+        <v>14.403</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.15</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4501</v>
+        <v>0.4093</v>
       </c>
       <c r="J188" t="n">
-        <v>13.503</v>
+        <v>12.279</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4261</v>
+        <v>0.3855</v>
       </c>
       <c r="J189" t="n">
-        <v>12.783</v>
+        <v>11.565</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>1.05</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1896</v>
+        <v>0.1597</v>
       </c>
       <c r="J190" t="n">
-        <v>5.688</v>
+        <v>4.791</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.87</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4351</v>
+        <v>-0.3922</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.053</v>
+        <v>-11.766</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.63</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0424</v>
+        <v>1.0187</v>
       </c>
       <c r="J192" t="n">
-        <v>29.1872</v>
+        <v>28.5236</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>1.22</v>
       </c>
       <c r="I193" t="n">
-        <v>0.4535</v>
+        <v>0.3956</v>
       </c>
       <c r="J193" t="n">
-        <v>12.698</v>
+        <v>11.0768</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>0.92</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.129</v>
+        <v>-0.1099</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.612</v>
+        <v>-3.0772</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.79</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2679</v>
+        <v>-0.2489</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.5012</v>
+        <v>-6.9692</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.76</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.297</v>
+        <v>-0.2793</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.316000000000001</v>
+        <v>-7.8204</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.42</v>
       </c>
       <c r="I197" t="n">
-        <v>1.013</v>
+        <v>1.0128</v>
       </c>
       <c r="J197" t="n">
-        <v>28.364</v>
+        <v>28.3584</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.38</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9415</v>
+        <v>0.9286</v>
       </c>
       <c r="J198" t="n">
-        <v>26.362</v>
+        <v>26.0008</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.07</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2461</v>
+        <v>0.2125</v>
       </c>
       <c r="J199" t="n">
-        <v>6.8908</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>0.84</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5114</v>
+        <v>-0.4701</v>
       </c>
       <c r="J200" t="n">
-        <v>-14.3192</v>
+        <v>-13.1628</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>0.74</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7402</v>
+        <v>-0.7117</v>
       </c>
       <c r="J201" t="n">
-        <v>-20.7256</v>
+        <v>-19.9276</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>1.09</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3458</v>
+        <v>0.3167</v>
       </c>
       <c r="J202" t="n">
-        <v>6.916</v>
+        <v>6.334</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>0.62</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.3856</v>
+        <v>-0.3743</v>
       </c>
       <c r="J203" t="n">
-        <v>-7.712</v>
+        <v>-7.486</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>0.58</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.4209</v>
+        <v>-0.4117</v>
       </c>
       <c r="J204" t="n">
-        <v>-8.417999999999999</v>
+        <v>-8.234</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4386</v>
+        <v>-0.4307</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.772</v>
+        <v>-8.614000000000001</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.55</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4474</v>
+        <v>-0.4403</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.948</v>
+        <v>-8.805999999999999</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>2.12</v>
       </c>
       <c r="I207" t="n">
-        <v>1.8139</v>
+        <v>1.8738</v>
       </c>
       <c r="J207" t="n">
-        <v>36.278</v>
+        <v>37.476</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>1.71</v>
       </c>
       <c r="I208" t="n">
-        <v>1.3287</v>
+        <v>1.3507</v>
       </c>
       <c r="J208" t="n">
-        <v>26.574</v>
+        <v>27.014</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>1.57</v>
       </c>
       <c r="I209" t="n">
-        <v>1.1541</v>
+        <v>1.1713</v>
       </c>
       <c r="J209" t="n">
-        <v>23.082</v>
+        <v>23.426</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1352</v>
+        <v>-0.1196</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.704</v>
+        <v>-2.392</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.309</v>
+        <v>-0.2778</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.18</v>
+        <v>-5.556</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.95</v>
       </c>
       <c r="I212" t="n">
-        <v>1.6068</v>
+        <v>1.6463</v>
       </c>
       <c r="J212" t="n">
-        <v>33.7428</v>
+        <v>34.5723</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.68</v>
       </c>
       <c r="I213" t="n">
-        <v>1.2849</v>
+        <v>1.3064</v>
       </c>
       <c r="J213" t="n">
-        <v>26.9829</v>
+        <v>27.4344</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>1.38</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8665</v>
+        <v>0.8605</v>
       </c>
       <c r="J214" t="n">
-        <v>18.1965</v>
+        <v>18.0705</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>1.36</v>
       </c>
       <c r="I215" t="n">
-        <v>0.8285</v>
+        <v>0.8196</v>
       </c>
       <c r="J215" t="n">
-        <v>17.3985</v>
+        <v>17.2116</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>1.22</v>
       </c>
       <c r="I216" t="n">
-        <v>0.5444</v>
+        <v>0.5174</v>
       </c>
       <c r="J216" t="n">
-        <v>11.4324</v>
+        <v>10.8654</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>0.73</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.2645</v>
+        <v>-0.2508</v>
       </c>
       <c r="J217" t="n">
-        <v>-5.5545</v>
+        <v>-5.2668</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>0.55</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.4318</v>
+        <v>-0.4264</v>
       </c>
       <c r="J218" t="n">
-        <v>-9.0678</v>
+        <v>-8.9544</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>0.55</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4318</v>
+        <v>-0.4264</v>
       </c>
       <c r="J219" t="n">
-        <v>-9.0678</v>
+        <v>-8.9544</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>0.52</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4575</v>
+        <v>-0.4531</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.6075</v>
+        <v>-9.5151</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.48</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4924</v>
+        <v>-0.4903</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.3404</v>
+        <v>-10.2963</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.3</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7493</v>
+        <v>0.7228</v>
       </c>
       <c r="J222" t="n">
-        <v>21.7297</v>
+        <v>20.9612</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.25</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6475</v>
+        <v>0.6168</v>
       </c>
       <c r="J223" t="n">
-        <v>18.7775</v>
+        <v>17.8872</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.23</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6062</v>
+        <v>0.5744</v>
       </c>
       <c r="J224" t="n">
-        <v>17.5798</v>
+        <v>16.6576</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.17</v>
       </c>
       <c r="I225" t="n">
-        <v>0.4769</v>
+        <v>0.4432</v>
       </c>
       <c r="J225" t="n">
-        <v>13.8301</v>
+        <v>12.8528</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>1.15</v>
       </c>
       <c r="I226" t="n">
-        <v>0.4307</v>
+        <v>0.3968</v>
       </c>
       <c r="J226" t="n">
-        <v>12.4903</v>
+        <v>11.5072</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.14</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3629</v>
+        <v>0.311</v>
       </c>
       <c r="J227" t="n">
-        <v>10.5241</v>
+        <v>9.019</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>0.89</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1483</v>
+        <v>-0.1312</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.3007</v>
+        <v>-3.8048</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>0.85</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1899</v>
+        <v>-0.1712</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.5071</v>
+        <v>-4.9648</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.82</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2201</v>
+        <v>-0.2009</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.3829</v>
+        <v>-5.8261</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.64</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3895</v>
+        <v>-0.3773</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.2955</v>
+        <v>-10.9417</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.91</v>
       </c>
       <c r="I232" t="n">
-        <v>1.6166</v>
+        <v>1.6613</v>
       </c>
       <c r="J232" t="n">
-        <v>37.1818</v>
+        <v>38.2099</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>1.47</v>
       </c>
       <c r="I233" t="n">
-        <v>1.0487</v>
+        <v>1.0548</v>
       </c>
       <c r="J233" t="n">
-        <v>24.1201</v>
+        <v>24.2604</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>1.15</v>
       </c>
       <c r="I234" t="n">
-        <v>0.423</v>
+        <v>0.3906</v>
       </c>
       <c r="J234" t="n">
-        <v>9.728999999999999</v>
+        <v>8.9838</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.97</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1835</v>
+        <v>-0.1531</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.2205</v>
+        <v>-3.5213</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5188</v>
+        <v>-0.4818</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.9324</v>
+        <v>-11.0814</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.06</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2115</v>
+        <v>0.172</v>
       </c>
       <c r="J237" t="n">
-        <v>4.8645</v>
+        <v>3.956</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.01</v>
       </c>
       <c r="I238" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0589</v>
       </c>
       <c r="J238" t="n">
-        <v>1.8009</v>
+        <v>1.3547</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>0.82</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2168</v>
+        <v>-0.1988</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.9864</v>
+        <v>-4.5724</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3396</v>
+        <v>-0.3239</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.8108</v>
+        <v>-7.4497</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.55</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4648</v>
+        <v>-0.4599</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.6904</v>
+        <v>-10.5777</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.17</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3722</v>
+        <v>0.3176</v>
       </c>
       <c r="J242" t="n">
-        <v>13.3992</v>
+        <v>11.4336</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>1.15</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3371</v>
+        <v>0.2846</v>
       </c>
       <c r="J243" t="n">
-        <v>12.1356</v>
+        <v>10.2456</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>1.15</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3371</v>
+        <v>0.2846</v>
       </c>
       <c r="J244" t="n">
-        <v>12.1356</v>
+        <v>10.2456</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>1.04</v>
       </c>
       <c r="I245" t="n">
-        <v>0.12</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="J245" t="n">
-        <v>4.32</v>
+        <v>3.3048</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.73</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.324</v>
+        <v>-0.3079</v>
       </c>
       <c r="J246" t="n">
-        <v>-11.664</v>
+        <v>-11.0844</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.3</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7827</v>
+        <v>0.7547</v>
       </c>
       <c r="J247" t="n">
-        <v>28.1772</v>
+        <v>27.1692</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.27</v>
       </c>
       <c r="I248" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J248" t="n">
-        <v>25.8948</v>
+        <v>24.732</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.06</v>
       </c>
       <c r="I249" t="n">
-        <v>0.2193</v>
+        <v>0.187</v>
       </c>
       <c r="J249" t="n">
-        <v>7.8948</v>
+        <v>6.732</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>0.95</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2148</v>
+        <v>-0.1781</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.7328</v>
+        <v>-6.4116</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5412</v>
       </c>
       <c r="J251" t="n">
-        <v>-20.8836</v>
+        <v>-19.4832</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.49</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1043</v>
+        <v>1.1162</v>
       </c>
       <c r="J252" t="n">
-        <v>30.9204</v>
+        <v>31.2536</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.38</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9266</v>
+        <v>0.9115</v>
       </c>
       <c r="J253" t="n">
-        <v>25.9448</v>
+        <v>25.522</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>1.37</v>
       </c>
       <c r="I254" t="n">
-        <v>0.9072</v>
+        <v>0.8899</v>
       </c>
       <c r="J254" t="n">
-        <v>25.4016</v>
+        <v>24.9172</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>0.83</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5448</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="J255" t="n">
-        <v>-15.2544</v>
+        <v>-14.154</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.63</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.9806</v>
+        <v>-0.9784</v>
       </c>
       <c r="J256" t="n">
-        <v>-27.4568</v>
+        <v>-27.3952</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.14</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3449</v>
+        <v>0.2918</v>
       </c>
       <c r="J257" t="n">
-        <v>9.6572</v>
+        <v>8.170400000000001</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>1.09</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2475</v>
+        <v>0.2012</v>
       </c>
       <c r="J258" t="n">
-        <v>6.93</v>
+        <v>5.6336</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>0.91</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1297</v>
+        <v>-0.1121</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.6316</v>
+        <v>-3.1388</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>0.82</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2257</v>
+        <v>-0.2055</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.3196</v>
+        <v>-5.754</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.68</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3593</v>
+        <v>-0.3449</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.0604</v>
+        <v>-9.6572</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.54</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1809</v>
+        <v>1.1969</v>
       </c>
       <c r="J262" t="n">
-        <v>29.5225</v>
+        <v>29.9225</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.27</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7098</v>
+        <v>0.6775</v>
       </c>
       <c r="J263" t="n">
-        <v>17.745</v>
+        <v>16.9375</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>0.99</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0779</v>
+        <v>-0.0575</v>
       </c>
       <c r="J264" t="n">
-        <v>-1.9475</v>
+        <v>-1.4375</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>0.92</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3098</v>
+        <v>-0.2685</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.745</v>
+        <v>-6.7125</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>0.85</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4917</v>
+        <v>-0.4502</v>
       </c>
       <c r="J266" t="n">
-        <v>-12.2925</v>
+        <v>-11.255</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.25</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5387</v>
+        <v>0.4818</v>
       </c>
       <c r="J267" t="n">
-        <v>13.4675</v>
+        <v>12.045</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>1.11</v>
       </c>
       <c r="I268" t="n">
-        <v>0.2881</v>
+        <v>0.2385</v>
       </c>
       <c r="J268" t="n">
-        <v>7.2025</v>
+        <v>5.9625</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.97</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0535</v>
+        <v>-0.043</v>
       </c>
       <c r="J269" t="n">
-        <v>-1.3375</v>
+        <v>-1.075</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.35</v>
+        <v>-0.3349</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.75</v>
+        <v>-8.3725</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.61</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.422</v>
+        <v>-0.4132</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.55</v>
+        <v>-10.33</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.34</v>
       </c>
       <c r="I272" t="n">
-        <v>0.8413</v>
+        <v>0.8187</v>
       </c>
       <c r="J272" t="n">
-        <v>21.0325</v>
+        <v>20.4675</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.24</v>
       </c>
       <c r="I273" t="n">
-        <v>0.6354</v>
+        <v>0.6015</v>
       </c>
       <c r="J273" t="n">
-        <v>15.885</v>
+        <v>15.0375</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>1.22</v>
       </c>
       <c r="I274" t="n">
-        <v>0.5927</v>
+        <v>0.5575</v>
       </c>
       <c r="J274" t="n">
-        <v>14.8175</v>
+        <v>13.9375</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>1.18</v>
       </c>
       <c r="I275" t="n">
-        <v>0.5053</v>
+        <v>0.4689</v>
       </c>
       <c r="J275" t="n">
-        <v>12.6325</v>
+        <v>11.7225</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.84</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5252</v>
+        <v>-0.4857</v>
       </c>
       <c r="J276" t="n">
-        <v>-13.13</v>
+        <v>-12.1425</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.11</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3137</v>
+        <v>0.2656</v>
       </c>
       <c r="J277" t="n">
-        <v>7.8425</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>0.93</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0984</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J278" t="n">
-        <v>-2.46</v>
+        <v>-2.1125</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>0.92</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1107</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J279" t="n">
-        <v>-2.7675</v>
+        <v>-2.405</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>0.63</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3956</v>
+        <v>-0.3837</v>
       </c>
       <c r="J280" t="n">
-        <v>-9.890000000000001</v>
+        <v>-9.592499999999999</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.61</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4134</v>
+        <v>-0.4032</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.335</v>
+        <v>-10.08</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.2</v>
       </c>
       <c r="I282" t="n">
-        <v>0.4292</v>
+        <v>0.3718</v>
       </c>
       <c r="J282" t="n">
-        <v>10.3008</v>
+        <v>8.9232</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.07</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1886</v>
+        <v>0.1495</v>
       </c>
       <c r="J283" t="n">
-        <v>4.5264</v>
+        <v>3.588</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>1.04</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1222</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="J284" t="n">
-        <v>2.9328</v>
+        <v>2.2272</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.92</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1253</v>
+        <v>-0.1065</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.0072</v>
+        <v>-2.556</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.87</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.182</v>
+        <v>-0.1614</v>
       </c>
       <c r="J286" t="n">
-        <v>-4.368</v>
+        <v>-3.8736</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.25</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6731</v>
+        <v>0.6384</v>
       </c>
       <c r="J287" t="n">
-        <v>16.1544</v>
+        <v>15.3216</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.14</v>
       </c>
       <c r="I288" t="n">
-        <v>0.424</v>
+        <v>0.3839</v>
       </c>
       <c r="J288" t="n">
-        <v>10.176</v>
+        <v>9.2136</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>1.09</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2997</v>
+        <v>0.2631</v>
       </c>
       <c r="J289" t="n">
-        <v>7.1928</v>
+        <v>6.3144</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>1.03</v>
       </c>
       <c r="I290" t="n">
-        <v>0.1232</v>
+        <v>0.1004</v>
       </c>
       <c r="J290" t="n">
-        <v>2.9568</v>
+        <v>2.4096</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2475</v>
+        <v>-0.2087</v>
       </c>
       <c r="J291" t="n">
-        <v>-5.94</v>
+        <v>-5.0088</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.43</v>
       </c>
       <c r="I292" t="n">
-        <v>0.8766</v>
+        <v>0.8504</v>
       </c>
       <c r="J292" t="n">
-        <v>5.2596</v>
+        <v>5.1024</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.04</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1655</v>
+        <v>0.1317</v>
       </c>
       <c r="J293" t="n">
-        <v>0.993</v>
+        <v>0.7902</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>0.59</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.429</v>
+        <v>-0.4202</v>
       </c>
       <c r="J294" t="n">
-        <v>-2.574</v>
+        <v>-2.5212</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.57</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4467</v>
+        <v>-0.4396</v>
       </c>
       <c r="J295" t="n">
-        <v>-2.6802</v>
+        <v>-2.6376</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.47</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5334</v>
+        <v>-0.5374</v>
       </c>
       <c r="J296" t="n">
-        <v>-3.2004</v>
+        <v>-3.2244</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.83</v>
       </c>
       <c r="I297" t="n">
-        <v>1.4945</v>
+        <v>1.5258</v>
       </c>
       <c r="J297" t="n">
-        <v>8.967000000000001</v>
+        <v>9.1548</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.61</v>
       </c>
       <c r="I298" t="n">
-        <v>1.2192</v>
+        <v>1.2355</v>
       </c>
       <c r="J298" t="n">
-        <v>7.3152</v>
+        <v>7.413</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>1.45</v>
       </c>
       <c r="I299" t="n">
-        <v>1.0039</v>
+        <v>1.0063</v>
       </c>
       <c r="J299" t="n">
-        <v>6.0234</v>
+        <v>6.0378</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>1.29</v>
       </c>
       <c r="I300" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.6911</v>
       </c>
       <c r="J300" t="n">
-        <v>4.2732</v>
+        <v>4.1466</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.64</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.9908</v>
+        <v>-0.9966</v>
       </c>
       <c r="J301" t="n">
-        <v>-5.9448</v>
+        <v>-5.9796</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.71</v>
       </c>
       <c r="I302" t="n">
-        <v>1.3715</v>
+        <v>1.3956</v>
       </c>
       <c r="J302" t="n">
-        <v>23.3155</v>
+        <v>23.7252</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.4</v>
       </c>
       <c r="I303" t="n">
-        <v>0.9384</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="J303" t="n">
-        <v>15.9528</v>
+        <v>15.7573</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>1.38</v>
       </c>
       <c r="I304" t="n">
-        <v>0.901</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="J304" t="n">
-        <v>15.317</v>
+        <v>15.0552</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.88</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4405</v>
+        <v>-0.401</v>
       </c>
       <c r="J305" t="n">
-        <v>-7.4885</v>
+        <v>-6.817</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.87</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4658</v>
+        <v>-0.4267</v>
       </c>
       <c r="J306" t="n">
-        <v>-7.9186</v>
+        <v>-7.2539</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.09</v>
       </c>
       <c r="I307" t="n">
-        <v>0.2525</v>
+        <v>0.206</v>
       </c>
       <c r="J307" t="n">
-        <v>4.2925</v>
+        <v>3.502</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>1.08</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2317</v>
+        <v>0.1871</v>
       </c>
       <c r="J308" t="n">
-        <v>3.9389</v>
+        <v>3.1807</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>0.99</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0181</v>
+        <v>-0.0133</v>
       </c>
       <c r="J309" t="n">
-        <v>-0.3077</v>
+        <v>-0.2261</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>0.82</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2238</v>
+        <v>-0.2039</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.8046</v>
+        <v>-3.4663</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4641</v>
+        <v>-0.46</v>
       </c>
       <c r="J311" t="n">
-        <v>-7.8897</v>
+        <v>-7.82</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.03</v>
       </c>
       <c r="I312" t="n">
-        <v>0.1571</v>
+        <v>0.1257</v>
       </c>
       <c r="J312" t="n">
-        <v>4.713</v>
+        <v>3.771</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>0.95</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1862</v>
+        <v>-0.1574</v>
       </c>
       <c r="J313" t="n">
-        <v>-5.586</v>
+        <v>-4.722</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2163</v>
+        <v>-0.1852</v>
       </c>
       <c r="J314" t="n">
-        <v>-6.489</v>
+        <v>-5.556</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.86</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.4253</v>
+        <v>-0.3848</v>
       </c>
       <c r="J315" t="n">
-        <v>-12.759</v>
+        <v>-11.544</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.76</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6577</v>
+        <v>-0.6218</v>
       </c>
       <c r="J316" t="n">
-        <v>-19.731</v>
+        <v>-18.654</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.49</v>
       </c>
       <c r="I317" t="n">
-        <v>0.8455</v>
+        <v>0.7923</v>
       </c>
       <c r="J317" t="n">
-        <v>25.365</v>
+        <v>23.769</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.27</v>
       </c>
       <c r="I318" t="n">
-        <v>0.5222</v>
+        <v>0.4634</v>
       </c>
       <c r="J318" t="n">
-        <v>15.666</v>
+        <v>13.902</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>1.11</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2562</v>
+        <v>0.213</v>
       </c>
       <c r="J319" t="n">
-        <v>7.686</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>1.02</v>
       </c>
       <c r="I320" t="n">
-        <v>0.0598</v>
+        <v>0.0439</v>
       </c>
       <c r="J320" t="n">
-        <v>1.794</v>
+        <v>1.317</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.73</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3301</v>
+        <v>-0.3152</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.903</v>
+        <v>-9.456</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.27</v>
       </c>
       <c r="I322" t="n">
-        <v>0.5354</v>
+        <v>0.4757</v>
       </c>
       <c r="J322" t="n">
-        <v>15.5266</v>
+        <v>13.7953</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.1</v>
       </c>
       <c r="I323" t="n">
-        <v>0.2435</v>
+        <v>0.1993</v>
       </c>
       <c r="J323" t="n">
-        <v>7.0615</v>
+        <v>5.7797</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.08</v>
       </c>
       <c r="I324" t="n">
-        <v>0.2044</v>
+        <v>0.1646</v>
       </c>
       <c r="J324" t="n">
-        <v>5.9276</v>
+        <v>4.7734</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>1.02</v>
       </c>
       <c r="I325" t="n">
-        <v>0.068</v>
+        <v>0.0498</v>
       </c>
       <c r="J325" t="n">
-        <v>1.972</v>
+        <v>1.4442</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.82</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2375</v>
+        <v>-0.2174</v>
       </c>
       <c r="J326" t="n">
-        <v>-6.8875</v>
+        <v>-6.3046</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.32</v>
       </c>
       <c r="I327" t="n">
-        <v>0.8268</v>
+        <v>0.8023</v>
       </c>
       <c r="J327" t="n">
-        <v>23.9772</v>
+        <v>23.2667</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>1.21</v>
       </c>
       <c r="I328" t="n">
-        <v>0.5903</v>
+        <v>0.5516</v>
       </c>
       <c r="J328" t="n">
-        <v>17.1187</v>
+        <v>15.9964</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>1</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0104</v>
+        <v>-0.0067</v>
       </c>
       <c r="J329" t="n">
-        <v>-0.3016</v>
+        <v>-0.1943</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>0.93</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.273</v>
+        <v>-0.2329</v>
       </c>
       <c r="J330" t="n">
-        <v>-7.917</v>
+        <v>-6.7541</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.89</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3823</v>
+        <v>-0.3393</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.0867</v>
+        <v>-9.839700000000001</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>1.27</v>
       </c>
       <c r="I332" t="n">
-        <v>0.6138</v>
+        <v>0.5669</v>
       </c>
       <c r="J332" t="n">
-        <v>14.7312</v>
+        <v>13.6056</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>0.9</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.1322</v>
+        <v>-0.1168</v>
       </c>
       <c r="J333" t="n">
-        <v>-3.1728</v>
+        <v>-2.8032</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>0.85</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.1869</v>
+        <v>-0.1697</v>
       </c>
       <c r="J334" t="n">
-        <v>-4.4856</v>
+        <v>-4.0728</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.66</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3665</v>
+        <v>-0.3525</v>
       </c>
       <c r="J335" t="n">
-        <v>-8.795999999999999</v>
+        <v>-8.460000000000001</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.43</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5677</v>
+        <v>-0.577</v>
       </c>
       <c r="J336" t="n">
-        <v>-13.6248</v>
+        <v>-13.848</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.67</v>
       </c>
       <c r="I337" t="n">
-        <v>1.3166</v>
+        <v>1.337</v>
       </c>
       <c r="J337" t="n">
-        <v>31.5984</v>
+        <v>32.088</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.45</v>
       </c>
       <c r="I338" t="n">
-        <v>1.0202</v>
+        <v>1.0217</v>
       </c>
       <c r="J338" t="n">
-        <v>24.4848</v>
+        <v>24.5208</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>1.33</v>
       </c>
       <c r="I339" t="n">
-        <v>0.8018</v>
+        <v>0.7801</v>
       </c>
       <c r="J339" t="n">
-        <v>19.2432</v>
+        <v>18.7224</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>1.03</v>
       </c>
       <c r="I340" t="n">
-        <v>0.0936</v>
+        <v>0.073</v>
       </c>
       <c r="J340" t="n">
-        <v>2.2464</v>
+        <v>1.752</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>0.83</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5655</v>
+        <v>-0.5302</v>
       </c>
       <c r="J341" t="n">
-        <v>-13.572</v>
+        <v>-12.7248</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.3</v>
       </c>
       <c r="I342" t="n">
-        <v>0.582</v>
+        <v>0.5221</v>
       </c>
       <c r="J342" t="n">
-        <v>16.296</v>
+        <v>14.6188</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.14</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3173</v>
+        <v>0.2665</v>
       </c>
       <c r="J343" t="n">
-        <v>8.884399999999999</v>
+        <v>7.462</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>1.12</v>
       </c>
       <c r="I344" t="n">
-        <v>0.2809</v>
+        <v>0.2331</v>
       </c>
       <c r="J344" t="n">
-        <v>7.8652</v>
+        <v>6.5268</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>0.96</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.0772</v>
+        <v>-0.0619</v>
       </c>
       <c r="J345" t="n">
-        <v>-2.1616</v>
+        <v>-1.7332</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.78</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2774</v>
+        <v>-0.2587</v>
       </c>
       <c r="J346" t="n">
-        <v>-7.7672</v>
+        <v>-7.2436</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.26</v>
       </c>
       <c r="I347" t="n">
-        <v>0.6995</v>
+        <v>0.666</v>
       </c>
       <c r="J347" t="n">
-        <v>19.586</v>
+        <v>18.648</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>1.19</v>
       </c>
       <c r="I348" t="n">
-        <v>0.5446</v>
+        <v>0.5047</v>
       </c>
       <c r="J348" t="n">
-        <v>15.2488</v>
+        <v>14.1316</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>1.09</v>
       </c>
       <c r="I349" t="n">
-        <v>0.3015</v>
+        <v>0.264</v>
       </c>
       <c r="J349" t="n">
-        <v>8.442</v>
+        <v>7.392</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2441</v>
+        <v>-0.2055</v>
       </c>
       <c r="J350" t="n">
-        <v>-6.8348</v>
+        <v>-5.754</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.88</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4085</v>
+        <v>-0.3655</v>
       </c>
       <c r="J351" t="n">
-        <v>-11.438</v>
+        <v>-10.234</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.3</v>
       </c>
       <c r="I352" t="n">
-        <v>0.6008</v>
+        <v>0.5423</v>
       </c>
       <c r="J352" t="n">
-        <v>18.024</v>
+        <v>16.269</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.08</v>
       </c>
       <c r="I353" t="n">
-        <v>0.2145</v>
+        <v>0.1717</v>
       </c>
       <c r="J353" t="n">
-        <v>6.435</v>
+        <v>5.151</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>0.95</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.0852</v>
+        <v>-0.0697</v>
       </c>
       <c r="J354" t="n">
-        <v>-2.556</v>
+        <v>-2.091</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.2414</v>
+        <v>-0.2212</v>
       </c>
       <c r="J355" t="n">
-        <v>-7.242</v>
+        <v>-6.636</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.8</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.2513</v>
+        <v>-0.2314</v>
       </c>
       <c r="J356" t="n">
-        <v>-7.539</v>
+        <v>-6.942</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.52</v>
       </c>
       <c r="I357" t="n">
-        <v>1.1334</v>
+        <v>1.146</v>
       </c>
       <c r="J357" t="n">
-        <v>34.002</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.41</v>
       </c>
       <c r="I358" t="n">
-        <v>0.9687</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="J358" t="n">
-        <v>29.061</v>
+        <v>28.806</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>1.12</v>
       </c>
       <c r="I359" t="n">
-        <v>0.3624</v>
+        <v>0.3283</v>
       </c>
       <c r="J359" t="n">
-        <v>10.872</v>
+        <v>9.849</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>1.12</v>
       </c>
       <c r="I360" t="n">
-        <v>0.3624</v>
+        <v>0.3283</v>
       </c>
       <c r="J360" t="n">
-        <v>10.872</v>
+        <v>9.849</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.79</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.6469</v>
+        <v>-0.6141</v>
       </c>
       <c r="J361" t="n">
-        <v>-19.407</v>
+        <v>-18.423</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.21</v>
       </c>
       <c r="I362" t="n">
-        <v>0.579</v>
+        <v>0.5415</v>
       </c>
       <c r="J362" t="n">
-        <v>20.844</v>
+        <v>19.494</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>1.16</v>
       </c>
       <c r="I363" t="n">
-        <v>0.4661</v>
+        <v>0.4272</v>
       </c>
       <c r="J363" t="n">
-        <v>16.7796</v>
+        <v>15.3792</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>1.1</v>
       </c>
       <c r="I364" t="n">
-        <v>0.3223</v>
+        <v>0.2863</v>
       </c>
       <c r="J364" t="n">
-        <v>11.6028</v>
+        <v>10.3068</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>1.09</v>
       </c>
       <c r="I365" t="n">
-        <v>0.2963</v>
+        <v>0.2614</v>
       </c>
       <c r="J365" t="n">
-        <v>10.6668</v>
+        <v>9.410399999999999</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>1.04</v>
       </c>
       <c r="I366" t="n">
-        <v>0.1516</v>
+        <v>0.1264</v>
       </c>
       <c r="J366" t="n">
-        <v>5.4576</v>
+        <v>4.5504</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.01</v>
       </c>
       <c r="I367" t="n">
-        <v>0.0598</v>
+        <v>0.0414</v>
       </c>
       <c r="J367" t="n">
-        <v>2.1528</v>
+        <v>1.4904</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>0.97</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.0508</v>
+        <v>-0.0409</v>
       </c>
       <c r="J368" t="n">
-        <v>-1.8288</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>0.9</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.1393</v>
+        <v>-0.1218</v>
       </c>
       <c r="J369" t="n">
-        <v>-5.0148</v>
+        <v>-4.3848</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>0.85</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.1923</v>
+        <v>-0.1728</v>
       </c>
       <c r="J370" t="n">
-        <v>-6.9228</v>
+        <v>-6.2208</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.76</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.2816</v>
+        <v>-0.2629</v>
       </c>
       <c r="J371" t="n">
-        <v>-10.1376</v>
+        <v>-9.464399999999999</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>0.93</v>
       </c>
       <c r="I372" t="n">
-        <v>-0.0677</v>
+        <v>-0.051</v>
       </c>
       <c r="J372" t="n">
-        <v>-1.4894</v>
+        <v>-1.122</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>0.91</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.0767</v>
       </c>
       <c r="J373" t="n">
-        <v>-2.0614</v>
+        <v>-1.6874</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>0.59</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.4121</v>
+        <v>-0.4023</v>
       </c>
       <c r="J374" t="n">
-        <v>-9.0662</v>
+        <v>-8.8506</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>0.59</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.4121</v>
+        <v>-0.4023</v>
       </c>
       <c r="J375" t="n">
-        <v>-9.0662</v>
+        <v>-8.8506</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>0.38</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.5961</v>
+        <v>-0.6079</v>
       </c>
       <c r="J376" t="n">
-        <v>-13.1142</v>
+        <v>-13.3738</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.69</v>
       </c>
       <c r="I377" t="n">
-        <v>1.3194</v>
+        <v>1.3398</v>
       </c>
       <c r="J377" t="n">
-        <v>29.0268</v>
+        <v>29.4756</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>1.4</v>
       </c>
       <c r="I378" t="n">
-        <v>0.9188</v>
+        <v>0.9107</v>
       </c>
       <c r="J378" t="n">
-        <v>20.2136</v>
+        <v>20.0354</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>1.34</v>
       </c>
       <c r="I379" t="n">
-        <v>0.8087</v>
+        <v>0.7932</v>
       </c>
       <c r="J379" t="n">
-        <v>17.7914</v>
+        <v>17.4504</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>1.3</v>
       </c>
       <c r="I380" t="n">
-        <v>0.731</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="J380" t="n">
-        <v>16.082</v>
+        <v>15.6464</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>1.13</v>
       </c>
       <c r="I381" t="n">
-        <v>0.3587</v>
+        <v>0.3267</v>
       </c>
       <c r="J381" t="n">
-        <v>7.8914</v>
+        <v>7.1874</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.22</v>
       </c>
       <c r="I382" t="n">
-        <v>0.4758</v>
+        <v>0.4176</v>
       </c>
       <c r="J382" t="n">
-        <v>13.3224</v>
+        <v>11.6928</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.18</v>
       </c>
       <c r="I383" t="n">
-        <v>0.4069</v>
+        <v>0.3505</v>
       </c>
       <c r="J383" t="n">
-        <v>11.3932</v>
+        <v>9.814</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.05</v>
       </c>
       <c r="I384" t="n">
-        <v>0.153</v>
+        <v>0.1176</v>
       </c>
       <c r="J384" t="n">
-        <v>4.284</v>
+        <v>3.2928</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>0.85</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.1986</v>
+        <v>-0.1781</v>
       </c>
       <c r="J385" t="n">
-        <v>-5.5608</v>
+        <v>-4.9868</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>0.54</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.4865</v>
+        <v>-0.4859</v>
       </c>
       <c r="J386" t="n">
-        <v>-13.622</v>
+        <v>-13.6052</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.27</v>
       </c>
       <c r="I387" t="n">
-        <v>0.7138</v>
+        <v>0.6815</v>
       </c>
       <c r="J387" t="n">
-        <v>19.9864</v>
+        <v>19.082</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>1.14</v>
       </c>
       <c r="I388" t="n">
-        <v>0.4226</v>
+        <v>0.3829</v>
       </c>
       <c r="J388" t="n">
-        <v>11.8328</v>
+        <v>10.7212</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>1.07</v>
       </c>
       <c r="I389" t="n">
-        <v>0.245</v>
+        <v>0.2119</v>
       </c>
       <c r="J389" t="n">
-        <v>6.86</v>
+        <v>5.9332</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>1.04</v>
       </c>
       <c r="I390" t="n">
-        <v>0.1552</v>
+        <v>0.1292</v>
       </c>
       <c r="J390" t="n">
-        <v>4.3456</v>
+        <v>3.6176</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.97</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.1529</v>
+        <v>-0.1218</v>
       </c>
       <c r="J391" t="n">
-        <v>-4.2812</v>
+        <v>-3.4104</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>1.27</v>
       </c>
       <c r="I392" t="n">
-        <v>0.6148</v>
+        <v>0.5682</v>
       </c>
       <c r="J392" t="n">
-        <v>15.9848</v>
+        <v>14.7732</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>0.85</v>
       </c>
       <c r="I393" t="n">
-        <v>-0.1867</v>
+        <v>-0.1695</v>
       </c>
       <c r="J393" t="n">
-        <v>-4.8542</v>
+        <v>-4.407</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>0.77</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.2643</v>
+        <v>-0.2462</v>
       </c>
       <c r="J394" t="n">
-        <v>-6.8718</v>
+        <v>-6.4012</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.68</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.3481</v>
+        <v>-0.3329</v>
       </c>
       <c r="J395" t="n">
-        <v>-9.050599999999999</v>
+        <v>-8.6554</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.53</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.4816</v>
+        <v>-0.4786</v>
       </c>
       <c r="J396" t="n">
-        <v>-12.5216</v>
+        <v>-12.4436</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>1.41</v>
       </c>
       <c r="I397" t="n">
-        <v>0.9606</v>
+        <v>0.9516</v>
       </c>
       <c r="J397" t="n">
-        <v>24.9756</v>
+        <v>24.7416</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.32</v>
       </c>
       <c r="I398" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.7638</v>
       </c>
       <c r="J398" t="n">
-        <v>20.4828</v>
+        <v>19.8588</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>1.29</v>
       </c>
       <c r="I399" t="n">
-        <v>0.7279</v>
+        <v>0.7007</v>
       </c>
       <c r="J399" t="n">
-        <v>18.9254</v>
+        <v>18.2182</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>1.13</v>
       </c>
       <c r="I400" t="n">
-        <v>0.3815</v>
+        <v>0.3481</v>
       </c>
       <c r="J400" t="n">
-        <v>9.919</v>
+        <v>9.050599999999999</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>0.99</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.0983</v>
+        <v>-0.0776</v>
       </c>
       <c r="J401" t="n">
-        <v>-2.5558</v>
+        <v>-2.0176</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.18</v>
       </c>
       <c r="I402" t="n">
-        <v>0.4132</v>
+        <v>0.357</v>
       </c>
       <c r="J402" t="n">
-        <v>9.9168</v>
+        <v>8.568</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.08</v>
       </c>
       <c r="I403" t="n">
-        <v>0.2232</v>
+        <v>0.1791</v>
       </c>
       <c r="J403" t="n">
-        <v>5.3568</v>
+        <v>4.2984</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>1.05</v>
       </c>
       <c r="I404" t="n">
-        <v>0.1575</v>
+        <v>0.1213</v>
       </c>
       <c r="J404" t="n">
-        <v>3.78</v>
+        <v>2.9112</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>0.78</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.2668</v>
+        <v>-0.2474</v>
       </c>
       <c r="J405" t="n">
-        <v>-6.4032</v>
+        <v>-5.9376</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.63</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.4059</v>
+        <v>-0.3957</v>
       </c>
       <c r="J406" t="n">
-        <v>-9.7416</v>
+        <v>-9.4968</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.28</v>
       </c>
       <c r="I407" t="n">
-        <v>0.721</v>
+        <v>0.6904</v>
       </c>
       <c r="J407" t="n">
-        <v>17.304</v>
+        <v>16.5696</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.27</v>
       </c>
       <c r="I408" t="n">
-        <v>0.7002</v>
+        <v>0.6686</v>
       </c>
       <c r="J408" t="n">
-        <v>16.8048</v>
+        <v>16.0464</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>1.24</v>
       </c>
       <c r="I409" t="n">
-        <v>0.6369</v>
+        <v>0.6027</v>
       </c>
       <c r="J409" t="n">
-        <v>15.2856</v>
+        <v>14.4648</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>1.01</v>
       </c>
       <c r="I410" t="n">
-        <v>0.034</v>
+        <v>0.024</v>
       </c>
       <c r="J410" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.576</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.98</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.127</v>
+        <v>-0.0997</v>
       </c>
       <c r="J411" t="n">
-        <v>-3.048</v>
+        <v>-2.3928</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.34</v>
       </c>
       <c r="I412" t="n">
-        <v>0.67</v>
+        <v>0.6139</v>
       </c>
       <c r="J412" t="n">
-        <v>34.84</v>
+        <v>31.9228</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.03</v>
       </c>
       <c r="I413" t="n">
-        <v>0.1046</v>
+        <v>0.0769</v>
       </c>
       <c r="J413" t="n">
-        <v>5.4392</v>
+        <v>3.9988</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>0.85</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.1986</v>
+        <v>-0.1781</v>
       </c>
       <c r="J414" t="n">
-        <v>-10.3272</v>
+        <v>-9.261200000000001</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>0.83</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.2193</v>
+        <v>-0.1988</v>
       </c>
       <c r="J415" t="n">
-        <v>-11.4036</v>
+        <v>-10.3376</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.79</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.2593</v>
+        <v>-0.2396</v>
       </c>
       <c r="J416" t="n">
-        <v>-13.4836</v>
+        <v>-12.4592</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.51</v>
       </c>
       <c r="I417" t="n">
-        <v>1.1248</v>
+        <v>1.1373</v>
       </c>
       <c r="J417" t="n">
-        <v>58.4896</v>
+        <v>59.1396</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.29</v>
       </c>
       <c r="I418" t="n">
-        <v>0.7386</v>
+        <v>0.7095</v>
       </c>
       <c r="J418" t="n">
-        <v>38.4072</v>
+        <v>36.894</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>1.08</v>
       </c>
       <c r="I419" t="n">
-        <v>0.2616</v>
+        <v>0.2299</v>
       </c>
       <c r="J419" t="n">
-        <v>13.6032</v>
+        <v>11.9548</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>1.02</v>
       </c>
       <c r="I420" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0566</v>
       </c>
       <c r="J420" t="n">
-        <v>3.7908</v>
+        <v>2.9432</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.95</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.2319</v>
+        <v>-0.195</v>
       </c>
       <c r="J421" t="n">
-        <v>-12.0588</v>
+        <v>-10.14</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.45</v>
       </c>
       <c r="I422" t="n">
-        <v>1.063</v>
+        <v>1.0717</v>
       </c>
       <c r="J422" t="n">
-        <v>28.701</v>
+        <v>28.9359</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.03</v>
       </c>
       <c r="I423" t="n">
-        <v>0.1248</v>
+        <v>0.1016</v>
       </c>
       <c r="J423" t="n">
-        <v>3.3696</v>
+        <v>2.7432</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>0.98</v>
       </c>
       <c r="I424" t="n">
-        <v>-0.1131</v>
+        <v>-0.0868</v>
       </c>
       <c r="J424" t="n">
-        <v>-3.0537</v>
+        <v>-2.3436</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>0.97</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.1496</v>
+        <v>-0.1188</v>
       </c>
       <c r="J425" t="n">
-        <v>-4.0392</v>
+        <v>-3.2076</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>0.97</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.1496</v>
+        <v>-0.1188</v>
       </c>
       <c r="J426" t="n">
-        <v>-4.0392</v>
+        <v>-3.2076</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.65</v>
       </c>
       <c r="I427" t="n">
-        <v>1.0811</v>
+        <v>1.0693</v>
       </c>
       <c r="J427" t="n">
-        <v>29.1897</v>
+        <v>28.8711</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>1.02</v>
       </c>
       <c r="I428" t="n">
-        <v>0.0727</v>
+        <v>0.0521</v>
       </c>
       <c r="J428" t="n">
-        <v>1.9629</v>
+        <v>1.4067</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.9</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.1475</v>
+        <v>-0.1278</v>
       </c>
       <c r="J429" t="n">
-        <v>-3.9825</v>
+        <v>-3.4506</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.74</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.311</v>
+        <v>-0.2937</v>
       </c>
       <c r="J430" t="n">
-        <v>-8.397</v>
+        <v>-7.9299</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.72</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.3297</v>
+        <v>-0.3137</v>
       </c>
       <c r="J431" t="n">
-        <v>-8.901899999999999</v>
+        <v>-8.469900000000001</v>
       </c>
     </row>
     <row r="432">
@@ -20549,10 +20549,10 @@
         <v>1.59</v>
       </c>
       <c r="I432" t="n">
-        <v>1.2005</v>
+        <v>1.2157</v>
       </c>
       <c r="J432" t="n">
-        <v>26.411</v>
+        <v>26.7454</v>
       </c>
     </row>
     <row r="433">
@@ -20589,10 +20589,10 @@
         <v>1.5</v>
       </c>
       <c r="I433" t="n">
-        <v>1.0819</v>
+        <v>1.093</v>
       </c>
       <c r="J433" t="n">
-        <v>23.8018</v>
+        <v>24.046</v>
       </c>
     </row>
     <row r="434">
@@ -20629,10 +20629,10 @@
         <v>1.36</v>
       </c>
       <c r="I434" t="n">
-        <v>0.8508</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="J434" t="n">
-        <v>18.7176</v>
+        <v>18.3744</v>
       </c>
     </row>
     <row r="435">
@@ -20669,10 +20669,10 @@
         <v>1.15</v>
       </c>
       <c r="I435" t="n">
-        <v>0.4149</v>
+        <v>0.3832</v>
       </c>
       <c r="J435" t="n">
-        <v>9.127800000000001</v>
+        <v>8.430400000000001</v>
       </c>
     </row>
     <row r="436">
@@ -20709,10 +20709,10 @@
         <v>1.01</v>
       </c>
       <c r="I436" t="n">
-        <v>0.0058</v>
+        <v>-0.0052</v>
       </c>
       <c r="J436" t="n">
-        <v>0.1276</v>
+        <v>-0.1144</v>
       </c>
     </row>
     <row r="437">
@@ -20749,10 +20749,10 @@
         <v>1.04</v>
       </c>
       <c r="I437" t="n">
-        <v>0.1926</v>
+        <v>0.1622</v>
       </c>
       <c r="J437" t="n">
-        <v>4.2372</v>
+        <v>3.5684</v>
       </c>
     </row>
     <row r="438">
@@ -20789,10 +20789,10 @@
         <v>0.84</v>
       </c>
       <c r="I438" t="n">
-        <v>-0.1884</v>
+        <v>-0.1727</v>
       </c>
       <c r="J438" t="n">
-        <v>-4.1448</v>
+        <v>-3.7994</v>
       </c>
     </row>
     <row r="439">
@@ -20829,10 +20829,10 @@
         <v>0.83</v>
       </c>
       <c r="I439" t="n">
-        <v>-0.1989</v>
+        <v>-0.1832</v>
       </c>
       <c r="J439" t="n">
-        <v>-4.3758</v>
+        <v>-4.0304</v>
       </c>
     </row>
     <row r="440">
@@ -20869,10 +20869,10 @@
         <v>0.53</v>
       </c>
       <c r="I440" t="n">
-        <v>-0.4736</v>
+        <v>-0.4691</v>
       </c>
       <c r="J440" t="n">
-        <v>-10.4192</v>
+        <v>-10.3202</v>
       </c>
     </row>
     <row r="441">
@@ -20909,10 +20909,10 @@
         <v>0.5</v>
       </c>
       <c r="I441" t="n">
-        <v>-0.4999</v>
+        <v>-0.4984</v>
       </c>
       <c r="J441" t="n">
-        <v>-10.9978</v>
+        <v>-10.9648</v>
       </c>
     </row>
     <row r="442">
@@ -20949,10 +20949,10 @@
         <v>1.36</v>
       </c>
       <c r="I442" t="n">
-        <v>0.6612</v>
+        <v>0.6019</v>
       </c>
       <c r="J442" t="n">
-        <v>18.5136</v>
+        <v>16.8532</v>
       </c>
     </row>
     <row r="443">
@@ -20989,10 +20989,10 @@
         <v>1.24</v>
       </c>
       <c r="I443" t="n">
-        <v>0.4771</v>
+        <v>0.4192</v>
       </c>
       <c r="J443" t="n">
-        <v>13.3588</v>
+        <v>11.7376</v>
       </c>
     </row>
     <row r="444">
@@ -21029,10 +21029,10 @@
         <v>1.03</v>
       </c>
       <c r="I444" t="n">
-        <v>0.0882</v>
+        <v>0.0669</v>
       </c>
       <c r="J444" t="n">
-        <v>2.4696</v>
+        <v>1.8732</v>
       </c>
     </row>
     <row r="445">
@@ -21069,10 +21069,10 @@
         <v>0.98</v>
       </c>
       <c r="I445" t="n">
-        <v>-0.0511</v>
+        <v>-0.039</v>
       </c>
       <c r="J445" t="n">
-        <v>-1.4308</v>
+        <v>-1.092</v>
       </c>
     </row>
     <row r="446">
@@ -21109,10 +21109,10 @@
         <v>0.95</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.0951</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="J446" t="n">
-        <v>-2.6628</v>
+        <v>-2.1896</v>
       </c>
     </row>
     <row r="447">
@@ -21149,10 +21149,10 @@
         <v>1.39</v>
       </c>
       <c r="I447" t="n">
-        <v>0.9819</v>
+        <v>0.9779</v>
       </c>
       <c r="J447" t="n">
-        <v>27.4932</v>
+        <v>27.3812</v>
       </c>
     </row>
     <row r="448">
@@ -21189,10 +21189,10 @@
         <v>1.11</v>
       </c>
       <c r="I448" t="n">
-        <v>0.3621</v>
+        <v>0.3204</v>
       </c>
       <c r="J448" t="n">
-        <v>10.1388</v>
+        <v>8.9712</v>
       </c>
     </row>
     <row r="449">
@@ -21229,10 +21229,10 @@
         <v>1.07</v>
       </c>
       <c r="I449" t="n">
-        <v>0.2543</v>
+        <v>0.217</v>
       </c>
       <c r="J449" t="n">
-        <v>7.1204</v>
+        <v>6.076</v>
       </c>
     </row>
     <row r="450">
@@ -21269,10 +21269,10 @@
         <v>0.8</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.5929</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="J450" t="n">
-        <v>-16.6012</v>
+        <v>-15.5092</v>
       </c>
     </row>
     <row r="451">
@@ -21309,10 +21309,10 @@
         <v>0.76</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.6835</v>
+        <v>-0.6496</v>
       </c>
       <c r="J451" t="n">
-        <v>-19.138</v>
+        <v>-18.1888</v>
       </c>
     </row>
     <row r="452">
@@ -21349,10 +21349,10 @@
         <v>1.69</v>
       </c>
       <c r="I452" t="n">
-        <v>1.0779</v>
+        <v>1.0571</v>
       </c>
       <c r="J452" t="n">
-        <v>32.337</v>
+        <v>31.713</v>
       </c>
     </row>
     <row r="453">
@@ -21389,10 +21389,10 @@
         <v>1.29</v>
       </c>
       <c r="I453" t="n">
-        <v>0.5457</v>
+        <v>0.4872</v>
       </c>
       <c r="J453" t="n">
-        <v>16.371</v>
+        <v>14.616</v>
       </c>
     </row>
     <row r="454">
@@ -21429,10 +21429,10 @@
         <v>1.14</v>
       </c>
       <c r="I454" t="n">
-        <v>0.306</v>
+        <v>0.2598</v>
       </c>
       <c r="J454" t="n">
-        <v>9.18</v>
+        <v>7.794</v>
       </c>
     </row>
     <row r="455">
@@ -21469,10 +21469,10 @@
         <v>0.86</v>
       </c>
       <c r="I455" t="n">
-        <v>-0.205</v>
+        <v>-0.1851</v>
       </c>
       <c r="J455" t="n">
-        <v>-6.15</v>
+        <v>-5.553</v>
       </c>
     </row>
     <row r="456">
@@ -21509,10 +21509,10 @@
         <v>0.86</v>
       </c>
       <c r="I456" t="n">
-        <v>-0.205</v>
+        <v>-0.1851</v>
       </c>
       <c r="J456" t="n">
-        <v>-6.15</v>
+        <v>-5.553</v>
       </c>
     </row>
     <row r="457">
@@ -21549,10 +21549,10 @@
         <v>1.23</v>
       </c>
       <c r="I457" t="n">
-        <v>0.6437</v>
+        <v>0.6069</v>
       </c>
       <c r="J457" t="n">
-        <v>19.311</v>
+        <v>18.207</v>
       </c>
     </row>
     <row r="458">
@@ -21589,10 +21589,10 @@
         <v>1.17</v>
       </c>
       <c r="I458" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.465</v>
       </c>
       <c r="J458" t="n">
-        <v>15.198</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="459">
@@ -21629,10 +21629,10 @@
         <v>1.07</v>
       </c>
       <c r="I459" t="n">
-        <v>0.2522</v>
+        <v>0.2156</v>
       </c>
       <c r="J459" t="n">
-        <v>7.566</v>
+        <v>6.468</v>
       </c>
     </row>
     <row r="460">
@@ -21669,10 +21669,10 @@
         <v>0.98</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.1056</v>
+        <v>-0.0806</v>
       </c>
       <c r="J460" t="n">
-        <v>-3.168</v>
+        <v>-2.418</v>
       </c>
     </row>
     <row r="461">
@@ -21709,10 +21709,10 @@
         <v>0.74</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.7302</v>
+        <v>-0.6998</v>
       </c>
       <c r="J461" t="n">
-        <v>-21.906</v>
+        <v>-20.994</v>
       </c>
     </row>
   </sheetData>
